--- a/Matar Trainings.xlsx
+++ b/Matar Trainings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.karuru\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB870DCF-D471-4A3A-B767-27761993F598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE84F89-B5E6-4C84-B1E5-91CAF3F161A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2ACD8935-9A55-49F4-8AD3-9F8021E2249D}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="Cargo Matar SOPS" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cargo Matar SOPS'!$A$1:$AB$229</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Meta Data'!$A$1:$E$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cargo Matar SOPS'!$A$1:$AF$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Meta Data'!$A$1:$E$217</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="498">
   <si>
     <t>Emp. No.</t>
   </si>
@@ -706,42 +706,6 @@
     <t>Q0629</t>
   </si>
   <si>
-    <t>Q0630</t>
-  </si>
-  <si>
-    <t>Q0631</t>
-  </si>
-  <si>
-    <t>Q0632</t>
-  </si>
-  <si>
-    <t>Q0633</t>
-  </si>
-  <si>
-    <t>Q0634</t>
-  </si>
-  <si>
-    <t>Q0635</t>
-  </si>
-  <si>
-    <t>Q0636</t>
-  </si>
-  <si>
-    <t>Q0637</t>
-  </si>
-  <si>
-    <t>Q0638</t>
-  </si>
-  <si>
-    <t>Q0639</t>
-  </si>
-  <si>
-    <t>Q0640</t>
-  </si>
-  <si>
-    <t>Q0641</t>
-  </si>
-  <si>
     <t>Cargo</t>
   </si>
   <si>
@@ -916,6 +880,9 @@
     <t>Norbert Mueller</t>
   </si>
   <si>
+    <t>Management</t>
+  </si>
+  <si>
     <t>Mohamed Farkan Mohamed Sareek</t>
   </si>
   <si>
@@ -925,6 +892,9 @@
     <t>Abdunaser Ahmed Aragaw</t>
   </si>
   <si>
+    <t>CARGO CM</t>
+  </si>
+  <si>
     <t>Rizardo Villalobos</t>
   </si>
   <si>
@@ -934,6 +904,9 @@
     <t xml:space="preserve">Mahesh Ramachandra </t>
   </si>
   <si>
+    <t>CARGO PM</t>
+  </si>
+  <si>
     <t>Joel Cabrillos Misa</t>
   </si>
   <si>
@@ -1159,6 +1132,9 @@
     <t>Sooraj Kurisinkal Reji</t>
   </si>
   <si>
+    <t>IT/PLC</t>
+  </si>
+  <si>
     <t>Jose Isagani Jr. Jamero Alaan</t>
   </si>
   <si>
@@ -1492,6 +1468,9 @@
     <t>Quennan Carandang Cuesta</t>
   </si>
   <si>
+    <t>U5</t>
+  </si>
+  <si>
     <t>Lester John Fuentes Monter</t>
   </si>
   <si>
@@ -1559,21 +1538,6 @@
   </si>
   <si>
     <t>Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon</t>
-  </si>
-  <si>
-    <t>Management</t>
-  </si>
-  <si>
-    <t>CARGO CM</t>
-  </si>
-  <si>
-    <t>CARGO PM</t>
-  </si>
-  <si>
-    <t>IT/PLC</t>
-  </si>
-  <si>
-    <t>U5</t>
   </si>
 </sst>
 </file>
@@ -2026,7 +1990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC757972-15C5-427C-AB07-EDA7DBD0B6ED}">
-  <dimension ref="A1:AC229"/>
+  <dimension ref="A1:AC217"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.5546875" customWidth="1"/>
@@ -2078,13 +2042,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>505</v>
+        <v>278</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -2098,13 +2062,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -2118,13 +2082,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -2138,16 +2102,16 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -2160,16 +2124,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -2182,13 +2146,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -2202,16 +2166,16 @@
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -2224,16 +2188,16 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -2246,13 +2210,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -2266,16 +2230,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -2288,13 +2252,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>505</v>
+        <v>278</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2308,13 +2272,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -2328,16 +2292,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -2350,16 +2314,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -2372,13 +2336,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -2392,16 +2356,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -2414,16 +2378,16 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -2436,16 +2400,16 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -2458,16 +2422,16 @@
         <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -2480,16 +2444,16 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -2502,13 +2466,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -2522,13 +2486,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -2542,16 +2506,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -2564,16 +2528,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -2586,13 +2550,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -2606,13 +2570,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -2626,13 +2590,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -2646,16 +2610,16 @@
         <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -2668,13 +2632,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -2688,16 +2652,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -2710,13 +2674,13 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -2730,13 +2694,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -2750,13 +2714,13 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -2770,16 +2734,16 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -2792,16 +2756,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -2814,13 +2778,13 @@
         <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -2834,16 +2798,16 @@
         <v>40</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -2856,13 +2820,13 @@
         <v>41</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -2876,16 +2840,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -2898,16 +2862,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -2920,13 +2884,13 @@
         <v>44</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -2940,13 +2904,13 @@
         <v>45</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -2960,13 +2924,13 @@
         <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -2980,13 +2944,13 @@
         <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -3000,13 +2964,13 @@
         <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -3020,13 +2984,13 @@
         <v>49</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -3040,13 +3004,13 @@
         <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -3060,13 +3024,13 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -3080,13 +3044,13 @@
         <v>52</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -3100,13 +3064,13 @@
         <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -3120,13 +3084,13 @@
         <v>54</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -3140,13 +3104,13 @@
         <v>55</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -3160,16 +3124,16 @@
         <v>56</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -3182,13 +3146,13 @@
         <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>505</v>
+        <v>278</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -3202,13 +3166,13 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -3222,16 +3186,16 @@
         <v>59</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -3244,16 +3208,16 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -3266,16 +3230,16 @@
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -3288,16 +3252,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -3310,13 +3274,13 @@
         <v>63</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -3330,13 +3294,13 @@
         <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
@@ -3350,16 +3314,16 @@
         <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -3372,16 +3336,16 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -3394,13 +3358,13 @@
         <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -3414,13 +3378,13 @@
         <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -3434,13 +3398,13 @@
         <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -3454,13 +3418,13 @@
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
@@ -3474,13 +3438,13 @@
         <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
@@ -3494,13 +3458,13 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
@@ -3514,16 +3478,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -3536,13 +3500,13 @@
         <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
@@ -3556,13 +3520,13 @@
         <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -3576,16 +3540,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -3598,13 +3562,13 @@
         <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -3618,16 +3582,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -3640,16 +3604,16 @@
         <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -3662,16 +3626,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -3684,13 +3648,13 @@
         <v>81</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
@@ -3704,16 +3668,16 @@
         <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
@@ -3726,16 +3690,16 @@
         <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
@@ -3748,13 +3712,13 @@
         <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
@@ -3768,13 +3732,13 @@
         <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>508</v>
+        <v>362</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -3788,13 +3752,13 @@
         <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
@@ -3808,13 +3772,13 @@
         <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -3828,13 +3792,13 @@
         <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
@@ -3848,13 +3812,13 @@
         <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
@@ -3868,13 +3832,13 @@
         <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -3888,13 +3852,13 @@
         <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
@@ -3908,16 +3872,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
@@ -3930,13 +3894,13 @@
         <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
@@ -3950,16 +3914,16 @@
         <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
@@ -3972,13 +3936,13 @@
         <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
@@ -3992,13 +3956,13 @@
         <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
@@ -4012,13 +3976,13 @@
         <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
@@ -4032,13 +3996,13 @@
         <v>98</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
@@ -4052,13 +4016,13 @@
         <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -4072,13 +4036,13 @@
         <v>100</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
@@ -4092,13 +4056,13 @@
         <v>101</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
@@ -4112,13 +4076,13 @@
         <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
@@ -4132,16 +4096,16 @@
         <v>103</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
@@ -4154,13 +4118,13 @@
         <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
@@ -4174,16 +4138,16 @@
         <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
@@ -4196,13 +4160,13 @@
         <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
@@ -4216,13 +4180,13 @@
         <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
@@ -4236,16 +4200,16 @@
         <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
@@ -4258,16 +4222,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
@@ -4280,16 +4244,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
@@ -4302,16 +4266,16 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
@@ -4324,13 +4288,13 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
@@ -4344,13 +4308,13 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
@@ -4364,13 +4328,13 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>508</v>
+        <v>362</v>
       </c>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
@@ -4384,13 +4348,13 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>508</v>
+        <v>362</v>
       </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
@@ -4404,13 +4368,13 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
@@ -4424,16 +4388,16 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
@@ -4446,13 +4410,13 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
@@ -4466,13 +4430,13 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
@@ -4486,13 +4450,13 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
@@ -4506,13 +4470,13 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
@@ -4526,13 +4490,13 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
@@ -4546,16 +4510,16 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
@@ -4568,13 +4532,13 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
@@ -4588,16 +4552,16 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
@@ -4610,13 +4574,13 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
@@ -4630,13 +4594,13 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
@@ -4650,16 +4614,16 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
@@ -4672,13 +4636,13 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
@@ -4692,13 +4656,13 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>508</v>
+        <v>362</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -4712,13 +4676,13 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>505</v>
+        <v>278</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -4732,13 +4696,13 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
@@ -4752,13 +4716,13 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>508</v>
+        <v>362</v>
       </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -4772,16 +4736,16 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
@@ -4794,13 +4758,13 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
@@ -4814,13 +4778,13 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
@@ -4834,16 +4798,16 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
@@ -4856,13 +4820,13 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
@@ -4876,16 +4840,16 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
@@ -4898,13 +4862,13 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
@@ -4918,16 +4882,16 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
@@ -4940,13 +4904,13 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
@@ -4960,13 +4924,13 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
@@ -4980,13 +4944,13 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
@@ -5000,13 +4964,13 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
@@ -5020,16 +4984,16 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
@@ -5042,13 +5006,13 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
@@ -5062,13 +5026,13 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
@@ -5082,13 +5046,13 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
@@ -5102,13 +5066,13 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
@@ -5122,16 +5086,16 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
@@ -5144,13 +5108,13 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
@@ -5164,16 +5128,16 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
@@ -5186,16 +5150,16 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
@@ -5208,13 +5172,13 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>508</v>
+        <v>362</v>
       </c>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
@@ -5228,13 +5192,13 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>508</v>
+        <v>362</v>
       </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
@@ -5248,16 +5212,16 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
@@ -5270,16 +5234,16 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
@@ -5292,13 +5256,13 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
@@ -5312,16 +5276,16 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
@@ -5334,16 +5298,16 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
@@ -5356,16 +5320,16 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
@@ -5378,16 +5342,16 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
@@ -5400,13 +5364,13 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
@@ -5420,13 +5384,13 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
@@ -5440,16 +5404,16 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
@@ -5462,13 +5426,13 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
@@ -5482,13 +5446,13 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
@@ -5502,13 +5466,13 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
@@ -5522,13 +5486,13 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
@@ -5542,13 +5506,13 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
@@ -5562,13 +5526,13 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
@@ -5582,16 +5546,16 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
@@ -5604,13 +5568,13 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>508</v>
+        <v>362</v>
       </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -5624,13 +5588,13 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
@@ -5644,13 +5608,13 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>505</v>
+        <v>278</v>
       </c>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
@@ -5664,13 +5628,13 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C175" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
@@ -5684,13 +5648,13 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
@@ -5704,16 +5668,16 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
@@ -5726,13 +5690,13 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
@@ -5746,16 +5710,16 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
@@ -5768,16 +5732,16 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
@@ -5790,16 +5754,16 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F181" s="1"/>
       <c r="G181" s="1"/>
@@ -5812,13 +5776,13 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>508</v>
+        <v>362</v>
       </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
@@ -5832,13 +5796,13 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>508</v>
+        <v>362</v>
       </c>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
@@ -5852,16 +5816,16 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
@@ -5874,13 +5838,13 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>505</v>
+        <v>278</v>
       </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
@@ -5894,13 +5858,13 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
@@ -5914,16 +5878,16 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F187" s="1"/>
       <c r="G187" s="1"/>
@@ -5936,16 +5900,16 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
@@ -5958,13 +5922,13 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
@@ -5978,13 +5942,13 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
@@ -5998,16 +5962,16 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
@@ -6020,16 +5984,16 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
@@ -6042,16 +6006,16 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
@@ -6064,16 +6028,16 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>509</v>
+        <v>474</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F194" s="1"/>
       <c r="G194" s="1"/>
@@ -6086,13 +6050,13 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
@@ -6106,16 +6070,16 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
@@ -6128,13 +6092,13 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
@@ -6148,13 +6112,13 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
@@ -6168,16 +6132,16 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
@@ -6190,16 +6154,16 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
@@ -6212,13 +6176,13 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
@@ -6232,13 +6196,13 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
@@ -6252,16 +6216,16 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
@@ -6274,16 +6238,16 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
@@ -6296,16 +6260,16 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
@@ -6318,13 +6282,13 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
@@ -6338,16 +6302,16 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F207" s="1"/>
       <c r="G207" s="1"/>
@@ -6360,16 +6324,16 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
@@ -6382,16 +6346,16 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>506</v>
+        <v>282</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F209" s="1"/>
       <c r="G209" s="1"/>
@@ -6404,13 +6368,13 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>505</v>
+        <v>278</v>
       </c>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
@@ -6424,13 +6388,13 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>508</v>
+        <v>362</v>
       </c>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
@@ -6444,13 +6408,13 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
@@ -6464,13 +6428,13 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
@@ -6484,16 +6448,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F214" s="1"/>
       <c r="G214" s="1"/>
@@ -6506,13 +6470,13 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
@@ -6526,16 +6490,16 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F216" s="1"/>
       <c r="G216" s="1"/>
@@ -6548,16 +6512,16 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F217" s="1"/>
       <c r="G217" s="1"/>
@@ -6565,248 +6529,8 @@
       <c r="I217" s="1"/>
       <c r="J217" s="1"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A218" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B218" s="1">
-        <v>0</v>
-      </c>
-      <c r="C218" s="1">
-        <v>0</v>
-      </c>
-      <c r="D218" s="1">
-        <v>0</v>
-      </c>
-      <c r="E218" s="1"/>
-      <c r="F218" s="1"/>
-      <c r="G218" s="1"/>
-      <c r="H218" s="1"/>
-      <c r="I218" s="1"/>
-      <c r="J218" s="1"/>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A219" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B219" s="1">
-        <v>0</v>
-      </c>
-      <c r="C219" s="1">
-        <v>0</v>
-      </c>
-      <c r="D219" s="1">
-        <v>0</v>
-      </c>
-      <c r="E219" s="1"/>
-      <c r="F219" s="1"/>
-      <c r="G219" s="1"/>
-      <c r="H219" s="1"/>
-      <c r="I219" s="1"/>
-      <c r="J219" s="1"/>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A220" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B220" s="1">
-        <v>0</v>
-      </c>
-      <c r="C220" s="1">
-        <v>0</v>
-      </c>
-      <c r="D220" s="1">
-        <v>0</v>
-      </c>
-      <c r="E220" s="1"/>
-      <c r="F220" s="1"/>
-      <c r="G220" s="1"/>
-      <c r="H220" s="1"/>
-      <c r="I220" s="1"/>
-      <c r="J220" s="1"/>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A221" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B221" s="1">
-        <v>0</v>
-      </c>
-      <c r="C221" s="1">
-        <v>0</v>
-      </c>
-      <c r="D221" s="1">
-        <v>0</v>
-      </c>
-      <c r="E221" s="1"/>
-      <c r="F221" s="1"/>
-      <c r="G221" s="1"/>
-      <c r="H221" s="1"/>
-      <c r="I221" s="1"/>
-      <c r="J221" s="1"/>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A222" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B222" s="1">
-        <v>0</v>
-      </c>
-      <c r="C222" s="1">
-        <v>0</v>
-      </c>
-      <c r="D222" s="1">
-        <v>0</v>
-      </c>
-      <c r="E222" s="1"/>
-      <c r="F222" s="1"/>
-      <c r="G222" s="1"/>
-      <c r="H222" s="1"/>
-      <c r="I222" s="1"/>
-      <c r="J222" s="1"/>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A223" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B223" s="1">
-        <v>0</v>
-      </c>
-      <c r="C223" s="1">
-        <v>0</v>
-      </c>
-      <c r="D223" s="1">
-        <v>0</v>
-      </c>
-      <c r="E223" s="1"/>
-      <c r="F223" s="1"/>
-      <c r="G223" s="1"/>
-      <c r="H223" s="1"/>
-      <c r="I223" s="1"/>
-      <c r="J223" s="1"/>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A224" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B224" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C224" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D224" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E224" s="1"/>
-      <c r="F224" s="1"/>
-      <c r="G224" s="1"/>
-      <c r="H224" s="1"/>
-      <c r="I224" s="1"/>
-      <c r="J224" s="1"/>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A225" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B225" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C225" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D225" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E225" s="1"/>
-      <c r="F225" s="1"/>
-      <c r="G225" s="1"/>
-      <c r="H225" s="1"/>
-      <c r="I225" s="1"/>
-      <c r="J225" s="1"/>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A226" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B226" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C226" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D226" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E226" s="1"/>
-      <c r="F226" s="1"/>
-      <c r="G226" s="1"/>
-      <c r="H226" s="1"/>
-      <c r="I226" s="1"/>
-      <c r="J226" s="1"/>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A227" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B227" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C227" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D227" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E227" s="1"/>
-      <c r="F227" s="1"/>
-      <c r="G227" s="1"/>
-      <c r="H227" s="1"/>
-      <c r="I227" s="1"/>
-      <c r="J227" s="1"/>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A228" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B228" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C228" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D228" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E228" s="1"/>
-      <c r="F228" s="1"/>
-      <c r="G228" s="1"/>
-      <c r="H228" s="1"/>
-      <c r="I228" s="1"/>
-      <c r="J228" s="1"/>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A229" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B229" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C229" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D229" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E229" s="1"/>
-      <c r="F229" s="1"/>
-      <c r="G229" s="1"/>
-      <c r="H229" s="1"/>
-      <c r="I229" s="1"/>
-      <c r="J229" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E229" xr:uid="{CC757972-15C5-427C-AB07-EDA7DBD0B6ED}"/>
+  <autoFilter ref="A1:E217" xr:uid="{CC757972-15C5-427C-AB07-EDA7DBD0B6ED}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6815,7 +6539,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3D0D685-D75C-4894-B13E-60533E1B3A71}">
-  <dimension ref="A1:AF229"/>
+  <dimension ref="A1:AF217"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" customWidth="1"/>
@@ -6851,79 +6575,79 @@
         <v>3</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="L1" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="Y1" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="M1" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="U1" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="V1" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="W1" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="X1" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y1" s="7" t="s">
-        <v>288</v>
-      </c>
       <c r="Z1" s="7" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="AA1" s="7" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="AB1" s="7" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="AC1" s="7"/>
       <c r="AD1" s="7"/>
@@ -6935,10 +6659,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -6977,10 +6701,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -7019,10 +6743,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -7061,10 +6785,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -7103,10 +6827,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -7145,10 +6869,10 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -7187,10 +6911,10 @@
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -7229,10 +6953,10 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -7271,10 +6995,10 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -7313,10 +7037,10 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -7355,10 +7079,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -7397,10 +7121,10 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -7439,10 +7163,10 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -7481,10 +7205,10 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -7523,10 +7247,10 @@
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -7565,10 +7289,10 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -7607,10 +7331,10 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -7649,10 +7373,10 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D19" s="1">
         <v>20</v>
@@ -7731,10 +7455,10 @@
         <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D20" s="1">
         <v>18</v>
@@ -7809,10 +7533,10 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D21" s="1">
         <v>18</v>
@@ -7887,10 +7611,10 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -7929,10 +7653,10 @@
         <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -7971,10 +7695,10 @@
         <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -8013,10 +7737,10 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D25" s="1">
         <v>21</v>
@@ -8097,10 +7821,10 @@
         <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -8139,10 +7863,10 @@
         <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -8181,10 +7905,10 @@
         <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -8223,10 +7947,10 @@
         <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D29" s="1">
         <v>14</v>
@@ -8293,10 +8017,10 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -8335,10 +8059,10 @@
         <v>33</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D31" s="1">
         <v>16</v>
@@ -8409,10 +8133,10 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
@@ -8451,10 +8175,10 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
@@ -8493,10 +8217,10 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
@@ -8535,10 +8259,10 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D35" s="1">
         <v>18</v>
@@ -8613,13 +8337,13 @@
         <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D36" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E36" s="8">
         <v>46176</v>
@@ -8663,7 +8387,9 @@
       <c r="R36" s="8">
         <v>46210</v>
       </c>
-      <c r="S36" s="6"/>
+      <c r="S36" s="6">
+        <v>46219</v>
+      </c>
       <c r="T36" s="6"/>
       <c r="U36" s="8">
         <v>46183</v>
@@ -8672,10 +8398,16 @@
         <v>46183</v>
       </c>
       <c r="W36" s="6"/>
-      <c r="X36" s="6"/>
-      <c r="Y36" s="6"/>
+      <c r="X36" s="6">
+        <v>46219</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>46219</v>
+      </c>
       <c r="Z36" s="6"/>
-      <c r="AA36" s="6"/>
+      <c r="AA36" s="6">
+        <v>46219</v>
+      </c>
       <c r="AB36" s="8">
         <v>46210</v>
       </c>
@@ -8689,10 +8421,10 @@
         <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
@@ -8731,10 +8463,10 @@
         <v>40</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D38" s="1">
         <v>4</v>
@@ -8781,10 +8513,10 @@
         <v>41</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
@@ -8823,10 +8555,10 @@
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D40" s="1">
         <v>21</v>
@@ -8907,10 +8639,10 @@
         <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D41" s="1">
         <v>21</v>
@@ -8991,10 +8723,10 @@
         <v>44</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
@@ -9033,10 +8765,10 @@
         <v>45</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
@@ -9075,10 +8807,10 @@
         <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
@@ -9117,10 +8849,10 @@
         <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
@@ -9159,10 +8891,10 @@
         <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
@@ -9201,10 +8933,10 @@
         <v>49</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
@@ -9243,10 +8975,10 @@
         <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
@@ -9285,10 +9017,10 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
@@ -9327,10 +9059,10 @@
         <v>52</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
@@ -9369,10 +9101,10 @@
         <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
@@ -9411,10 +9143,10 @@
         <v>54</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -9453,10 +9185,10 @@
         <v>55</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
@@ -9495,10 +9227,10 @@
         <v>56</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
@@ -9537,10 +9269,10 @@
         <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
@@ -9579,10 +9311,10 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -9621,10 +9353,10 @@
         <v>59</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D57" s="1">
         <v>21</v>
@@ -9705,10 +9437,10 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D58" s="1">
         <v>21</v>
@@ -9789,10 +9521,10 @@
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
@@ -9831,10 +9563,10 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D60" s="1">
         <v>4</v>
@@ -9881,10 +9613,10 @@
         <v>63</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
@@ -9923,10 +9655,10 @@
         <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
@@ -9965,10 +9697,10 @@
         <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D63" s="1">
         <v>14</v>
@@ -10035,10 +9767,10 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D64" s="1">
         <v>10</v>
@@ -10097,10 +9829,10 @@
         <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
@@ -10139,10 +9871,10 @@
         <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
@@ -10181,10 +9913,10 @@
         <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
@@ -10223,10 +9955,10 @@
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
@@ -10265,10 +9997,10 @@
         <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
@@ -10307,10 +10039,10 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
@@ -10349,13 +10081,13 @@
         <v>73</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D71" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E71" s="8">
         <v>46176</v>
@@ -10399,7 +10131,9 @@
       <c r="R71" s="8">
         <v>46210</v>
       </c>
-      <c r="S71" s="6"/>
+      <c r="S71" s="6">
+        <v>46219</v>
+      </c>
       <c r="T71" s="6"/>
       <c r="U71" s="6">
         <v>46183</v>
@@ -10408,10 +10142,16 @@
         <v>46183</v>
       </c>
       <c r="W71" s="6"/>
-      <c r="X71" s="6"/>
-      <c r="Y71" s="6"/>
+      <c r="X71" s="6">
+        <v>46219</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>46219</v>
+      </c>
       <c r="Z71" s="6"/>
-      <c r="AA71" s="6"/>
+      <c r="AA71" s="6">
+        <v>46219</v>
+      </c>
       <c r="AB71" s="8">
         <v>46210</v>
       </c>
@@ -10425,10 +10165,10 @@
         <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
@@ -10467,10 +10207,10 @@
         <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
@@ -10509,10 +10249,10 @@
         <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D74" s="1">
         <v>20</v>
@@ -10591,10 +10331,10 @@
         <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
@@ -10633,10 +10373,10 @@
         <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D76" s="1">
         <v>21</v>
@@ -10717,10 +10457,10 @@
         <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D77" s="1">
         <v>21</v>
@@ -10801,13 +10541,13 @@
         <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D78" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E78" s="8">
         <v>46156</v>
@@ -10837,11 +10577,21 @@
       <c r="N78" s="8">
         <v>46177</v>
       </c>
-      <c r="O78" s="6"/>
-      <c r="P78" s="6"/>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6"/>
+      <c r="O78" s="8">
+        <v>46223</v>
+      </c>
+      <c r="P78" s="8">
+        <v>46223</v>
+      </c>
+      <c r="Q78" s="8">
+        <v>46223</v>
+      </c>
+      <c r="R78" s="8">
+        <v>46223</v>
+      </c>
+      <c r="S78" s="8">
+        <v>46223</v>
+      </c>
       <c r="T78" s="6"/>
       <c r="U78" s="6">
         <v>46177</v>
@@ -10865,10 +10615,10 @@
         <v>81</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
@@ -10907,10 +10657,10 @@
         <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D80" s="1">
         <v>4</v>
@@ -10957,10 +10707,10 @@
         <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D81" s="1">
         <v>4</v>
@@ -11007,10 +10757,10 @@
         <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
@@ -11049,10 +10799,10 @@
         <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
@@ -11091,10 +10841,10 @@
         <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
@@ -11133,10 +10883,10 @@
         <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
@@ -11175,10 +10925,10 @@
         <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
@@ -11217,10 +10967,10 @@
         <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
@@ -11259,10 +11009,10 @@
         <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
@@ -11301,10 +11051,10 @@
         <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
@@ -11343,10 +11093,10 @@
         <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D90" s="1">
         <v>20</v>
@@ -11425,10 +11175,10 @@
         <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
@@ -11467,10 +11217,10 @@
         <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D92" s="1">
         <v>11</v>
@@ -11531,10 +11281,10 @@
         <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
@@ -11573,10 +11323,10 @@
         <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
@@ -11615,10 +11365,10 @@
         <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
@@ -11657,10 +11407,10 @@
         <v>98</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
@@ -11699,10 +11449,10 @@
         <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
@@ -11741,10 +11491,10 @@
         <v>100</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
@@ -11783,10 +11533,10 @@
         <v>101</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
@@ -11825,10 +11575,10 @@
         <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
@@ -11867,13 +11617,13 @@
         <v>103</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D101" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E101" s="8">
         <v>46156</v>
@@ -11900,18 +11650,20 @@
         <v>46162</v>
       </c>
       <c r="O101" s="8">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="P101" s="8">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="Q101" s="8">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="R101" s="8">
-        <v>46210</v>
-      </c>
-      <c r="S101" s="6"/>
+        <v>46223</v>
+      </c>
+      <c r="S101" s="8">
+        <v>46223</v>
+      </c>
       <c r="T101" s="6"/>
       <c r="U101" s="6"/>
       <c r="V101" s="6"/>
@@ -11933,10 +11685,10 @@
         <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
@@ -11975,10 +11727,10 @@
         <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D103" s="1">
         <v>20</v>
@@ -12057,10 +11809,10 @@
         <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
@@ -12099,10 +11851,10 @@
         <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
@@ -12141,10 +11893,10 @@
         <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D106" s="1">
         <v>18</v>
@@ -12219,10 +11971,10 @@
         <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
@@ -12261,10 +12013,10 @@
         <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D108" s="1">
         <v>4</v>
@@ -12311,10 +12063,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D109" s="1">
         <v>21</v>
@@ -12395,10 +12147,10 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
@@ -12437,10 +12189,10 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
@@ -12479,10 +12231,10 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
@@ -12521,10 +12273,10 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
@@ -12563,10 +12315,10 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
@@ -12605,13 +12357,13 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D115" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E115" s="8">
         <v>46176</v>
@@ -12655,7 +12407,9 @@
       <c r="R115" s="8">
         <v>46210</v>
       </c>
-      <c r="S115" s="6"/>
+      <c r="S115" s="6">
+        <v>46219</v>
+      </c>
       <c r="T115" s="6"/>
       <c r="U115" s="6">
         <v>46183</v>
@@ -12664,10 +12418,16 @@
         <v>46183</v>
       </c>
       <c r="W115" s="6"/>
-      <c r="X115" s="6"/>
-      <c r="Y115" s="6"/>
+      <c r="X115" s="6">
+        <v>46219</v>
+      </c>
+      <c r="Y115" s="6">
+        <v>46219</v>
+      </c>
       <c r="Z115" s="6"/>
-      <c r="AA115" s="6"/>
+      <c r="AA115" s="6">
+        <v>46219</v>
+      </c>
       <c r="AB115" s="8">
         <v>46210</v>
       </c>
@@ -12681,10 +12441,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
@@ -12723,10 +12483,10 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D117" s="1">
         <v>0</v>
@@ -12765,10 +12525,10 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D118" s="1">
         <v>0</v>
@@ -12807,10 +12567,10 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
@@ -12849,10 +12609,10 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
@@ -12891,10 +12651,10 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D121" s="1">
         <v>18</v>
@@ -12969,10 +12729,10 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D122" s="1">
         <v>0</v>
@@ -13011,10 +12771,10 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
@@ -13053,10 +12813,10 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D124" s="1">
         <v>0</v>
@@ -13095,10 +12855,10 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D125" s="1">
         <v>0</v>
@@ -13137,10 +12897,10 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D126" s="1">
         <v>19</v>
@@ -13217,10 +12977,10 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
@@ -13259,10 +13019,10 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
@@ -13301,10 +13061,10 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D129" s="1">
         <v>0</v>
@@ -13343,10 +13103,10 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
@@ -13385,10 +13145,10 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
@@ -13427,10 +13187,10 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D132" s="1">
         <v>21</v>
@@ -13511,10 +13271,10 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D133" s="1">
         <v>0</v>
@@ -13553,10 +13313,10 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D134" s="1">
         <v>0</v>
@@ -13595,10 +13355,10 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D135" s="1">
         <v>4</v>
@@ -13645,10 +13405,10 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D136" s="1">
         <v>0</v>
@@ -13687,10 +13447,10 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D137" s="1">
         <v>18</v>
@@ -13765,10 +13525,10 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
@@ -13807,13 +13567,13 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D139" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E139" s="8">
         <v>46156</v>
@@ -13843,11 +13603,21 @@
       <c r="N139" s="8">
         <v>46177</v>
       </c>
-      <c r="O139" s="6"/>
-      <c r="P139" s="6"/>
-      <c r="Q139" s="6"/>
-      <c r="R139" s="6"/>
-      <c r="S139" s="6"/>
+      <c r="O139" s="8">
+        <v>46223</v>
+      </c>
+      <c r="P139" s="8">
+        <v>46223</v>
+      </c>
+      <c r="Q139" s="8">
+        <v>46223</v>
+      </c>
+      <c r="R139" s="8">
+        <v>46223</v>
+      </c>
+      <c r="S139" s="8">
+        <v>46223</v>
+      </c>
       <c r="T139" s="6"/>
       <c r="U139" s="6">
         <v>46177</v>
@@ -13871,10 +13641,10 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D140" s="1">
         <v>0</v>
@@ -13913,10 +13683,10 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D141" s="1">
         <v>0</v>
@@ -13955,10 +13725,10 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D142" s="1">
         <v>0</v>
@@ -13997,7 +13767,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -14039,10 +13809,10 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D144" s="1">
         <v>21</v>
@@ -14123,10 +13893,10 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D145" s="1">
         <v>0</v>
@@ -14165,10 +13935,10 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D146" s="1">
         <v>0</v>
@@ -14207,10 +13977,10 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D147" s="1">
         <v>0</v>
@@ -14249,10 +14019,10 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D148" s="1">
         <v>0</v>
@@ -14291,13 +14061,13 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D149" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E149" s="8">
         <v>46176</v>
@@ -14341,7 +14111,9 @@
       <c r="R149" s="8">
         <v>46210</v>
       </c>
-      <c r="S149" s="6"/>
+      <c r="S149" s="6">
+        <v>46219</v>
+      </c>
       <c r="T149" s="6"/>
       <c r="U149" s="6">
         <v>46183</v>
@@ -14350,10 +14122,16 @@
         <v>46183</v>
       </c>
       <c r="W149" s="6"/>
-      <c r="X149" s="6"/>
-      <c r="Y149" s="6"/>
+      <c r="X149" s="6">
+        <v>46219</v>
+      </c>
+      <c r="Y149" s="6">
+        <v>46219</v>
+      </c>
       <c r="Z149" s="6"/>
-      <c r="AA149" s="6"/>
+      <c r="AA149" s="6">
+        <v>46219</v>
+      </c>
       <c r="AB149" s="8">
         <v>46210</v>
       </c>
@@ -14367,10 +14145,10 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
@@ -14409,10 +14187,10 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D151" s="1">
         <v>13</v>
@@ -14477,10 +14255,10 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D152" s="1">
         <v>0</v>
@@ -14519,10 +14297,10 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D153" s="1">
         <v>0</v>
@@ -14561,10 +14339,10 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D154" s="1">
         <v>0</v>
@@ -14603,13 +14381,13 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D155" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E155" s="8">
         <v>46154</v>
@@ -14635,7 +14413,9 @@
       <c r="P155" s="6"/>
       <c r="Q155" s="6"/>
       <c r="R155" s="6"/>
-      <c r="S155" s="6"/>
+      <c r="S155" s="6">
+        <v>46219</v>
+      </c>
       <c r="T155" s="6"/>
       <c r="U155" s="6">
         <v>46183</v>
@@ -14644,10 +14424,16 @@
         <v>46183</v>
       </c>
       <c r="W155" s="6"/>
-      <c r="X155" s="6"/>
-      <c r="Y155" s="6"/>
+      <c r="X155" s="6">
+        <v>46219</v>
+      </c>
+      <c r="Y155" s="6">
+        <v>46219</v>
+      </c>
       <c r="Z155" s="6"/>
-      <c r="AA155" s="6"/>
+      <c r="AA155" s="6">
+        <v>46219</v>
+      </c>
       <c r="AB155" s="6"/>
       <c r="AC155" s="6"/>
       <c r="AD155" s="6"/>
@@ -14659,10 +14445,10 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D156" s="1">
         <v>0</v>
@@ -14701,10 +14487,10 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D157" s="1">
         <v>0</v>
@@ -14743,10 +14529,10 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D158" s="1">
         <v>0</v>
@@ -14785,13 +14571,13 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D159" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E159" s="8">
         <v>46176</v>
@@ -14835,7 +14621,9 @@
       <c r="R159" s="10">
         <v>46198</v>
       </c>
-      <c r="S159" s="6"/>
+      <c r="S159" s="6">
+        <v>46219</v>
+      </c>
       <c r="T159" s="6"/>
       <c r="U159" s="6">
         <v>46183</v>
@@ -14844,10 +14632,16 @@
         <v>46183</v>
       </c>
       <c r="W159" s="6"/>
-      <c r="X159" s="6"/>
-      <c r="Y159" s="6"/>
+      <c r="X159" s="6">
+        <v>46219</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>46219</v>
+      </c>
       <c r="Z159" s="6"/>
-      <c r="AA159" s="6"/>
+      <c r="AA159" s="6">
+        <v>46219</v>
+      </c>
       <c r="AB159" s="6"/>
       <c r="AC159" s="6"/>
       <c r="AD159" s="6"/>
@@ -14859,10 +14653,10 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D160" s="1">
         <v>0</v>
@@ -14901,10 +14695,10 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D161" s="1">
         <v>19</v>
@@ -14981,10 +14775,10 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D162" s="1">
         <v>0</v>
@@ -15023,10 +14817,10 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D163" s="1">
         <v>0</v>
@@ -15065,10 +14859,10 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D164" s="1">
         <v>0</v>
@@ -15107,10 +14901,10 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D165" s="1">
         <v>0</v>
@@ -15149,10 +14943,10 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D166" s="1">
         <v>0</v>
@@ -15191,10 +14985,10 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D167" s="1">
         <v>0</v>
@@ -15233,10 +15027,10 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D168" s="1">
         <v>0</v>
@@ -15275,10 +15069,10 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D169" s="1">
         <v>0</v>
@@ -15317,10 +15111,10 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D170" s="1">
         <v>0</v>
@@ -15359,10 +15153,10 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D171" s="1">
         <v>0</v>
@@ -15401,10 +15195,10 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D172" s="1">
         <v>0</v>
@@ -15443,10 +15237,10 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D173" s="1">
         <v>0</v>
@@ -15485,10 +15279,10 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D174" s="1">
         <v>0</v>
@@ -15527,10 +15321,10 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D175" s="1">
         <v>0</v>
@@ -15569,10 +15363,10 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D176" s="1">
         <v>0</v>
@@ -15611,10 +15405,10 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D177" s="1">
         <v>18</v>
@@ -15689,10 +15483,10 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D178" s="1">
         <v>0</v>
@@ -15731,10 +15525,10 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D179" s="1">
         <v>14</v>
@@ -15801,10 +15595,10 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D180" s="1">
         <v>18</v>
@@ -15879,13 +15673,13 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D181" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
@@ -15903,11 +15697,21 @@
       <c r="N181" s="8">
         <v>46177</v>
       </c>
-      <c r="O181" s="6"/>
-      <c r="P181" s="6"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="6"/>
-      <c r="S181" s="6"/>
+      <c r="O181" s="8">
+        <v>46223</v>
+      </c>
+      <c r="P181" s="8">
+        <v>46223</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>46223</v>
+      </c>
+      <c r="R181" s="8">
+        <v>46223</v>
+      </c>
+      <c r="S181" s="8">
+        <v>46223</v>
+      </c>
       <c r="T181" s="6"/>
       <c r="U181" s="6">
         <v>46177</v>
@@ -15931,10 +15735,10 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D182" s="1">
         <v>0</v>
@@ -15973,10 +15777,10 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D183" s="1">
         <v>0</v>
@@ -16015,10 +15819,10 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D184" s="1">
         <v>0</v>
@@ -16057,10 +15861,10 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D185" s="1">
         <v>0</v>
@@ -16099,10 +15903,10 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D186" s="1">
         <v>0</v>
@@ -16141,10 +15945,10 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D187" s="1">
         <v>0</v>
@@ -16183,10 +15987,10 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D188" s="1">
         <v>19</v>
@@ -16263,10 +16067,10 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D189" s="1">
         <v>0</v>
@@ -16305,10 +16109,10 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="D190" s="1">
         <v>0</v>
@@ -16347,10 +16151,10 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D191" s="1">
         <v>21</v>
@@ -16431,13 +16235,13 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D192" s="1">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E192" s="6">
         <v>46149</v>
@@ -16463,11 +16267,21 @@
       <c r="N192" s="8">
         <v>46177</v>
       </c>
-      <c r="O192" s="6"/>
-      <c r="P192" s="6"/>
-      <c r="Q192" s="6"/>
-      <c r="R192" s="6"/>
-      <c r="S192" s="6"/>
+      <c r="O192" s="8">
+        <v>46223</v>
+      </c>
+      <c r="P192" s="8">
+        <v>46223</v>
+      </c>
+      <c r="Q192" s="8">
+        <v>46223</v>
+      </c>
+      <c r="R192" s="8">
+        <v>46223</v>
+      </c>
+      <c r="S192" s="8">
+        <v>46223</v>
+      </c>
       <c r="T192" s="6"/>
       <c r="U192" s="6">
         <v>46177</v>
@@ -16491,10 +16305,10 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D193" s="1">
         <v>13</v>
@@ -16559,10 +16373,10 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D194" s="1">
         <v>0</v>
@@ -16601,10 +16415,10 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D195" s="1">
         <v>0</v>
@@ -16643,10 +16457,10 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D196" s="1">
         <v>0</v>
@@ -16685,10 +16499,10 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D197" s="1">
         <v>0</v>
@@ -16727,10 +16541,10 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D198" s="1">
         <v>0</v>
@@ -16769,10 +16583,10 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D199" s="1">
         <v>20</v>
@@ -16851,10 +16665,10 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D200" s="1">
         <v>21</v>
@@ -16935,10 +16749,10 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D201" s="1">
         <v>0</v>
@@ -16977,10 +16791,10 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D202" s="1">
         <v>0</v>
@@ -17019,10 +16833,10 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D203" s="1">
         <v>21</v>
@@ -17103,10 +16917,10 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D204" s="1">
         <v>18</v>
@@ -17181,10 +16995,10 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D205" s="1">
         <v>0</v>
@@ -17223,10 +17037,10 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D206" s="1">
         <v>0</v>
@@ -17265,10 +17079,10 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D207" s="1">
         <v>8</v>
@@ -17323,10 +17137,10 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D208" s="1">
         <v>14</v>
@@ -17393,10 +17207,10 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D209" s="1">
         <v>21</v>
@@ -17477,10 +17291,10 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D210" s="1">
         <v>0</v>
@@ -17519,10 +17333,10 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D211" s="1">
         <v>0</v>
@@ -17561,10 +17375,10 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D212" s="1">
         <v>0</v>
@@ -17603,10 +17417,10 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D213" s="1">
         <v>0</v>
@@ -17645,10 +17459,10 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D214" s="1">
         <v>18</v>
@@ -17723,10 +17537,10 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D215" s="1">
         <v>0</v>
@@ -17765,13 +17579,13 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D216" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E216" s="8">
         <v>46176</v>
@@ -17815,7 +17629,9 @@
       <c r="R216" s="8">
         <v>46210</v>
       </c>
-      <c r="S216" s="6"/>
+      <c r="S216" s="6">
+        <v>46219</v>
+      </c>
       <c r="T216" s="6"/>
       <c r="U216" s="8">
         <v>46183</v>
@@ -17824,10 +17640,16 @@
         <v>46183</v>
       </c>
       <c r="W216" s="6"/>
-      <c r="X216" s="6"/>
-      <c r="Y216" s="6"/>
+      <c r="X216" s="6">
+        <v>46219</v>
+      </c>
+      <c r="Y216" s="6">
+        <v>46219</v>
+      </c>
       <c r="Z216" s="6"/>
-      <c r="AA216" s="6"/>
+      <c r="AA216" s="6">
+        <v>46219</v>
+      </c>
       <c r="AB216" s="8">
         <v>46210</v>
       </c>
@@ -17841,13 +17663,13 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D217" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E217" s="8">
         <v>46156</v>
@@ -17877,11 +17699,21 @@
       <c r="N217" s="8">
         <v>46177</v>
       </c>
-      <c r="O217" s="6"/>
-      <c r="P217" s="6"/>
-      <c r="Q217" s="6"/>
-      <c r="R217" s="6"/>
-      <c r="S217" s="6"/>
+      <c r="O217" s="8">
+        <v>46223</v>
+      </c>
+      <c r="P217" s="8">
+        <v>46223</v>
+      </c>
+      <c r="Q217" s="8">
+        <v>46223</v>
+      </c>
+      <c r="R217" s="8">
+        <v>46223</v>
+      </c>
+      <c r="S217" s="8">
+        <v>46223</v>
+      </c>
       <c r="T217" s="6"/>
       <c r="U217" s="8">
         <v>46177</v>
@@ -17900,510 +17732,6 @@
       <c r="AE217" s="6"/>
       <c r="AF217" s="6"/>
     </row>
-    <row r="218" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A218" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B218" s="1">
-        <v>0</v>
-      </c>
-      <c r="C218" s="1">
-        <v>0</v>
-      </c>
-      <c r="D218" s="1">
-        <v>0</v>
-      </c>
-      <c r="E218" s="6"/>
-      <c r="F218" s="6"/>
-      <c r="G218" s="6"/>
-      <c r="H218" s="6"/>
-      <c r="I218" s="6"/>
-      <c r="J218" s="6"/>
-      <c r="K218" s="6"/>
-      <c r="L218" s="6"/>
-      <c r="M218" s="6"/>
-      <c r="N218" s="6"/>
-      <c r="O218" s="6"/>
-      <c r="P218" s="6"/>
-      <c r="Q218" s="6"/>
-      <c r="R218" s="6"/>
-      <c r="S218" s="6"/>
-      <c r="T218" s="6"/>
-      <c r="U218" s="6"/>
-      <c r="V218" s="6"/>
-      <c r="W218" s="6"/>
-      <c r="X218" s="6"/>
-      <c r="Y218" s="6"/>
-      <c r="Z218" s="6"/>
-      <c r="AA218" s="6"/>
-      <c r="AB218" s="6"/>
-      <c r="AC218" s="6"/>
-      <c r="AD218" s="6"/>
-      <c r="AE218" s="6"/>
-      <c r="AF218" s="6"/>
-    </row>
-    <row r="219" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A219" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B219" s="1">
-        <v>0</v>
-      </c>
-      <c r="C219" s="1">
-        <v>0</v>
-      </c>
-      <c r="D219" s="1">
-        <v>0</v>
-      </c>
-      <c r="E219" s="6"/>
-      <c r="F219" s="6"/>
-      <c r="G219" s="6"/>
-      <c r="H219" s="6"/>
-      <c r="I219" s="6"/>
-      <c r="J219" s="6"/>
-      <c r="K219" s="6"/>
-      <c r="L219" s="6"/>
-      <c r="M219" s="6"/>
-      <c r="N219" s="6"/>
-      <c r="O219" s="6"/>
-      <c r="P219" s="6"/>
-      <c r="Q219" s="6"/>
-      <c r="R219" s="6"/>
-      <c r="S219" s="6"/>
-      <c r="T219" s="6"/>
-      <c r="U219" s="6"/>
-      <c r="V219" s="6"/>
-      <c r="W219" s="6"/>
-      <c r="X219" s="6"/>
-      <c r="Y219" s="6"/>
-      <c r="Z219" s="6"/>
-      <c r="AA219" s="6"/>
-      <c r="AB219" s="6"/>
-      <c r="AC219" s="6"/>
-      <c r="AD219" s="6"/>
-      <c r="AE219" s="6"/>
-      <c r="AF219" s="6"/>
-    </row>
-    <row r="220" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A220" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B220" s="1">
-        <v>0</v>
-      </c>
-      <c r="C220" s="1">
-        <v>0</v>
-      </c>
-      <c r="D220" s="1">
-        <v>0</v>
-      </c>
-      <c r="E220" s="6"/>
-      <c r="F220" s="6"/>
-      <c r="G220" s="6"/>
-      <c r="H220" s="6"/>
-      <c r="I220" s="6"/>
-      <c r="J220" s="6"/>
-      <c r="K220" s="6"/>
-      <c r="L220" s="6"/>
-      <c r="M220" s="6"/>
-      <c r="N220" s="6"/>
-      <c r="O220" s="6"/>
-      <c r="P220" s="6"/>
-      <c r="Q220" s="6"/>
-      <c r="R220" s="6"/>
-      <c r="S220" s="6"/>
-      <c r="T220" s="6"/>
-      <c r="U220" s="6"/>
-      <c r="V220" s="6"/>
-      <c r="W220" s="6"/>
-      <c r="X220" s="6"/>
-      <c r="Y220" s="6"/>
-      <c r="Z220" s="6"/>
-      <c r="AA220" s="6"/>
-      <c r="AB220" s="6"/>
-      <c r="AC220" s="6"/>
-      <c r="AD220" s="6"/>
-      <c r="AE220" s="6"/>
-      <c r="AF220" s="6"/>
-    </row>
-    <row r="221" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A221" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B221" s="1">
-        <v>0</v>
-      </c>
-      <c r="C221" s="1">
-        <v>0</v>
-      </c>
-      <c r="D221" s="1">
-        <v>0</v>
-      </c>
-      <c r="E221" s="6"/>
-      <c r="F221" s="6"/>
-      <c r="G221" s="6"/>
-      <c r="H221" s="6"/>
-      <c r="I221" s="6"/>
-      <c r="J221" s="6"/>
-      <c r="K221" s="6"/>
-      <c r="L221" s="6"/>
-      <c r="M221" s="6"/>
-      <c r="N221" s="6"/>
-      <c r="O221" s="6"/>
-      <c r="P221" s="6"/>
-      <c r="Q221" s="6"/>
-      <c r="R221" s="6"/>
-      <c r="S221" s="6"/>
-      <c r="T221" s="6"/>
-      <c r="U221" s="6"/>
-      <c r="V221" s="6"/>
-      <c r="W221" s="6"/>
-      <c r="X221" s="6"/>
-      <c r="Y221" s="6"/>
-      <c r="Z221" s="6"/>
-      <c r="AA221" s="6"/>
-      <c r="AB221" s="6"/>
-      <c r="AC221" s="6"/>
-      <c r="AD221" s="6"/>
-      <c r="AE221" s="6"/>
-      <c r="AF221" s="6"/>
-    </row>
-    <row r="222" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A222" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B222" s="1">
-        <v>0</v>
-      </c>
-      <c r="C222" s="1">
-        <v>0</v>
-      </c>
-      <c r="D222" s="1">
-        <v>0</v>
-      </c>
-      <c r="E222" s="6"/>
-      <c r="F222" s="6"/>
-      <c r="G222" s="6"/>
-      <c r="H222" s="6"/>
-      <c r="I222" s="6"/>
-      <c r="J222" s="6"/>
-      <c r="K222" s="6"/>
-      <c r="L222" s="6"/>
-      <c r="M222" s="6"/>
-      <c r="N222" s="6"/>
-      <c r="O222" s="6"/>
-      <c r="P222" s="6"/>
-      <c r="Q222" s="6"/>
-      <c r="R222" s="6"/>
-      <c r="S222" s="6"/>
-      <c r="T222" s="6"/>
-      <c r="U222" s="6"/>
-      <c r="V222" s="6"/>
-      <c r="W222" s="6"/>
-      <c r="X222" s="6"/>
-      <c r="Y222" s="6"/>
-      <c r="Z222" s="6"/>
-      <c r="AA222" s="6"/>
-      <c r="AB222" s="6"/>
-      <c r="AC222" s="6"/>
-      <c r="AD222" s="6"/>
-      <c r="AE222" s="6"/>
-      <c r="AF222" s="6"/>
-    </row>
-    <row r="223" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A223" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B223" s="1">
-        <v>0</v>
-      </c>
-      <c r="C223" s="1">
-        <v>0</v>
-      </c>
-      <c r="D223" s="1">
-        <v>0</v>
-      </c>
-      <c r="E223" s="6"/>
-      <c r="F223" s="6"/>
-      <c r="G223" s="6"/>
-      <c r="H223" s="6"/>
-      <c r="I223" s="6"/>
-      <c r="J223" s="6"/>
-      <c r="K223" s="6"/>
-      <c r="L223" s="6"/>
-      <c r="M223" s="6"/>
-      <c r="N223" s="6"/>
-      <c r="O223" s="6"/>
-      <c r="P223" s="6"/>
-      <c r="Q223" s="6"/>
-      <c r="R223" s="6"/>
-      <c r="S223" s="6"/>
-      <c r="T223" s="6"/>
-      <c r="U223" s="6"/>
-      <c r="V223" s="6"/>
-      <c r="W223" s="6"/>
-      <c r="X223" s="6"/>
-      <c r="Y223" s="6"/>
-      <c r="Z223" s="6"/>
-      <c r="AA223" s="6"/>
-      <c r="AB223" s="6"/>
-      <c r="AC223" s="6"/>
-      <c r="AD223" s="6"/>
-      <c r="AE223" s="6"/>
-      <c r="AF223" s="6"/>
-    </row>
-    <row r="224" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A224" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B224" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C224" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D224" s="1">
-        <v>0</v>
-      </c>
-      <c r="E224" s="6"/>
-      <c r="F224" s="6"/>
-      <c r="G224" s="6"/>
-      <c r="H224" s="6"/>
-      <c r="I224" s="6"/>
-      <c r="J224" s="6"/>
-      <c r="K224" s="6"/>
-      <c r="L224" s="6"/>
-      <c r="M224" s="6"/>
-      <c r="N224" s="6"/>
-      <c r="O224" s="6"/>
-      <c r="P224" s="6"/>
-      <c r="Q224" s="6"/>
-      <c r="R224" s="6"/>
-      <c r="S224" s="6"/>
-      <c r="T224" s="6"/>
-      <c r="U224" s="6"/>
-      <c r="V224" s="6"/>
-      <c r="W224" s="6"/>
-      <c r="X224" s="6"/>
-      <c r="Y224" s="6"/>
-      <c r="Z224" s="6"/>
-      <c r="AA224" s="6"/>
-      <c r="AB224" s="6"/>
-      <c r="AC224" s="6"/>
-      <c r="AD224" s="6"/>
-      <c r="AE224" s="6"/>
-      <c r="AF224" s="6"/>
-    </row>
-    <row r="225" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A225" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B225" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C225" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D225" s="1">
-        <v>0</v>
-      </c>
-      <c r="E225" s="6"/>
-      <c r="F225" s="6"/>
-      <c r="G225" s="6"/>
-      <c r="H225" s="6"/>
-      <c r="I225" s="6"/>
-      <c r="J225" s="6"/>
-      <c r="K225" s="6"/>
-      <c r="L225" s="6"/>
-      <c r="M225" s="6"/>
-      <c r="N225" s="6"/>
-      <c r="O225" s="6"/>
-      <c r="P225" s="6"/>
-      <c r="Q225" s="6"/>
-      <c r="R225" s="6"/>
-      <c r="S225" s="6"/>
-      <c r="T225" s="6"/>
-      <c r="U225" s="6"/>
-      <c r="V225" s="6"/>
-      <c r="W225" s="6"/>
-      <c r="X225" s="6"/>
-      <c r="Y225" s="6"/>
-      <c r="Z225" s="6"/>
-      <c r="AA225" s="6"/>
-      <c r="AB225" s="6"/>
-      <c r="AC225" s="6"/>
-      <c r="AD225" s="6"/>
-      <c r="AE225" s="6"/>
-      <c r="AF225" s="6"/>
-    </row>
-    <row r="226" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A226" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B226" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C226" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D226" s="1">
-        <v>0</v>
-      </c>
-      <c r="E226" s="6"/>
-      <c r="F226" s="6"/>
-      <c r="G226" s="6"/>
-      <c r="H226" s="6"/>
-      <c r="I226" s="6"/>
-      <c r="J226" s="6"/>
-      <c r="K226" s="6"/>
-      <c r="L226" s="6"/>
-      <c r="M226" s="6"/>
-      <c r="N226" s="6"/>
-      <c r="O226" s="6"/>
-      <c r="P226" s="6"/>
-      <c r="Q226" s="6"/>
-      <c r="R226" s="6"/>
-      <c r="S226" s="6"/>
-      <c r="T226" s="6"/>
-      <c r="U226" s="6"/>
-      <c r="V226" s="6"/>
-      <c r="W226" s="6"/>
-      <c r="X226" s="6"/>
-      <c r="Y226" s="6"/>
-      <c r="Z226" s="6"/>
-      <c r="AA226" s="6"/>
-      <c r="AB226" s="6"/>
-      <c r="AC226" s="6"/>
-      <c r="AD226" s="6"/>
-      <c r="AE226" s="6"/>
-      <c r="AF226" s="6"/>
-    </row>
-    <row r="227" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A227" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B227" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C227" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D227" s="1">
-        <v>0</v>
-      </c>
-      <c r="E227" s="6"/>
-      <c r="F227" s="6"/>
-      <c r="G227" s="6"/>
-      <c r="H227" s="6"/>
-      <c r="I227" s="6"/>
-      <c r="J227" s="6"/>
-      <c r="K227" s="6"/>
-      <c r="L227" s="6"/>
-      <c r="M227" s="6"/>
-      <c r="N227" s="6"/>
-      <c r="O227" s="6"/>
-      <c r="P227" s="6"/>
-      <c r="Q227" s="6"/>
-      <c r="R227" s="6"/>
-      <c r="S227" s="6"/>
-      <c r="T227" s="6"/>
-      <c r="U227" s="6"/>
-      <c r="V227" s="6"/>
-      <c r="W227" s="6"/>
-      <c r="X227" s="6"/>
-      <c r="Y227" s="6"/>
-      <c r="Z227" s="6"/>
-      <c r="AA227" s="6"/>
-      <c r="AB227" s="6"/>
-      <c r="AC227" s="6"/>
-      <c r="AD227" s="6"/>
-      <c r="AE227" s="6"/>
-      <c r="AF227" s="6"/>
-    </row>
-    <row r="228" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A228" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B228" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C228" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D228" s="1">
-        <v>0</v>
-      </c>
-      <c r="E228" s="6"/>
-      <c r="F228" s="6"/>
-      <c r="G228" s="6"/>
-      <c r="H228" s="6"/>
-      <c r="I228" s="6"/>
-      <c r="J228" s="6"/>
-      <c r="K228" s="6"/>
-      <c r="L228" s="6"/>
-      <c r="M228" s="6"/>
-      <c r="N228" s="6"/>
-      <c r="O228" s="6"/>
-      <c r="P228" s="6"/>
-      <c r="Q228" s="6"/>
-      <c r="R228" s="6"/>
-      <c r="S228" s="6"/>
-      <c r="T228" s="6"/>
-      <c r="U228" s="6"/>
-      <c r="V228" s="6"/>
-      <c r="W228" s="6"/>
-      <c r="X228" s="6"/>
-      <c r="Y228" s="6"/>
-      <c r="Z228" s="6"/>
-      <c r="AA228" s="6"/>
-      <c r="AB228" s="6"/>
-      <c r="AC228" s="6"/>
-      <c r="AD228" s="6"/>
-      <c r="AE228" s="6"/>
-      <c r="AF228" s="6"/>
-    </row>
-    <row r="229" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A229" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B229" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C229" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D229" s="1">
-        <v>0</v>
-      </c>
-      <c r="E229" s="6"/>
-      <c r="F229" s="6"/>
-      <c r="G229" s="6"/>
-      <c r="H229" s="6"/>
-      <c r="I229" s="6"/>
-      <c r="J229" s="6"/>
-      <c r="K229" s="6"/>
-      <c r="L229" s="6"/>
-      <c r="M229" s="6"/>
-      <c r="N229" s="6"/>
-      <c r="O229" s="6"/>
-      <c r="P229" s="6"/>
-      <c r="Q229" s="6"/>
-      <c r="R229" s="6"/>
-      <c r="S229" s="6"/>
-      <c r="T229" s="6"/>
-      <c r="U229" s="6"/>
-      <c r="V229" s="6"/>
-      <c r="W229" s="6"/>
-      <c r="X229" s="6"/>
-      <c r="Y229" s="6"/>
-      <c r="Z229" s="6"/>
-      <c r="AA229" s="6"/>
-      <c r="AB229" s="6"/>
-      <c r="AC229" s="6"/>
-      <c r="AD229" s="6"/>
-      <c r="AE229" s="6"/>
-      <c r="AF229" s="6"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Matar Trainings.xlsx
+++ b/Matar Trainings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.karuru\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE84F89-B5E6-4C84-B1E5-91CAF3F161A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3D27E1-0404-4E48-A55D-819364E01357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2ACD8935-9A55-49F4-8AD3-9F8021E2249D}"/>
+    <workbookView xWindow="28692" yWindow="408" windowWidth="25416" windowHeight="15252" activeTab="1" xr2:uid="{2ACD8935-9A55-49F4-8AD3-9F8021E2249D}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta Data" sheetId="1" r:id="rId1"/>
@@ -880,664 +880,664 @@
     <t>Norbert Mueller</t>
   </si>
   <si>
+    <t>Mohamed Farkan Mohamed Sareek</t>
+  </si>
+  <si>
+    <t>Destiny Emmanuel</t>
+  </si>
+  <si>
+    <t>Abdunaser Ahmed Aragaw</t>
+  </si>
+  <si>
+    <t>Rizardo Villalobos</t>
+  </si>
+  <si>
+    <t>Chidanand Bhaskara Chaithanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahesh Ramachandra </t>
+  </si>
+  <si>
+    <t>Joel Cabrillos Misa</t>
+  </si>
+  <si>
+    <t>Ericson Murcillos Victorino</t>
+  </si>
+  <si>
+    <t>Fernan Dela Cruz</t>
+  </si>
+  <si>
+    <t>Bindu Pillai</t>
+  </si>
+  <si>
+    <t>Philippe Musangilay Kubula</t>
+  </si>
+  <si>
+    <t>Sandy De Vera Apigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerry Arnejo Carandang </t>
+  </si>
+  <si>
+    <t>Vicente Mendigorin Morelos</t>
+  </si>
+  <si>
+    <t>Sivagaran Ramanathan</t>
+  </si>
+  <si>
+    <t>Cletes Albert Perera</t>
+  </si>
+  <si>
+    <t>Tharanga Pradeep Pathirannehelage</t>
+  </si>
+  <si>
+    <t>Pubudu Maduranga Hearth Ralalage</t>
+  </si>
+  <si>
+    <t>Joevergil Cajocson Dormitorio</t>
+  </si>
+  <si>
+    <t>Ricky Catibog Katigbak</t>
+  </si>
+  <si>
+    <t>Venice Mendova Jadloc</t>
+  </si>
+  <si>
+    <t>Lemuel Celeste Anacleto</t>
+  </si>
+  <si>
+    <t>Arnel Butiu Guevarra</t>
+  </si>
+  <si>
+    <t>Edwin Balakid Tegli</t>
+  </si>
+  <si>
+    <t>Jessie Jr. Alcuizar Hellera</t>
+  </si>
+  <si>
+    <t>Noel Jarabe Riego</t>
+  </si>
+  <si>
+    <t>Edilberto Angsioco</t>
+  </si>
+  <si>
+    <t>Jose Dino Constantino</t>
+  </si>
+  <si>
+    <t>Regin Alis</t>
+  </si>
+  <si>
+    <t>Restito Fabic</t>
+  </si>
+  <si>
+    <t>Kamalanathan Poopalapillai</t>
+  </si>
+  <si>
+    <t>Anil Kumara</t>
+  </si>
+  <si>
+    <t>Lani Fernando Kachchakaduge</t>
+  </si>
+  <si>
+    <t>Sampath Chamin</t>
+  </si>
+  <si>
+    <t>Raymond Ian Montero</t>
+  </si>
+  <si>
+    <t>James Magnaye Catapia</t>
+  </si>
+  <si>
+    <t>Marty Tolosa Ambas</t>
+  </si>
+  <si>
+    <t>Nove Manuel Menorisa Tagpuno</t>
+  </si>
+  <si>
+    <t>Edgar Noceja</t>
+  </si>
+  <si>
+    <t>Ma. Edelfa Mendoza</t>
+  </si>
+  <si>
+    <t>Mark Jayson Rosima</t>
+  </si>
+  <si>
+    <t>Cristopher Cruz</t>
+  </si>
+  <si>
+    <t>Ramanan Thavarasa</t>
+  </si>
+  <si>
+    <t>Renato Dimalanta Canlas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruben Dela Cruz Malabo </t>
+  </si>
+  <si>
+    <t>Manuel Jr. Esplago Feniza</t>
+  </si>
+  <si>
+    <t>Billy Jim Morelos</t>
+  </si>
+  <si>
+    <t>Haren Del Campo</t>
+  </si>
+  <si>
+    <t>Mohamed Nabhan M. Shahiq</t>
+  </si>
+  <si>
+    <t>Rogelio Reyes Gomez Jr.</t>
+  </si>
+  <si>
+    <t>John Michael Yagonia</t>
+  </si>
+  <si>
+    <t>Ronnie Villanueva Gutierrez</t>
+  </si>
+  <si>
+    <t>Nenad Jovkovic</t>
+  </si>
+  <si>
+    <t>Nhuel Caguicla Landicho</t>
+  </si>
+  <si>
+    <t>Mohamed Riswan Mohamed Salyh</t>
+  </si>
+  <si>
+    <t>Dennis Ibe Sudario</t>
+  </si>
+  <si>
+    <t>Christian Archie Barbosa Niez</t>
+  </si>
+  <si>
+    <t>Clint Jude Duarte Bicoy</t>
+  </si>
+  <si>
+    <t>Willie Facun Adi</t>
+  </si>
+  <si>
+    <t>Eduard Embate Endonela</t>
+  </si>
+  <si>
+    <t>Sugathadasa Pattiwilage</t>
+  </si>
+  <si>
+    <t>Gomer Repaso Plenos</t>
+  </si>
+  <si>
+    <t>John Errol Para Marino</t>
+  </si>
+  <si>
+    <t>Gabuin James Buintim</t>
+  </si>
+  <si>
+    <t>Marlon Rodel Fracisco Pimentel</t>
+  </si>
+  <si>
+    <t>Nathaniel Laguidao Gamosa</t>
+  </si>
+  <si>
+    <t>Ernesto JR Leona Campana</t>
+  </si>
+  <si>
+    <t>William Villanueva Gutierrez</t>
+  </si>
+  <si>
+    <t>Conrado DE Guzman Vineza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elecer Hernandez Llamoso </t>
+  </si>
+  <si>
+    <t>Elesor JR Cas Frondozo</t>
+  </si>
+  <si>
+    <t>Carlo Alcoran Tenorio</t>
+  </si>
+  <si>
+    <t>Alvin Quizon Tabasa</t>
+  </si>
+  <si>
+    <t>Miguelito Costelo Mainit</t>
+  </si>
+  <si>
+    <t>Mohamed Nasardeen Mohamadu Main</t>
+  </si>
+  <si>
+    <t>Dominic Munyua Kanyotu</t>
+  </si>
+  <si>
+    <t>Lenson Kiarie Karuru</t>
+  </si>
+  <si>
+    <t>Ryan Mauring Adol</t>
+  </si>
+  <si>
+    <t>Joey JR Tiwo Meramonte</t>
+  </si>
+  <si>
+    <t>Mario Dorado Hernandez</t>
+  </si>
+  <si>
+    <t>Sooraj Kurisinkal Reji</t>
+  </si>
+  <si>
+    <t>Jose Isagani Jr. Jamero Alaan</t>
+  </si>
+  <si>
+    <t>Jishnu Surendran</t>
+  </si>
+  <si>
+    <t>Saritha Oromariyil Sukumaran</t>
+  </si>
+  <si>
+    <t>Renz Jake Orense Lontoc</t>
+  </si>
+  <si>
+    <t>Dennis Delfino Daginotan</t>
+  </si>
+  <si>
+    <t>John Eric Bonganay Borcelis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Maitem Maureal </t>
+  </si>
+  <si>
+    <t>Paul Jeric Azul Falcatan</t>
+  </si>
+  <si>
+    <t>Roderick Cailao Amar</t>
+  </si>
+  <si>
+    <t>Jimmy Mallari Dela Cruz</t>
+  </si>
+  <si>
+    <t>Meegle Mathew</t>
+  </si>
+  <si>
+    <t>Thuvarakan Pulenthiran</t>
+  </si>
+  <si>
+    <t>Jerome Latagan Cardejon</t>
+  </si>
+  <si>
+    <t>Jay Tucker Mendoza</t>
+  </si>
+  <si>
+    <t>Crisfo Lo Nibal</t>
+  </si>
+  <si>
+    <t>Simon Kenneth Inoceno Hernandez</t>
+  </si>
+  <si>
+    <t>Levitico Jose Caniedo</t>
+  </si>
+  <si>
+    <t>Mohamed Faizal Mohamed Uvais</t>
+  </si>
+  <si>
+    <t>Nhar Jaradal Cillo</t>
+  </si>
+  <si>
+    <t>Herwin Fatalla Mimay</t>
+  </si>
+  <si>
+    <t>Nino Vercide Arda</t>
+  </si>
+  <si>
+    <t>Jason Puzon Dy</t>
+  </si>
+  <si>
+    <t>Rholie Pacio Casison</t>
+  </si>
+  <si>
+    <t>Jeffrey Manarpaac Urolaza</t>
+  </si>
+  <si>
+    <t>Edison Mendoza Rojas</t>
+  </si>
+  <si>
+    <t>Mark Merill Jovenes Tirol</t>
+  </si>
+  <si>
+    <t>Kennedy Gichuhi Ngaruiya</t>
+  </si>
+  <si>
+    <t>Francis Agbor Eyong Atem</t>
+  </si>
+  <si>
+    <t>Siraj Moolakkappil</t>
+  </si>
+  <si>
+    <t>Mohamed Bilal Muneer Basha</t>
+  </si>
+  <si>
+    <t>Alen Cherippanat Babu</t>
+  </si>
+  <si>
+    <t>Mohamed Shafras Jawlangull</t>
+  </si>
+  <si>
+    <t>Renson Gicheha Gicheru</t>
+  </si>
+  <si>
+    <t>Mohamed Faris Mohamed Naleem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shihabdeen Seeni Mohamed </t>
+  </si>
+  <si>
+    <t>Prakyath Prabhakar Amin</t>
+  </si>
+  <si>
+    <t>Julius Kateregga</t>
+  </si>
+  <si>
+    <t>Kishanraj Pulenthiran</t>
+  </si>
+  <si>
+    <t>James Kariungi Muthee</t>
+  </si>
+  <si>
+    <t>Kasansula Francis Kiwanuka</t>
+  </si>
+  <si>
+    <t>Arnel Neri Montemayor</t>
+  </si>
+  <si>
+    <t>Erick Omondi Okoyo</t>
+  </si>
+  <si>
+    <t>Trevin Christopher Neydorf</t>
+  </si>
+  <si>
+    <t>Mohamed Mufaris Mohamed Jameel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasim Kinarullaparambath Kunhabdulla </t>
+  </si>
+  <si>
+    <t>Naser Qasim Mohammad Alhaj Ahmed</t>
+  </si>
+  <si>
+    <t>Jeffrey Sayson Bagatua</t>
+  </si>
+  <si>
+    <t>Wali Mohammed Sabry</t>
+  </si>
+  <si>
+    <t>Rommel Tamayo Eleosida</t>
+  </si>
+  <si>
+    <t>Errolnil Purificacion Atienza</t>
+  </si>
+  <si>
+    <t>Hernan John Baguion Murcillos</t>
+  </si>
+  <si>
+    <t>Ivan Raphael Macatangay Del Mundo</t>
+  </si>
+  <si>
+    <t>Jerico Tallorin Atienzo</t>
+  </si>
+  <si>
+    <t>Alvin Tumboc Cuevas</t>
+  </si>
+  <si>
+    <t>James Andrew Aquino Rodillo</t>
+  </si>
+  <si>
+    <t>Alvin Cataquiz Austria</t>
+  </si>
+  <si>
+    <t>Jayson Ruz Oligan</t>
+  </si>
+  <si>
+    <t>John Michael Angelo Mesina Clemen</t>
+  </si>
+  <si>
+    <t>Lemuel Carcellar Macatangay</t>
+  </si>
+  <si>
+    <t>Nikko Villanueva Cruz</t>
+  </si>
+  <si>
+    <t>Justin Paolo Macatangay Ilao</t>
+  </si>
+  <si>
+    <t>Jake Alinabon Salibay</t>
+  </si>
+  <si>
+    <t>Marlon Yuson Pamplona</t>
+  </si>
+  <si>
+    <t>Joe Vergil Jr Calanza Dormitorio</t>
+  </si>
+  <si>
+    <t>Bonifacio Arano Bayer</t>
+  </si>
+  <si>
+    <t>Sumedha Pradeep Dissanayaka</t>
+  </si>
+  <si>
+    <t>Yuvashanth Somasuntharam kukasuthan</t>
+  </si>
+  <si>
+    <t>Jonel Catibog Katigbak</t>
+  </si>
+  <si>
+    <t>Catalino Mendoza Rojas</t>
+  </si>
+  <si>
+    <t>Murshidul Haq Patteri Thazhe Kuni</t>
+  </si>
+  <si>
+    <t>Nisham Kizhakke Valappil</t>
+  </si>
+  <si>
+    <t>Pasidu Pamodaya Rathnayake Rathnayake Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Chalana Ishan Dishanayake Dishanayake Pathiranage</t>
+  </si>
+  <si>
+    <t>Mohamed Ahthir Abdul Majeed</t>
+  </si>
+  <si>
+    <t>Niroshan Abesingha Abesingha Karunarathna Mudalige</t>
+  </si>
+  <si>
+    <t>Sathis Gunawardhana Dikella Kandha Yakdhehirallage</t>
+  </si>
+  <si>
+    <t>Tharaka Thanujaya Dissanayaka Dissanayaka Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Nishan Ekanayake Ekanayake Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Jacky Chan Nava Gastardo</t>
+  </si>
+  <si>
+    <t>Mohammed Fahim Mohammed Laffir</t>
+  </si>
+  <si>
+    <t>Sameera Lakmal Rupasinghe Arachchige</t>
+  </si>
+  <si>
+    <t>Dushan Priyankara Herath Herath Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Pathmapriyan Muruguppilla</t>
+  </si>
+  <si>
+    <t>Roshan Chaminda Udawaththa Udawaththa Kankanamge</t>
+  </si>
+  <si>
+    <t>Kusal Sharmila Hewa Kokawalage</t>
+  </si>
+  <si>
+    <t>Mohomed Minnas Mohomed Ramees</t>
+  </si>
+  <si>
+    <t>Mabin Pauly</t>
+  </si>
+  <si>
+    <t>Jahsim Saycon Apila</t>
+  </si>
+  <si>
+    <t>Shern Sebastian Sebastian Simon</t>
+  </si>
+  <si>
+    <t>Wai Hin Phyo</t>
+  </si>
+  <si>
+    <t>Hicham Charkaoui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mohamed Shaheer Mohamed Laffir </t>
+  </si>
+  <si>
+    <t>Antony Kamau Kageche</t>
+  </si>
+  <si>
+    <t>Abdulrashid Byarugaba </t>
+  </si>
+  <si>
+    <t>Justine Tiangson Clave</t>
+  </si>
+  <si>
+    <t>Harikaran Seenithamby</t>
+  </si>
+  <si>
+    <t>Wycliffe Mushori</t>
+  </si>
+  <si>
+    <t>Peter Nganga Kamau</t>
+  </si>
+  <si>
+    <t>Sumesh Soman</t>
+  </si>
+  <si>
+    <t>Muhammed Ashiq Mohamed Mumtaz</t>
+  </si>
+  <si>
+    <t>Arvin Clyde D.Crisme</t>
+  </si>
+  <si>
+    <t>Gary John Packer</t>
+  </si>
+  <si>
+    <t>Ifras Mohammed</t>
+  </si>
+  <si>
+    <t>Alby Manchandiyil Antony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ifran Ansari </t>
+  </si>
+  <si>
+    <t>Piratheepan Thiyagarasa</t>
+  </si>
+  <si>
+    <t>Moustafa Hassan Ibrahim Elsayyad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harsha Shetty </t>
+  </si>
+  <si>
+    <t>Kevin Carl Enriquez Serrano</t>
+  </si>
+  <si>
+    <t>Romie Ross Tamayo Eleosida</t>
+  </si>
+  <si>
+    <t>Quennan Carandang Cuesta</t>
+  </si>
+  <si>
+    <t>Lester John Fuentes Monter</t>
+  </si>
+  <si>
+    <t>Neil Jhon Sabile Ramos</t>
+  </si>
+  <si>
+    <t>Kim Harvey Cuevas Ayag</t>
+  </si>
+  <si>
+    <t>Nelson Jr Ybut Sancho</t>
+  </si>
+  <si>
+    <t>Rolly Miano Valdez</t>
+  </si>
+  <si>
+    <t>Daniel Bacolcol Orquiza</t>
+  </si>
+  <si>
+    <t>Roby Chua Malinao</t>
+  </si>
+  <si>
+    <t>Lorence Cardenas Cabales</t>
+  </si>
+  <si>
+    <t>Emmanuel Richard Marasigan Velasco</t>
+  </si>
+  <si>
+    <t>Michael Jorge Toscano Masaoy</t>
+  </si>
+  <si>
+    <t>Jeffrey De Vera Cabico</t>
+  </si>
+  <si>
+    <t>Joe Peter Angustia Pimentel</t>
+  </si>
+  <si>
+    <t>Mark Roentgen Macatangay Delen</t>
+  </si>
+  <si>
+    <t>Arjay Imperial Gabarda</t>
+  </si>
+  <si>
+    <t>Noey Francisco Canonizado</t>
+  </si>
+  <si>
+    <t>Omar Zaki Saad Abdel Nabi</t>
+  </si>
+  <si>
+    <t>Abdul Rehman Mohammed Abdul Mohammed</t>
+  </si>
+  <si>
+    <t>Christian Merck Morada Martija</t>
+  </si>
+  <si>
+    <t>Imesha Rashmi Mudannayaka Mudannayakage</t>
+  </si>
+  <si>
+    <t>Sajith Dulanjana Kumara Rathnayaka Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Thisura Kaumal Wijesinghe</t>
+  </si>
+  <si>
+    <t>Shanel Rukshan Perera Kurana Patabendige</t>
+  </si>
+  <si>
+    <t>Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon</t>
+  </si>
+  <si>
     <t>Management</t>
   </si>
   <si>
-    <t>Mohamed Farkan Mohamed Sareek</t>
-  </si>
-  <si>
-    <t>Destiny Emmanuel</t>
-  </si>
-  <si>
-    <t>Abdunaser Ahmed Aragaw</t>
-  </si>
-  <si>
     <t>CARGO CM</t>
   </si>
   <si>
-    <t>Rizardo Villalobos</t>
-  </si>
-  <si>
-    <t>Chidanand Bhaskara Chaithanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahesh Ramachandra </t>
-  </si>
-  <si>
     <t>CARGO PM</t>
   </si>
   <si>
-    <t>Joel Cabrillos Misa</t>
-  </si>
-  <si>
-    <t>Ericson Murcillos Victorino</t>
-  </si>
-  <si>
-    <t>Fernan Dela Cruz</t>
-  </si>
-  <si>
-    <t>Bindu Pillai</t>
-  </si>
-  <si>
-    <t>Philippe Musangilay Kubula</t>
-  </si>
-  <si>
-    <t>Sandy De Vera Apigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerry Arnejo Carandang </t>
-  </si>
-  <si>
-    <t>Vicente Mendigorin Morelos</t>
-  </si>
-  <si>
-    <t>Sivagaran Ramanathan</t>
-  </si>
-  <si>
-    <t>Cletes Albert Perera</t>
-  </si>
-  <si>
-    <t>Tharanga Pradeep Pathirannehelage</t>
-  </si>
-  <si>
-    <t>Pubudu Maduranga Hearth Ralalage</t>
-  </si>
-  <si>
-    <t>Joevergil Cajocson Dormitorio</t>
-  </si>
-  <si>
-    <t>Ricky Catibog Katigbak</t>
-  </si>
-  <si>
-    <t>Venice Mendova Jadloc</t>
-  </si>
-  <si>
-    <t>Lemuel Celeste Anacleto</t>
-  </si>
-  <si>
-    <t>Arnel Butiu Guevarra</t>
-  </si>
-  <si>
-    <t>Edwin Balakid Tegli</t>
-  </si>
-  <si>
-    <t>Jessie Jr. Alcuizar Hellera</t>
-  </si>
-  <si>
-    <t>Noel Jarabe Riego</t>
-  </si>
-  <si>
-    <t>Edilberto Angsioco</t>
-  </si>
-  <si>
-    <t>Jose Dino Constantino</t>
-  </si>
-  <si>
-    <t>Regin Alis</t>
-  </si>
-  <si>
-    <t>Restito Fabic</t>
-  </si>
-  <si>
-    <t>Kamalanathan Poopalapillai</t>
-  </si>
-  <si>
-    <t>Anil Kumara</t>
-  </si>
-  <si>
-    <t>Lani Fernando Kachchakaduge</t>
-  </si>
-  <si>
-    <t>Sampath Chamin</t>
-  </si>
-  <si>
-    <t>Raymond Ian Montero</t>
-  </si>
-  <si>
-    <t>James Magnaye Catapia</t>
-  </si>
-  <si>
-    <t>Marty Tolosa Ambas</t>
-  </si>
-  <si>
-    <t>Nove Manuel Menorisa Tagpuno</t>
-  </si>
-  <si>
-    <t>Edgar Noceja</t>
-  </si>
-  <si>
-    <t>Ma. Edelfa Mendoza</t>
-  </si>
-  <si>
-    <t>Mark Jayson Rosima</t>
-  </si>
-  <si>
-    <t>Cristopher Cruz</t>
-  </si>
-  <si>
-    <t>Ramanan Thavarasa</t>
-  </si>
-  <si>
-    <t>Renato Dimalanta Canlas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ruben Dela Cruz Malabo </t>
-  </si>
-  <si>
-    <t>Manuel Jr. Esplago Feniza</t>
-  </si>
-  <si>
-    <t>Billy Jim Morelos</t>
-  </si>
-  <si>
-    <t>Haren Del Campo</t>
-  </si>
-  <si>
-    <t>Mohamed Nabhan M. Shahiq</t>
-  </si>
-  <si>
-    <t>Rogelio Reyes Gomez Jr.</t>
-  </si>
-  <si>
-    <t>John Michael Yagonia</t>
-  </si>
-  <si>
-    <t>Ronnie Villanueva Gutierrez</t>
-  </si>
-  <si>
-    <t>Nenad Jovkovic</t>
-  </si>
-  <si>
-    <t>Nhuel Caguicla Landicho</t>
-  </si>
-  <si>
-    <t>Mohamed Riswan Mohamed Salyh</t>
-  </si>
-  <si>
-    <t>Dennis Ibe Sudario</t>
-  </si>
-  <si>
-    <t>Christian Archie Barbosa Niez</t>
-  </si>
-  <si>
-    <t>Clint Jude Duarte Bicoy</t>
-  </si>
-  <si>
-    <t>Willie Facun Adi</t>
-  </si>
-  <si>
-    <t>Eduard Embate Endonela</t>
-  </si>
-  <si>
-    <t>Sugathadasa Pattiwilage</t>
-  </si>
-  <si>
-    <t>Gomer Repaso Plenos</t>
-  </si>
-  <si>
-    <t>John Errol Para Marino</t>
-  </si>
-  <si>
-    <t>Gabuin James Buintim</t>
-  </si>
-  <si>
-    <t>Marlon Rodel Fracisco Pimentel</t>
-  </si>
-  <si>
-    <t>Nathaniel Laguidao Gamosa</t>
-  </si>
-  <si>
-    <t>Ernesto JR Leona Campana</t>
-  </si>
-  <si>
-    <t>William Villanueva Gutierrez</t>
-  </si>
-  <si>
-    <t>Conrado DE Guzman Vineza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elecer Hernandez Llamoso </t>
-  </si>
-  <si>
-    <t>Elesor JR Cas Frondozo</t>
-  </si>
-  <si>
-    <t>Carlo Alcoran Tenorio</t>
-  </si>
-  <si>
-    <t>Alvin Quizon Tabasa</t>
-  </si>
-  <si>
-    <t>Miguelito Costelo Mainit</t>
-  </si>
-  <si>
-    <t>Mohamed Nasardeen Mohamadu Main</t>
-  </si>
-  <si>
-    <t>Dominic Munyua Kanyotu</t>
-  </si>
-  <si>
-    <t>Lenson Kiarie Karuru</t>
-  </si>
-  <si>
-    <t>Ryan Mauring Adol</t>
-  </si>
-  <si>
-    <t>Joey JR Tiwo Meramonte</t>
-  </si>
-  <si>
-    <t>Mario Dorado Hernandez</t>
-  </si>
-  <si>
-    <t>Sooraj Kurisinkal Reji</t>
-  </si>
-  <si>
     <t>IT/PLC</t>
   </si>
   <si>
-    <t>Jose Isagani Jr. Jamero Alaan</t>
-  </si>
-  <si>
-    <t>Jishnu Surendran</t>
-  </si>
-  <si>
-    <t>Saritha Oromariyil Sukumaran</t>
-  </si>
-  <si>
-    <t>Renz Jake Orense Lontoc</t>
-  </si>
-  <si>
-    <t>Dennis Delfino Daginotan</t>
-  </si>
-  <si>
-    <t>John Eric Bonganay Borcelis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Maitem Maureal </t>
-  </si>
-  <si>
-    <t>Paul Jeric Azul Falcatan</t>
-  </si>
-  <si>
-    <t>Roderick Cailao Amar</t>
-  </si>
-  <si>
-    <t>Jimmy Mallari Dela Cruz</t>
-  </si>
-  <si>
-    <t>Meegle Mathew</t>
-  </si>
-  <si>
-    <t>Thuvarakan Pulenthiran</t>
-  </si>
-  <si>
-    <t>Jerome Latagan Cardejon</t>
-  </si>
-  <si>
-    <t>Jay Tucker Mendoza</t>
-  </si>
-  <si>
-    <t>Crisfo Lo Nibal</t>
-  </si>
-  <si>
-    <t>Simon Kenneth Inoceno Hernandez</t>
-  </si>
-  <si>
-    <t>Levitico Jose Caniedo</t>
-  </si>
-  <si>
-    <t>Mohamed Faizal Mohamed Uvais</t>
-  </si>
-  <si>
-    <t>Nhar Jaradal Cillo</t>
-  </si>
-  <si>
-    <t>Herwin Fatalla Mimay</t>
-  </si>
-  <si>
-    <t>Nino Vercide Arda</t>
-  </si>
-  <si>
-    <t>Jason Puzon Dy</t>
-  </si>
-  <si>
-    <t>Rholie Pacio Casison</t>
-  </si>
-  <si>
-    <t>Jeffrey Manarpaac Urolaza</t>
-  </si>
-  <si>
-    <t>Edison Mendoza Rojas</t>
-  </si>
-  <si>
-    <t>Mark Merill Jovenes Tirol</t>
-  </si>
-  <si>
-    <t>Kennedy Gichuhi Ngaruiya</t>
-  </si>
-  <si>
-    <t>Francis Agbor Eyong Atem</t>
-  </si>
-  <si>
-    <t>Siraj Moolakkappil</t>
-  </si>
-  <si>
-    <t>Mohamed Bilal Muneer Basha</t>
-  </si>
-  <si>
-    <t>Alen Cherippanat Babu</t>
-  </si>
-  <si>
-    <t>Mohamed Shafras Jawlangull</t>
-  </si>
-  <si>
-    <t>Renson Gicheha Gicheru</t>
-  </si>
-  <si>
-    <t>Mohamed Faris Mohamed Naleem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shihabdeen Seeni Mohamed </t>
-  </si>
-  <si>
-    <t>Prakyath Prabhakar Amin</t>
-  </si>
-  <si>
-    <t>Julius Kateregga</t>
-  </si>
-  <si>
-    <t>Kishanraj Pulenthiran</t>
-  </si>
-  <si>
-    <t>James Kariungi Muthee</t>
-  </si>
-  <si>
-    <t>Kasansula Francis Kiwanuka</t>
-  </si>
-  <si>
-    <t>Arnel Neri Montemayor</t>
-  </si>
-  <si>
-    <t>Erick Omondi Okoyo</t>
-  </si>
-  <si>
-    <t>Trevin Christopher Neydorf</t>
-  </si>
-  <si>
-    <t>Mohamed Mufaris Mohamed Jameel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasim Kinarullaparambath Kunhabdulla </t>
-  </si>
-  <si>
-    <t>Naser Qasim Mohammad Alhaj Ahmed</t>
-  </si>
-  <si>
-    <t>Jeffrey Sayson Bagatua</t>
-  </si>
-  <si>
-    <t>Wali Mohammed Sabry</t>
-  </si>
-  <si>
-    <t>Rommel Tamayo Eleosida</t>
-  </si>
-  <si>
-    <t>Errolnil Purificacion Atienza</t>
-  </si>
-  <si>
-    <t>Hernan John Baguion Murcillos</t>
-  </si>
-  <si>
-    <t>Ivan Raphael Macatangay Del Mundo</t>
-  </si>
-  <si>
-    <t>Jerico Tallorin Atienzo</t>
-  </si>
-  <si>
-    <t>Alvin Tumboc Cuevas</t>
-  </si>
-  <si>
-    <t>James Andrew Aquino Rodillo</t>
-  </si>
-  <si>
-    <t>Alvin Cataquiz Austria</t>
-  </si>
-  <si>
-    <t>Jayson Ruz Oligan</t>
-  </si>
-  <si>
-    <t>John Michael Angelo Mesina Clemen</t>
-  </si>
-  <si>
-    <t>Lemuel Carcellar Macatangay</t>
-  </si>
-  <si>
-    <t>Nikko Villanueva Cruz</t>
-  </si>
-  <si>
-    <t>Justin Paolo Macatangay Ilao</t>
-  </si>
-  <si>
-    <t>Jake Alinabon Salibay</t>
-  </si>
-  <si>
-    <t>Marlon Yuson Pamplona</t>
-  </si>
-  <si>
-    <t>Joe Vergil Jr Calanza Dormitorio</t>
-  </si>
-  <si>
-    <t>Bonifacio Arano Bayer</t>
-  </si>
-  <si>
-    <t>Sumedha Pradeep Dissanayaka</t>
-  </si>
-  <si>
-    <t>Yuvashanth Somasuntharam kukasuthan</t>
-  </si>
-  <si>
-    <t>Jonel Catibog Katigbak</t>
-  </si>
-  <si>
-    <t>Catalino Mendoza Rojas</t>
-  </si>
-  <si>
-    <t>Murshidul Haq Patteri Thazhe Kuni</t>
-  </si>
-  <si>
-    <t>Nisham Kizhakke Valappil</t>
-  </si>
-  <si>
-    <t>Pasidu Pamodaya Rathnayake Rathnayake Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Chalana Ishan Dishanayake Dishanayake Pathiranage</t>
-  </si>
-  <si>
-    <t>Mohamed Ahthir Abdul Majeed</t>
-  </si>
-  <si>
-    <t>Niroshan Abesingha Abesingha Karunarathna Mudalige</t>
-  </si>
-  <si>
-    <t>Sathis Gunawardhana Dikella Kandha Yakdhehirallage</t>
-  </si>
-  <si>
-    <t>Tharaka Thanujaya Dissanayaka Dissanayaka Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Nishan Ekanayake Ekanayake Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Jacky Chan Nava Gastardo</t>
-  </si>
-  <si>
-    <t>Mohammed Fahim Mohammed Laffir</t>
-  </si>
-  <si>
-    <t>Sameera Lakmal Rupasinghe Arachchige</t>
-  </si>
-  <si>
-    <t>Dushan Priyankara Herath Herath Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Pathmapriyan Muruguppilla</t>
-  </si>
-  <si>
-    <t>Roshan Chaminda Udawaththa Udawaththa Kankanamge</t>
-  </si>
-  <si>
-    <t>Kusal Sharmila Hewa Kokawalage</t>
-  </si>
-  <si>
-    <t>Mohomed Minnas Mohomed Ramees</t>
-  </si>
-  <si>
-    <t>Mabin Pauly</t>
-  </si>
-  <si>
-    <t>Jahsim Saycon Apila</t>
-  </si>
-  <si>
-    <t>Shern Sebastian Sebastian Simon</t>
-  </si>
-  <si>
-    <t>Wai Hin Phyo</t>
-  </si>
-  <si>
-    <t>Hicham Charkaoui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mohamed Shaheer Mohamed Laffir </t>
-  </si>
-  <si>
-    <t>Antony Kamau Kageche</t>
-  </si>
-  <si>
-    <t>Abdulrashid Byarugaba </t>
-  </si>
-  <si>
-    <t>Justine Tiangson Clave</t>
-  </si>
-  <si>
-    <t>Harikaran Seenithamby</t>
-  </si>
-  <si>
-    <t>Wycliffe Mushori</t>
-  </si>
-  <si>
-    <t>Peter Nganga Kamau</t>
-  </si>
-  <si>
-    <t>Sumesh Soman</t>
-  </si>
-  <si>
-    <t>Muhammed Ashiq Mohamed Mumtaz</t>
-  </si>
-  <si>
-    <t>Arvin Clyde D.Crisme</t>
-  </si>
-  <si>
-    <t>Gary John Packer</t>
-  </si>
-  <si>
-    <t>Ifras Mohammed</t>
-  </si>
-  <si>
-    <t>Alby Manchandiyil Antony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ifran Ansari </t>
-  </si>
-  <si>
-    <t>Piratheepan Thiyagarasa</t>
-  </si>
-  <si>
-    <t>Moustafa Hassan Ibrahim Elsayyad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harsha Shetty </t>
-  </si>
-  <si>
-    <t>Kevin Carl Enriquez Serrano</t>
-  </si>
-  <si>
-    <t>Romie Ross Tamayo Eleosida</t>
-  </si>
-  <si>
-    <t>Quennan Carandang Cuesta</t>
-  </si>
-  <si>
     <t>U5</t>
-  </si>
-  <si>
-    <t>Lester John Fuentes Monter</t>
-  </si>
-  <si>
-    <t>Neil Jhon Sabile Ramos</t>
-  </si>
-  <si>
-    <t>Kim Harvey Cuevas Ayag</t>
-  </si>
-  <si>
-    <t>Nelson Jr Ybut Sancho</t>
-  </si>
-  <si>
-    <t>Rolly Miano Valdez</t>
-  </si>
-  <si>
-    <t>Daniel Bacolcol Orquiza</t>
-  </si>
-  <si>
-    <t>Roby Chua Malinao</t>
-  </si>
-  <si>
-    <t>Lorence Cardenas Cabales</t>
-  </si>
-  <si>
-    <t>Emmanuel Richard Marasigan Velasco</t>
-  </si>
-  <si>
-    <t>Michael Jorge Toscano Masaoy</t>
-  </si>
-  <si>
-    <t>Jeffrey De Vera Cabico</t>
-  </si>
-  <si>
-    <t>Joe Peter Angustia Pimentel</t>
-  </si>
-  <si>
-    <t>Mark Roentgen Macatangay Delen</t>
-  </si>
-  <si>
-    <t>Arjay Imperial Gabarda</t>
-  </si>
-  <si>
-    <t>Noey Francisco Canonizado</t>
-  </si>
-  <si>
-    <t>Omar Zaki Saad Abdel Nabi</t>
-  </si>
-  <si>
-    <t>Abdul Rehman Mohammed Abdul Mohammed</t>
-  </si>
-  <si>
-    <t>Christian Merck Morada Martija</t>
-  </si>
-  <si>
-    <t>Imesha Rashmi Mudannayaka Mudannayakage</t>
-  </si>
-  <si>
-    <t>Sajith Dulanjana Kumara Rathnayaka Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Thisura Kaumal Wijesinghe</t>
-  </si>
-  <si>
-    <t>Shanel Rukshan Perera Kurana Patabendige</t>
-  </si>
-  <si>
-    <t>Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon</t>
   </si>
 </sst>
 </file>
@@ -2048,7 +2048,7 @@
         <v>233</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>278</v>
+        <v>493</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -2062,7 +2062,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>234</v>
@@ -2082,7 +2082,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>235</v>
@@ -2102,13 +2102,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>220</v>
@@ -2124,13 +2124,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>220</v>
@@ -2146,7 +2146,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>238</v>
@@ -2166,13 +2166,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>220</v>
@@ -2188,13 +2188,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>220</v>
@@ -2210,7 +2210,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>235</v>
@@ -2230,13 +2230,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>220</v>
@@ -2252,13 +2252,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>278</v>
+        <v>493</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2272,7 +2272,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>234</v>
@@ -2292,13 +2292,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>220</v>
@@ -2314,13 +2314,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>220</v>
@@ -2336,7 +2336,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>242</v>
@@ -2356,13 +2356,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>220</v>
@@ -2378,13 +2378,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>220</v>
@@ -2400,13 +2400,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>220</v>
@@ -2422,13 +2422,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>220</v>
@@ -2444,13 +2444,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>220</v>
@@ -2466,7 +2466,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>245</v>
@@ -2486,7 +2486,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>242</v>
@@ -2506,13 +2506,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>220</v>
@@ -2528,13 +2528,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>220</v>
@@ -2550,7 +2550,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>242</v>
@@ -2570,7 +2570,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>234</v>
@@ -2590,7 +2590,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>242</v>
@@ -2610,13 +2610,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>220</v>
@@ -2632,7 +2632,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>234</v>
@@ -2652,13 +2652,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>220</v>
@@ -2674,7 +2674,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>234</v>
@@ -2694,7 +2694,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>246</v>
@@ -2714,7 +2714,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>246</v>
@@ -2734,13 +2734,13 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>220</v>
@@ -2756,13 +2756,13 @@
         <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>220</v>
@@ -2778,7 +2778,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>248</v>
@@ -2798,13 +2798,13 @@
         <v>40</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>220</v>
@@ -2820,7 +2820,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>242</v>
@@ -2840,13 +2840,13 @@
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>220</v>
@@ -2862,13 +2862,13 @@
         <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>220</v>
@@ -2884,7 +2884,7 @@
         <v>44</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>234</v>
@@ -2904,7 +2904,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>242</v>
@@ -2924,7 +2924,7 @@
         <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>249</v>
@@ -2944,7 +2944,7 @@
         <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>246</v>
@@ -2964,7 +2964,7 @@
         <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>250</v>
@@ -2984,7 +2984,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>250</v>
@@ -3004,7 +3004,7 @@
         <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>235</v>
@@ -3024,7 +3024,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>250</v>
@@ -3044,7 +3044,7 @@
         <v>52</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>235</v>
@@ -3064,7 +3064,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>249</v>
@@ -3084,7 +3084,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>250</v>
@@ -3104,7 +3104,7 @@
         <v>55</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>251</v>
@@ -3124,13 +3124,13 @@
         <v>56</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>220</v>
@@ -3146,13 +3146,13 @@
         <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>233</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>278</v>
+        <v>493</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -3166,7 +3166,7 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>238</v>
@@ -3186,13 +3186,13 @@
         <v>59</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>220</v>
@@ -3208,13 +3208,13 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>220</v>
@@ -3230,13 +3230,13 @@
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>220</v>
@@ -3252,13 +3252,13 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>220</v>
@@ -3274,7 +3274,7 @@
         <v>63</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>245</v>
@@ -3294,7 +3294,7 @@
         <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>242</v>
@@ -3314,13 +3314,13 @@
         <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>220</v>
@@ -3336,13 +3336,13 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>220</v>
@@ -3358,7 +3358,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>245</v>
@@ -3378,7 +3378,7 @@
         <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>234</v>
@@ -3398,7 +3398,7 @@
         <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>235</v>
@@ -3418,7 +3418,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>251</v>
@@ -3438,7 +3438,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>245</v>
@@ -3458,7 +3458,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>251</v>
@@ -3478,13 +3478,13 @@
         <v>73</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>220</v>
@@ -3500,7 +3500,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>250</v>
@@ -3520,7 +3520,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>253</v>
@@ -3540,13 +3540,13 @@
         <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>220</v>
@@ -3562,7 +3562,7 @@
         <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>245</v>
@@ -3582,13 +3582,13 @@
         <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>220</v>
@@ -3604,13 +3604,13 @@
         <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>220</v>
@@ -3626,13 +3626,13 @@
         <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>220</v>
@@ -3648,7 +3648,7 @@
         <v>81</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>234</v>
@@ -3668,13 +3668,13 @@
         <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>220</v>
@@ -3690,13 +3690,13 @@
         <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>220</v>
@@ -3712,7 +3712,7 @@
         <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>253</v>
@@ -3732,13 +3732,13 @@
         <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -3752,7 +3752,7 @@
         <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>235</v>
@@ -3772,7 +3772,7 @@
         <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>234</v>
@@ -3792,7 +3792,7 @@
         <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>234</v>
@@ -3812,7 +3812,7 @@
         <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>251</v>
@@ -3832,7 +3832,7 @@
         <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>242</v>
@@ -3852,7 +3852,7 @@
         <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>242</v>
@@ -3872,13 +3872,13 @@
         <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>220</v>
@@ -3894,7 +3894,7 @@
         <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>235</v>
@@ -3914,13 +3914,13 @@
         <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>220</v>
@@ -3936,7 +3936,7 @@
         <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>235</v>
@@ -3956,7 +3956,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>234</v>
@@ -3976,7 +3976,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>255</v>
@@ -3996,7 +3996,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>249</v>
@@ -4016,7 +4016,7 @@
         <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>245</v>
@@ -4036,7 +4036,7 @@
         <v>100</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>250</v>
@@ -4056,7 +4056,7 @@
         <v>101</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>234</v>
@@ -4076,7 +4076,7 @@
         <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>240</v>
@@ -4096,13 +4096,13 @@
         <v>103</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>220</v>
@@ -4118,7 +4118,7 @@
         <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>241</v>
@@ -4138,13 +4138,13 @@
         <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>220</v>
@@ -4160,7 +4160,7 @@
         <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>250</v>
@@ -4180,7 +4180,7 @@
         <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>234</v>
@@ -4200,13 +4200,13 @@
         <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>220</v>
@@ -4222,7 +4222,7 @@
         <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>241</v>
@@ -4244,13 +4244,13 @@
         <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>220</v>
@@ -4266,13 +4266,13 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>220</v>
@@ -4288,7 +4288,7 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>235</v>
@@ -4308,7 +4308,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>234</v>
@@ -4328,13 +4328,13 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
@@ -4348,13 +4348,13 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
@@ -4368,7 +4368,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>242</v>
@@ -4388,13 +4388,13 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>220</v>
@@ -4410,7 +4410,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>257</v>
@@ -4430,7 +4430,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>249</v>
@@ -4450,7 +4450,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>246</v>
@@ -4470,7 +4470,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>248</v>
@@ -4490,7 +4490,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>257</v>
@@ -4510,13 +4510,13 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>220</v>
@@ -4532,7 +4532,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>253</v>
@@ -4552,13 +4552,13 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>258</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>220</v>
@@ -4574,7 +4574,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>258</v>
@@ -4594,7 +4594,7 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>253</v>
@@ -4614,13 +4614,13 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>220</v>
@@ -4636,7 +4636,7 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>242</v>
@@ -4656,13 +4656,13 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -4676,13 +4676,13 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>238</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>278</v>
+        <v>493</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -4696,7 +4696,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>259</v>
@@ -4716,13 +4716,13 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -4736,13 +4736,13 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>220</v>
@@ -4758,7 +4758,7 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>242</v>
@@ -4778,7 +4778,7 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>253</v>
@@ -4798,13 +4798,13 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>220</v>
@@ -4820,7 +4820,7 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>235</v>
@@ -4840,13 +4840,13 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>220</v>
@@ -4862,7 +4862,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>245</v>
@@ -4882,13 +4882,13 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>220</v>
@@ -4904,7 +4904,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>235</v>
@@ -4924,7 +4924,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>249</v>
@@ -4944,7 +4944,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>245</v>
@@ -4964,7 +4964,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -4984,13 +4984,13 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>220</v>
@@ -5006,7 +5006,7 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>245</v>
@@ -5026,7 +5026,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>245</v>
@@ -5046,7 +5046,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>245</v>
@@ -5066,7 +5066,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>243</v>
@@ -5086,13 +5086,13 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>220</v>
@@ -5108,7 +5108,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>249</v>
@@ -5128,13 +5128,13 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>220</v>
@@ -5150,7 +5150,7 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>242</v>
@@ -5172,13 +5172,13 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
@@ -5192,13 +5192,13 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
@@ -5212,13 +5212,13 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>220</v>
@@ -5234,13 +5234,13 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>220</v>
@@ -5256,7 +5256,7 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>257</v>
@@ -5276,7 +5276,7 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>242</v>
@@ -5298,13 +5298,13 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>220</v>
@@ -5320,13 +5320,13 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>220</v>
@@ -5342,13 +5342,13 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>220</v>
@@ -5364,7 +5364,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>250</v>
@@ -5384,7 +5384,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>253</v>
@@ -5404,7 +5404,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>256</v>
@@ -5426,7 +5426,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>242</v>
@@ -5446,7 +5446,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>235</v>
@@ -5466,7 +5466,7 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>256</v>
@@ -5486,7 +5486,7 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>242</v>
@@ -5506,7 +5506,7 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>253</v>
@@ -5526,7 +5526,7 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>235</v>
@@ -5546,7 +5546,7 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>240</v>
@@ -5568,13 +5568,13 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -5588,7 +5588,7 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>235</v>
@@ -5608,13 +5608,13 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>260</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>278</v>
+        <v>493</v>
       </c>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
@@ -5628,7 +5628,7 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>245</v>
@@ -5648,7 +5648,7 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>245</v>
@@ -5668,13 +5668,13 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>220</v>
@@ -5690,7 +5690,7 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>247</v>
@@ -5710,13 +5710,13 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>220</v>
@@ -5732,13 +5732,13 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>220</v>
@@ -5754,13 +5754,13 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>220</v>
@@ -5776,13 +5776,13 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
@@ -5796,13 +5796,13 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
@@ -5816,7 +5816,7 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>239</v>
@@ -5838,13 +5838,13 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>261</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>278</v>
+        <v>493</v>
       </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
@@ -5858,7 +5858,7 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>249</v>
@@ -5878,13 +5878,13 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>220</v>
@@ -5900,13 +5900,13 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>220</v>
@@ -5922,7 +5922,7 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>262</v>
@@ -5942,7 +5942,7 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>263</v>
@@ -5962,13 +5962,13 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>220</v>
@@ -5984,13 +5984,13 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>220</v>
@@ -6006,13 +6006,13 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>220</v>
@@ -6028,13 +6028,13 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>254</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>220</v>
@@ -6050,7 +6050,7 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>235</v>
@@ -6070,7 +6070,7 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>254</v>
@@ -6092,7 +6092,7 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>235</v>
@@ -6112,7 +6112,7 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>250</v>
@@ -6132,13 +6132,13 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>220</v>
@@ -6154,13 +6154,13 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>220</v>
@@ -6176,7 +6176,7 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>248</v>
@@ -6196,7 +6196,7 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>235</v>
@@ -6216,13 +6216,13 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>220</v>
@@ -6238,13 +6238,13 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>220</v>
@@ -6260,7 +6260,7 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>254</v>
@@ -6282,7 +6282,7 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>250</v>
@@ -6302,13 +6302,13 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>220</v>
@@ -6324,13 +6324,13 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>254</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>220</v>
@@ -6346,13 +6346,13 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>220</v>
@@ -6368,13 +6368,13 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>238</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>278</v>
+        <v>493</v>
       </c>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
@@ -6388,13 +6388,13 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
@@ -6408,7 +6408,7 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>251</v>
@@ -6428,7 +6428,7 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>262</v>
@@ -6448,13 +6448,13 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>220</v>
@@ -6470,7 +6470,7 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>251</v>
@@ -6490,13 +6490,13 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>220</v>
@@ -6512,13 +6512,13 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>286</v>
+        <v>495</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>220</v>
@@ -6701,7 +6701,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>234</v>
@@ -6743,7 +6743,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>235</v>
@@ -6785,7 +6785,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>236</v>
@@ -6827,7 +6827,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>237</v>
@@ -6869,7 +6869,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>238</v>
@@ -6911,7 +6911,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>239</v>
@@ -6953,7 +6953,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>240</v>
@@ -6995,7 +6995,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>235</v>
@@ -7037,7 +7037,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>239</v>
@@ -7079,7 +7079,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>239</v>
@@ -7121,7 +7121,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>234</v>
@@ -7163,7 +7163,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>241</v>
@@ -7205,7 +7205,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>239</v>
@@ -7247,7 +7247,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>242</v>
@@ -7289,7 +7289,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>243</v>
@@ -7331,7 +7331,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>244</v>
@@ -7373,18 +7373,20 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D19" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E19" s="8">
         <v>46212</v>
       </c>
-      <c r="F19" s="6"/>
+      <c r="F19" s="6">
+        <v>46227</v>
+      </c>
       <c r="G19" s="8">
         <v>46212</v>
       </c>
@@ -7424,7 +7426,9 @@
       <c r="S19" s="8">
         <v>46166</v>
       </c>
-      <c r="T19" s="6"/>
+      <c r="T19" s="8">
+        <v>46227</v>
+      </c>
       <c r="U19" s="8">
         <v>46168</v>
       </c>
@@ -7455,7 +7459,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>243</v>
@@ -7533,18 +7537,20 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D21" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E21" s="8">
         <v>46212</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="F21" s="8">
+        <v>46227</v>
+      </c>
       <c r="G21" s="8">
         <v>46212</v>
       </c>
@@ -7584,7 +7590,9 @@
       <c r="S21" s="8">
         <v>46166</v>
       </c>
-      <c r="T21" s="6"/>
+      <c r="T21" s="8">
+        <v>46227</v>
+      </c>
       <c r="U21" s="8">
         <v>46168</v>
       </c>
@@ -7611,7 +7619,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>245</v>
@@ -7653,7 +7661,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>242</v>
@@ -7695,7 +7703,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>240</v>
@@ -7737,7 +7745,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>237</v>
@@ -7821,7 +7829,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>242</v>
@@ -7863,7 +7871,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>234</v>
@@ -7905,7 +7913,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>242</v>
@@ -7947,7 +7955,7 @@
         <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>236</v>
@@ -8017,7 +8025,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>234</v>
@@ -8059,7 +8067,7 @@
         <v>33</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>237</v>
@@ -8133,7 +8141,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>234</v>
@@ -8175,7 +8183,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>246</v>
@@ -8217,7 +8225,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>246</v>
@@ -8259,13 +8267,13 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D35" s="1">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E35" s="8">
         <v>46176</v>
@@ -8320,13 +8328,21 @@
         <v>46183</v>
       </c>
       <c r="W35" s="6"/>
-      <c r="X35" s="6"/>
-      <c r="Y35" s="6"/>
-      <c r="Z35" s="6"/>
+      <c r="X35" s="6">
+        <v>46232</v>
+      </c>
+      <c r="Y35" s="6">
+        <v>46232</v>
+      </c>
+      <c r="Z35" s="6">
+        <v>46232</v>
+      </c>
       <c r="AA35" s="6">
         <v>46188</v>
       </c>
-      <c r="AB35" s="6"/>
+      <c r="AB35" s="6">
+        <v>46232</v>
+      </c>
       <c r="AC35" s="6"/>
       <c r="AD35" s="6"/>
       <c r="AE35" s="6"/>
@@ -8337,7 +8353,7 @@
         <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>247</v>
@@ -8421,7 +8437,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>248</v>
@@ -8463,7 +8479,7 @@
         <v>40</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>240</v>
@@ -8513,7 +8529,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>242</v>
@@ -8555,7 +8571,7 @@
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>241</v>
@@ -8639,7 +8655,7 @@
         <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>241</v>
@@ -8723,7 +8739,7 @@
         <v>44</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>234</v>
@@ -8765,7 +8781,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>242</v>
@@ -8807,7 +8823,7 @@
         <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>249</v>
@@ -8849,7 +8865,7 @@
         <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>246</v>
@@ -8891,7 +8907,7 @@
         <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>250</v>
@@ -8933,7 +8949,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>250</v>
@@ -8975,7 +8991,7 @@
         <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>235</v>
@@ -9017,7 +9033,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>250</v>
@@ -9059,7 +9075,7 @@
         <v>52</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>235</v>
@@ -9101,7 +9117,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>249</v>
@@ -9143,7 +9159,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>250</v>
@@ -9185,7 +9201,7 @@
         <v>55</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>251</v>
@@ -9227,7 +9243,7 @@
         <v>56</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>239</v>
@@ -9269,7 +9285,7 @@
         <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>233</v>
@@ -9311,7 +9327,7 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>238</v>
@@ -9353,7 +9369,7 @@
         <v>59</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>252</v>
@@ -9437,7 +9453,7 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>241</v>
@@ -9521,7 +9537,7 @@
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>241</v>
@@ -9563,13 +9579,13 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D60" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
@@ -9581,8 +9597,12 @@
       <c r="J60" s="10"/>
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="6"/>
+      <c r="M60" s="8">
+        <v>46231</v>
+      </c>
+      <c r="N60" s="8">
+        <v>46231</v>
+      </c>
       <c r="O60" s="6"/>
       <c r="P60" s="6"/>
       <c r="Q60" s="6"/>
@@ -9591,8 +9611,12 @@
         <v>46193</v>
       </c>
       <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
-      <c r="V60" s="6"/>
+      <c r="U60" s="8">
+        <v>46227</v>
+      </c>
+      <c r="V60" s="8">
+        <v>46228</v>
+      </c>
       <c r="W60" s="6"/>
       <c r="X60" s="6"/>
       <c r="Y60" s="6"/>
@@ -9613,7 +9637,7 @@
         <v>63</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>245</v>
@@ -9655,7 +9679,7 @@
         <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>242</v>
@@ -9697,7 +9721,7 @@
         <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>244</v>
@@ -9767,7 +9791,7 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>237</v>
@@ -9829,7 +9853,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>245</v>
@@ -9871,7 +9895,7 @@
         <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>234</v>
@@ -9913,7 +9937,7 @@
         <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>235</v>
@@ -9955,7 +9979,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>251</v>
@@ -9997,7 +10021,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>245</v>
@@ -10039,7 +10063,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>251</v>
@@ -10081,7 +10105,7 @@
         <v>73</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>247</v>
@@ -10165,7 +10189,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>250</v>
@@ -10207,7 +10231,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>253</v>
@@ -10249,18 +10273,20 @@
         <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D74" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E74" s="8">
         <v>46212</v>
       </c>
-      <c r="F74" s="6"/>
+      <c r="F74" s="8">
+        <v>46227</v>
+      </c>
       <c r="G74" s="8">
         <v>46212</v>
       </c>
@@ -10300,7 +10326,9 @@
       <c r="S74" s="6">
         <v>46166</v>
       </c>
-      <c r="T74" s="6"/>
+      <c r="T74" s="8">
+        <v>46227</v>
+      </c>
       <c r="U74" s="6">
         <v>46168</v>
       </c>
@@ -10331,7 +10359,7 @@
         <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>245</v>
@@ -10373,7 +10401,7 @@
         <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>241</v>
@@ -10457,7 +10485,7 @@
         <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>252</v>
@@ -10541,13 +10569,13 @@
         <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D78" s="1">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E78" s="8">
         <v>46156</v>
@@ -10599,12 +10627,22 @@
       <c r="V78" s="8">
         <v>46177</v>
       </c>
-      <c r="W78" s="6"/>
-      <c r="X78" s="6"/>
-      <c r="Y78" s="6"/>
-      <c r="Z78" s="6"/>
+      <c r="W78" s="8">
+        <v>46229</v>
+      </c>
+      <c r="X78" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Y78" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Z78" s="8">
+        <v>46229</v>
+      </c>
       <c r="AA78" s="6"/>
-      <c r="AB78" s="6"/>
+      <c r="AB78" s="8">
+        <v>46229</v>
+      </c>
       <c r="AC78" s="6"/>
       <c r="AD78" s="6"/>
       <c r="AE78" s="6"/>
@@ -10615,7 +10653,7 @@
         <v>81</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>234</v>
@@ -10657,13 +10695,13 @@
         <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D80" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -10675,8 +10713,12 @@
       <c r="J80" s="10"/>
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
-      <c r="M80" s="6"/>
-      <c r="N80" s="6"/>
+      <c r="M80" s="8">
+        <v>46231</v>
+      </c>
+      <c r="N80" s="8">
+        <v>46231</v>
+      </c>
       <c r="O80" s="6"/>
       <c r="P80" s="6"/>
       <c r="Q80" s="6"/>
@@ -10685,8 +10727,12 @@
         <v>46193</v>
       </c>
       <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
-      <c r="V80" s="6"/>
+      <c r="U80" s="8">
+        <v>46227</v>
+      </c>
+      <c r="V80" s="8">
+        <v>46228</v>
+      </c>
       <c r="W80" s="6"/>
       <c r="X80" s="6"/>
       <c r="Y80" s="6"/>
@@ -10707,13 +10753,13 @@
         <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D81" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
@@ -10725,8 +10771,12 @@
       <c r="J81" s="10"/>
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
-      <c r="M81" s="6"/>
-      <c r="N81" s="6"/>
+      <c r="M81" s="8">
+        <v>46231</v>
+      </c>
+      <c r="N81" s="8">
+        <v>46231</v>
+      </c>
       <c r="O81" s="6"/>
       <c r="P81" s="6"/>
       <c r="Q81" s="6"/>
@@ -10735,8 +10785,12 @@
         <v>46193</v>
       </c>
       <c r="T81" s="6"/>
-      <c r="U81" s="6"/>
-      <c r="V81" s="6"/>
+      <c r="U81" s="8">
+        <v>46227</v>
+      </c>
+      <c r="V81" s="8">
+        <v>46228</v>
+      </c>
       <c r="W81" s="6"/>
       <c r="X81" s="6"/>
       <c r="Y81" s="6"/>
@@ -10757,7 +10811,7 @@
         <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>253</v>
@@ -10799,7 +10853,7 @@
         <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>239</v>
@@ -10841,7 +10895,7 @@
         <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>235</v>
@@ -10883,7 +10937,7 @@
         <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>234</v>
@@ -10925,7 +10979,7 @@
         <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>234</v>
@@ -10967,7 +11021,7 @@
         <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>251</v>
@@ -11009,7 +11063,7 @@
         <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>242</v>
@@ -11051,7 +11105,7 @@
         <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>242</v>
@@ -11093,18 +11147,20 @@
         <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D90" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E90" s="8">
         <v>46212</v>
       </c>
-      <c r="F90" s="6"/>
+      <c r="F90" s="8">
+        <v>46227</v>
+      </c>
       <c r="G90" s="8">
         <v>46212</v>
       </c>
@@ -11144,7 +11200,9 @@
       <c r="S90" s="6">
         <v>46166</v>
       </c>
-      <c r="T90" s="6"/>
+      <c r="T90" s="8">
+        <v>46227</v>
+      </c>
       <c r="U90" s="6">
         <v>46168</v>
       </c>
@@ -11175,7 +11233,7 @@
         <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>235</v>
@@ -11217,7 +11275,7 @@
         <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>237</v>
@@ -11281,7 +11339,7 @@
         <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>235</v>
@@ -11323,7 +11381,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>234</v>
@@ -11365,7 +11423,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>255</v>
@@ -11407,7 +11465,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>249</v>
@@ -11449,7 +11507,7 @@
         <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>245</v>
@@ -11491,7 +11549,7 @@
         <v>100</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>250</v>
@@ -11533,7 +11591,7 @@
         <v>101</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>234</v>
@@ -11575,38 +11633,54 @@
         <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D100" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
       <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
+      <c r="I100" s="8">
+        <v>46227</v>
+      </c>
       <c r="J100" s="6"/>
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
-      <c r="M100" s="6"/>
-      <c r="N100" s="6"/>
+      <c r="M100" s="8">
+        <v>46231</v>
+      </c>
+      <c r="N100" s="8">
+        <v>46231</v>
+      </c>
       <c r="O100" s="6"/>
       <c r="P100" s="6"/>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
-      <c r="S100" s="6"/>
+      <c r="S100" s="8">
+        <v>46228</v>
+      </c>
       <c r="T100" s="6"/>
-      <c r="U100" s="6"/>
-      <c r="V100" s="6"/>
+      <c r="U100" s="8">
+        <v>46227</v>
+      </c>
+      <c r="V100" s="8">
+        <v>46228</v>
+      </c>
       <c r="W100" s="6"/>
       <c r="X100" s="6"/>
       <c r="Y100" s="6"/>
       <c r="Z100" s="6"/>
-      <c r="AA100" s="6"/>
-      <c r="AB100" s="6"/>
+      <c r="AA100" s="8">
+        <v>46227</v>
+      </c>
+      <c r="AB100" s="8">
+        <v>46228</v>
+      </c>
       <c r="AC100" s="6"/>
       <c r="AD100" s="6"/>
       <c r="AE100" s="6"/>
@@ -11617,13 +11691,13 @@
         <v>103</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D101" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E101" s="8">
         <v>46156</v>
@@ -11667,13 +11741,21 @@
       <c r="T101" s="6"/>
       <c r="U101" s="6"/>
       <c r="V101" s="6"/>
-      <c r="W101" s="6"/>
-      <c r="X101" s="6"/>
-      <c r="Y101" s="6"/>
-      <c r="Z101" s="6"/>
+      <c r="W101" s="8">
+        <v>46229</v>
+      </c>
+      <c r="X101" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Y101" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Z101" s="8">
+        <v>46229</v>
+      </c>
       <c r="AA101" s="6"/>
       <c r="AB101" s="8">
-        <v>46210</v>
+        <v>46229</v>
       </c>
       <c r="AC101" s="6"/>
       <c r="AD101" s="6"/>
@@ -11685,7 +11767,7 @@
         <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>241</v>
@@ -11727,18 +11809,20 @@
         <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D103" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E103" s="8">
         <v>46212</v>
       </c>
-      <c r="F103" s="6"/>
+      <c r="F103" s="8">
+        <v>46227</v>
+      </c>
       <c r="G103" s="8">
         <v>46212</v>
       </c>
@@ -11778,7 +11862,9 @@
       <c r="S103" s="6">
         <v>46166</v>
       </c>
-      <c r="T103" s="6"/>
+      <c r="T103" s="8">
+        <v>46227</v>
+      </c>
       <c r="U103" s="6">
         <v>46168</v>
       </c>
@@ -11809,7 +11895,7 @@
         <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>250</v>
@@ -11851,7 +11937,7 @@
         <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>234</v>
@@ -11893,7 +11979,7 @@
         <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>236</v>
@@ -11940,7 +12026,7 @@
       <c r="S106" s="6">
         <v>46166</v>
       </c>
-      <c r="T106" s="6"/>
+      <c r="T106" s="8"/>
       <c r="U106" s="6">
         <v>46168</v>
       </c>
@@ -11971,7 +12057,7 @@
         <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>241</v>
@@ -12013,7 +12099,7 @@
         <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>240</v>
@@ -12063,7 +12149,7 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>237</v>
@@ -12147,7 +12233,7 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>235</v>
@@ -12189,7 +12275,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>234</v>
@@ -12231,7 +12317,7 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>239</v>
@@ -12273,7 +12359,7 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>239</v>
@@ -12315,7 +12401,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>242</v>
@@ -12357,7 +12443,7 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>247</v>
@@ -12441,7 +12527,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>257</v>
@@ -12483,7 +12569,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>249</v>
@@ -12525,7 +12611,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>246</v>
@@ -12567,7 +12653,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>248</v>
@@ -12609,7 +12695,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>257</v>
@@ -12651,7 +12737,7 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>243</v>
@@ -12729,7 +12815,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>253</v>
@@ -12771,7 +12857,7 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>258</v>
@@ -12813,7 +12899,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>258</v>
@@ -12855,7 +12941,7 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>253</v>
@@ -12897,7 +12983,7 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>244</v>
@@ -12977,7 +13063,7 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>242</v>
@@ -13019,7 +13105,7 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>239</v>
@@ -13061,7 +13147,7 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>238</v>
@@ -13103,7 +13189,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>259</v>
@@ -13145,7 +13231,7 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>239</v>
@@ -13187,7 +13273,7 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>241</v>
@@ -13271,7 +13357,7 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>242</v>
@@ -13313,7 +13399,7 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>253</v>
@@ -13355,13 +13441,13 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D135" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -13373,8 +13459,12 @@
       <c r="J135" s="10"/>
       <c r="K135" s="6"/>
       <c r="L135" s="6"/>
-      <c r="M135" s="6"/>
-      <c r="N135" s="6"/>
+      <c r="M135" s="8">
+        <v>46231</v>
+      </c>
+      <c r="N135" s="8">
+        <v>46231</v>
+      </c>
       <c r="O135" s="6"/>
       <c r="P135" s="6"/>
       <c r="Q135" s="6"/>
@@ -13383,8 +13473,12 @@
         <v>46193</v>
       </c>
       <c r="T135" s="6"/>
-      <c r="U135" s="6"/>
-      <c r="V135" s="6"/>
+      <c r="U135" s="8">
+        <v>46227</v>
+      </c>
+      <c r="V135" s="8">
+        <v>46228</v>
+      </c>
       <c r="W135" s="6"/>
       <c r="X135" s="6"/>
       <c r="Y135" s="6"/>
@@ -13405,7 +13499,7 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>235</v>
@@ -13447,7 +13541,7 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>252</v>
@@ -13525,7 +13619,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>245</v>
@@ -13567,13 +13661,13 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D139" s="1">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E139" s="8">
         <v>46156</v>
@@ -13625,12 +13719,22 @@
       <c r="V139" s="8">
         <v>46177</v>
       </c>
-      <c r="W139" s="6"/>
-      <c r="X139" s="6"/>
-      <c r="Y139" s="6"/>
-      <c r="Z139" s="6"/>
+      <c r="W139" s="8">
+        <v>46229</v>
+      </c>
+      <c r="X139" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Y139" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Z139" s="8">
+        <v>46229</v>
+      </c>
       <c r="AA139" s="6"/>
-      <c r="AB139" s="6"/>
+      <c r="AB139" s="8">
+        <v>46229</v>
+      </c>
       <c r="AC139" s="6"/>
       <c r="AD139" s="6"/>
       <c r="AE139" s="6"/>
@@ -13641,7 +13745,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>235</v>
@@ -13683,7 +13787,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>249</v>
@@ -13725,7 +13829,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>245</v>
@@ -13767,7 +13871,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -13809,7 +13913,7 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>237</v>
@@ -13893,7 +13997,7 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>245</v>
@@ -13935,7 +14039,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>245</v>
@@ -13977,7 +14081,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>245</v>
@@ -14019,7 +14123,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>243</v>
@@ -14061,7 +14165,7 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>243</v>
@@ -14145,7 +14249,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>249</v>
@@ -14187,7 +14291,7 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>252</v>
@@ -14255,7 +14359,7 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>242</v>
@@ -14297,7 +14401,7 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>239</v>
@@ -14339,7 +14443,7 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>239</v>
@@ -14381,7 +14485,7 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>247</v>
@@ -14445,7 +14549,7 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>252</v>
@@ -14487,7 +14591,7 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>257</v>
@@ -14529,7 +14633,7 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>242</v>
@@ -14571,7 +14675,7 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>247</v>
@@ -14653,7 +14757,7 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>239</v>
@@ -14695,7 +14799,7 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>244</v>
@@ -14775,7 +14879,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>250</v>
@@ -14817,7 +14921,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>253</v>
@@ -14859,7 +14963,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>256</v>
@@ -14901,7 +15005,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>242</v>
@@ -14943,7 +15047,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>235</v>
@@ -14985,7 +15089,7 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>256</v>
@@ -15027,7 +15131,7 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>242</v>
@@ -15069,7 +15173,7 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>253</v>
@@ -15111,7 +15215,7 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>235</v>
@@ -15153,7 +15257,7 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>240</v>
@@ -15195,7 +15299,7 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>239</v>
@@ -15237,7 +15341,7 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>235</v>
@@ -15279,7 +15383,7 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>260</v>
@@ -15321,7 +15425,7 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>245</v>
@@ -15363,7 +15467,7 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>245</v>
@@ -15405,13 +15509,13 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D177" s="1">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E177" s="8">
         <v>46176</v>
@@ -15466,13 +15570,21 @@
         <v>46183</v>
       </c>
       <c r="W177" s="6"/>
-      <c r="X177" s="6"/>
-      <c r="Y177" s="6"/>
-      <c r="Z177" s="6"/>
+      <c r="X177" s="6">
+        <v>46232</v>
+      </c>
+      <c r="Y177" s="6">
+        <v>46232</v>
+      </c>
+      <c r="Z177" s="6">
+        <v>46232</v>
+      </c>
       <c r="AA177" s="8">
         <v>46188</v>
       </c>
-      <c r="AB177" s="6"/>
+      <c r="AB177" s="6">
+        <v>46232</v>
+      </c>
       <c r="AC177" s="6"/>
       <c r="AD177" s="6"/>
       <c r="AE177" s="6"/>
@@ -15483,7 +15595,7 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>247</v>
@@ -15525,7 +15637,7 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>243</v>
@@ -15595,7 +15707,7 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>252</v>
@@ -15673,13 +15785,13 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D181" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
@@ -15719,12 +15831,22 @@
       <c r="V181" s="8">
         <v>46177</v>
       </c>
-      <c r="W181" s="6"/>
-      <c r="X181" s="6"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
+      <c r="W181" s="8">
+        <v>46229</v>
+      </c>
+      <c r="X181" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Y181" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Z181" s="8">
+        <v>46229</v>
+      </c>
       <c r="AA181" s="6"/>
-      <c r="AB181" s="6"/>
+      <c r="AB181" s="8">
+        <v>46229</v>
+      </c>
       <c r="AC181" s="6"/>
       <c r="AD181" s="6"/>
       <c r="AE181" s="6"/>
@@ -15735,7 +15857,7 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>239</v>
@@ -15777,7 +15899,7 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>250</v>
@@ -15819,7 +15941,7 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>239</v>
@@ -15861,7 +15983,7 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>261</v>
@@ -15903,7 +16025,7 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>249</v>
@@ -15945,7 +16067,7 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>239</v>
@@ -15987,7 +16109,7 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>244</v>
@@ -16067,7 +16189,7 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>262</v>
@@ -16109,7 +16231,7 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>263</v>
@@ -16151,7 +16273,7 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>241</v>
@@ -16235,13 +16357,13 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D192" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E192" s="6">
         <v>46149</v>
@@ -16289,12 +16411,22 @@
       <c r="V192" s="8">
         <v>46177</v>
       </c>
-      <c r="W192" s="6"/>
-      <c r="X192" s="6"/>
-      <c r="Y192" s="6"/>
-      <c r="Z192" s="6"/>
+      <c r="W192" s="8">
+        <v>46229</v>
+      </c>
+      <c r="X192" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Y192" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Z192" s="8">
+        <v>46229</v>
+      </c>
       <c r="AA192" s="6"/>
-      <c r="AB192" s="6"/>
+      <c r="AB192" s="8">
+        <v>46229</v>
+      </c>
       <c r="AC192" s="6"/>
       <c r="AD192" s="6"/>
       <c r="AE192" s="6"/>
@@ -16305,13 +16437,13 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D193" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E193" s="8">
         <v>46181</v>
@@ -16354,15 +16486,19 @@
       <c r="U193" s="6"/>
       <c r="V193" s="6"/>
       <c r="W193" s="6"/>
-      <c r="X193" s="8">
-        <v>46182</v>
-      </c>
-      <c r="Y193" s="8">
-        <v>46182</v>
-      </c>
-      <c r="Z193" s="6"/>
+      <c r="X193" s="6">
+        <v>46232</v>
+      </c>
+      <c r="Y193" s="6">
+        <v>46232</v>
+      </c>
+      <c r="Z193" s="6">
+        <v>46232</v>
+      </c>
       <c r="AA193" s="6"/>
-      <c r="AB193" s="6"/>
+      <c r="AB193" s="6">
+        <v>46232</v>
+      </c>
       <c r="AC193" s="6"/>
       <c r="AD193" s="6"/>
       <c r="AE193" s="6"/>
@@ -16373,7 +16509,7 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>254</v>
@@ -16415,7 +16551,7 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>235</v>
@@ -16457,7 +16593,7 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>254</v>
@@ -16499,7 +16635,7 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>235</v>
@@ -16541,7 +16677,7 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>250</v>
@@ -16583,18 +16719,20 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D199" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E199" s="8">
         <v>46212</v>
       </c>
-      <c r="F199" s="6"/>
+      <c r="F199" s="8">
+        <v>46227</v>
+      </c>
       <c r="G199" s="8">
         <v>46212</v>
       </c>
@@ -16634,7 +16772,9 @@
       <c r="S199" s="8">
         <v>46166</v>
       </c>
-      <c r="T199" s="6"/>
+      <c r="T199" s="8">
+        <v>46227</v>
+      </c>
       <c r="U199" s="6">
         <v>46168</v>
       </c>
@@ -16665,7 +16805,7 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>252</v>
@@ -16749,7 +16889,7 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>248</v>
@@ -16791,7 +16931,7 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>235</v>
@@ -16833,7 +16973,7 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>237</v>
@@ -16917,7 +17057,7 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>237</v>
@@ -16995,7 +17135,7 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>254</v>
@@ -17037,7 +17177,7 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>250</v>
@@ -17079,7 +17219,7 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>252</v>
@@ -17137,7 +17277,7 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>254</v>
@@ -17207,7 +17347,7 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>241</v>
@@ -17291,7 +17431,7 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>238</v>
@@ -17333,7 +17473,7 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>239</v>
@@ -17375,7 +17515,7 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>251</v>
@@ -17417,7 +17557,7 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>262</v>
@@ -17459,7 +17599,7 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>244</v>
@@ -17537,7 +17677,7 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>251</v>
@@ -17579,7 +17719,7 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>256</v>
@@ -17663,13 +17803,13 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D217" s="1">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E217" s="8">
         <v>46156</v>
@@ -17721,12 +17861,22 @@
       <c r="V217" s="8">
         <v>46177</v>
       </c>
-      <c r="W217" s="6"/>
-      <c r="X217" s="6"/>
-      <c r="Y217" s="6"/>
-      <c r="Z217" s="6"/>
+      <c r="W217" s="8">
+        <v>46229</v>
+      </c>
+      <c r="X217" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Y217" s="8">
+        <v>46229</v>
+      </c>
+      <c r="Z217" s="8">
+        <v>46229</v>
+      </c>
       <c r="AA217" s="6"/>
-      <c r="AB217" s="6"/>
+      <c r="AB217" s="8">
+        <v>46229</v>
+      </c>
       <c r="AC217" s="6"/>
       <c r="AD217" s="6"/>
       <c r="AE217" s="6"/>

--- a/Matar Trainings.xlsx
+++ b/Matar Trainings.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.karuru\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3D27E1-0404-4E48-A55D-819364E01357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075510EF-AA94-422A-A3A4-87502DD7A059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="408" windowWidth="25416" windowHeight="15252" activeTab="1" xr2:uid="{2ACD8935-9A55-49F4-8AD3-9F8021E2249D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2ACD8935-9A55-49F4-8AD3-9F8021E2249D}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta Data" sheetId="1" r:id="rId1"/>
     <sheet name="Cargo Matar SOPS" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cargo Matar SOPS'!$A$1:$AF$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cargo Matar SOPS'!$A$1:$AB$217</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Meta Data'!$A$1:$E$217</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="499">
   <si>
     <t>Emp. No.</t>
   </si>
@@ -875,6 +875,9 @@
   </si>
   <si>
     <t>CS INPUT AND OUTPUT CONVEYOR</t>
+  </si>
+  <si>
+    <t>CS TRANSFER DECK</t>
   </si>
   <si>
     <t>Norbert Mueller</t>
@@ -2042,13 +2045,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>233</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -2062,7 +2065,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>234</v>
@@ -2082,7 +2085,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>235</v>
@@ -2102,13 +2105,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>220</v>
@@ -2124,13 +2127,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>220</v>
@@ -2146,7 +2149,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>238</v>
@@ -2166,13 +2169,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>220</v>
@@ -2188,13 +2191,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>220</v>
@@ -2210,7 +2213,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>235</v>
@@ -2230,13 +2233,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>220</v>
@@ -2252,13 +2255,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2272,7 +2275,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>234</v>
@@ -2292,13 +2295,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>220</v>
@@ -2314,13 +2317,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>220</v>
@@ -2336,7 +2339,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>242</v>
@@ -2356,13 +2359,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>220</v>
@@ -2378,13 +2381,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>220</v>
@@ -2400,13 +2403,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>220</v>
@@ -2422,13 +2425,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>220</v>
@@ -2444,13 +2447,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>220</v>
@@ -2466,7 +2469,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>245</v>
@@ -2486,7 +2489,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>242</v>
@@ -2506,13 +2509,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>220</v>
@@ -2528,13 +2531,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>220</v>
@@ -2550,7 +2553,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>242</v>
@@ -2570,7 +2573,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>234</v>
@@ -2590,7 +2593,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>242</v>
@@ -2610,13 +2613,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>220</v>
@@ -2632,7 +2635,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>234</v>
@@ -2652,13 +2655,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>220</v>
@@ -2674,7 +2677,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>234</v>
@@ -2694,7 +2697,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>246</v>
@@ -2714,7 +2717,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>246</v>
@@ -2734,13 +2737,13 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>220</v>
@@ -2756,13 +2759,13 @@
         <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>220</v>
@@ -2778,7 +2781,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>248</v>
@@ -2798,13 +2801,13 @@
         <v>40</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>220</v>
@@ -2820,7 +2823,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>242</v>
@@ -2840,13 +2843,13 @@
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>220</v>
@@ -2862,13 +2865,13 @@
         <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>220</v>
@@ -2884,7 +2887,7 @@
         <v>44</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>234</v>
@@ -2904,7 +2907,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>242</v>
@@ -2924,7 +2927,7 @@
         <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>249</v>
@@ -2944,7 +2947,7 @@
         <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>246</v>
@@ -2964,7 +2967,7 @@
         <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>250</v>
@@ -2984,7 +2987,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>250</v>
@@ -3004,7 +3007,7 @@
         <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>235</v>
@@ -3024,7 +3027,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>250</v>
@@ -3044,7 +3047,7 @@
         <v>52</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>235</v>
@@ -3064,7 +3067,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>249</v>
@@ -3084,7 +3087,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>250</v>
@@ -3104,7 +3107,7 @@
         <v>55</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>251</v>
@@ -3124,13 +3127,13 @@
         <v>56</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>220</v>
@@ -3146,13 +3149,13 @@
         <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>233</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -3166,7 +3169,7 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>238</v>
@@ -3186,13 +3189,13 @@
         <v>59</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>220</v>
@@ -3208,13 +3211,13 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>220</v>
@@ -3230,13 +3233,13 @@
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>220</v>
@@ -3252,13 +3255,13 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>220</v>
@@ -3274,7 +3277,7 @@
         <v>63</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>245</v>
@@ -3294,7 +3297,7 @@
         <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>242</v>
@@ -3314,13 +3317,13 @@
         <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>220</v>
@@ -3336,13 +3339,13 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>220</v>
@@ -3358,7 +3361,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>245</v>
@@ -3378,7 +3381,7 @@
         <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>234</v>
@@ -3398,7 +3401,7 @@
         <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>235</v>
@@ -3418,7 +3421,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>251</v>
@@ -3438,7 +3441,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>245</v>
@@ -3458,7 +3461,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>251</v>
@@ -3478,13 +3481,13 @@
         <v>73</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>220</v>
@@ -3500,7 +3503,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>250</v>
@@ -3520,7 +3523,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>253</v>
@@ -3540,13 +3543,13 @@
         <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>220</v>
@@ -3562,7 +3565,7 @@
         <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>245</v>
@@ -3582,13 +3585,13 @@
         <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>220</v>
@@ -3604,13 +3607,13 @@
         <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>220</v>
@@ -3626,13 +3629,13 @@
         <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>220</v>
@@ -3648,7 +3651,7 @@
         <v>81</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>234</v>
@@ -3668,13 +3671,13 @@
         <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>220</v>
@@ -3690,13 +3693,13 @@
         <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>220</v>
@@ -3712,7 +3715,7 @@
         <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>253</v>
@@ -3732,13 +3735,13 @@
         <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -3752,7 +3755,7 @@
         <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>235</v>
@@ -3772,7 +3775,7 @@
         <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>234</v>
@@ -3792,7 +3795,7 @@
         <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>234</v>
@@ -3812,7 +3815,7 @@
         <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>251</v>
@@ -3832,7 +3835,7 @@
         <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>242</v>
@@ -3852,7 +3855,7 @@
         <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>242</v>
@@ -3872,13 +3875,13 @@
         <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>220</v>
@@ -3894,7 +3897,7 @@
         <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>235</v>
@@ -3914,13 +3917,13 @@
         <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>220</v>
@@ -3936,7 +3939,7 @@
         <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>235</v>
@@ -3956,7 +3959,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>234</v>
@@ -3976,7 +3979,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>255</v>
@@ -3996,7 +3999,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>249</v>
@@ -4016,7 +4019,7 @@
         <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>245</v>
@@ -4036,7 +4039,7 @@
         <v>100</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>250</v>
@@ -4056,7 +4059,7 @@
         <v>101</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>234</v>
@@ -4076,7 +4079,7 @@
         <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>240</v>
@@ -4096,13 +4099,13 @@
         <v>103</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>220</v>
@@ -4118,7 +4121,7 @@
         <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>241</v>
@@ -4138,13 +4141,13 @@
         <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>220</v>
@@ -4160,7 +4163,7 @@
         <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>250</v>
@@ -4180,7 +4183,7 @@
         <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>234</v>
@@ -4200,13 +4203,13 @@
         <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>220</v>
@@ -4222,7 +4225,7 @@
         <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>241</v>
@@ -4244,13 +4247,13 @@
         <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>220</v>
@@ -4266,13 +4269,13 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>220</v>
@@ -4288,7 +4291,7 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>235</v>
@@ -4308,7 +4311,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>234</v>
@@ -4328,13 +4331,13 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
@@ -4348,13 +4351,13 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
@@ -4368,7 +4371,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>242</v>
@@ -4388,13 +4391,13 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>220</v>
@@ -4410,7 +4413,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>257</v>
@@ -4430,7 +4433,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>249</v>
@@ -4450,7 +4453,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>246</v>
@@ -4470,7 +4473,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>248</v>
@@ -4490,7 +4493,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>257</v>
@@ -4510,13 +4513,13 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>220</v>
@@ -4532,7 +4535,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>253</v>
@@ -4552,13 +4555,13 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>258</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>220</v>
@@ -4574,7 +4577,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>258</v>
@@ -4594,7 +4597,7 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>253</v>
@@ -4614,13 +4617,13 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>220</v>
@@ -4636,7 +4639,7 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>242</v>
@@ -4656,13 +4659,13 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -4676,13 +4679,13 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>238</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -4696,7 +4699,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>259</v>
@@ -4716,13 +4719,13 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -4736,13 +4739,13 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>220</v>
@@ -4758,7 +4761,7 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>242</v>
@@ -4778,7 +4781,7 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>253</v>
@@ -4798,13 +4801,13 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>220</v>
@@ -4820,7 +4823,7 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>235</v>
@@ -4840,13 +4843,13 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>220</v>
@@ -4862,7 +4865,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>245</v>
@@ -4882,13 +4885,13 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>220</v>
@@ -4904,7 +4907,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>235</v>
@@ -4924,7 +4927,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>249</v>
@@ -4944,7 +4947,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>245</v>
@@ -4964,7 +4967,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -4984,13 +4987,13 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>220</v>
@@ -5006,7 +5009,7 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>245</v>
@@ -5026,7 +5029,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>245</v>
@@ -5046,7 +5049,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>245</v>
@@ -5066,7 +5069,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>243</v>
@@ -5086,13 +5089,13 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>220</v>
@@ -5108,7 +5111,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>249</v>
@@ -5128,13 +5131,13 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>220</v>
@@ -5150,7 +5153,7 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>242</v>
@@ -5172,13 +5175,13 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
@@ -5192,13 +5195,13 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
@@ -5212,13 +5215,13 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>220</v>
@@ -5234,13 +5237,13 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>220</v>
@@ -5256,7 +5259,7 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>257</v>
@@ -5276,7 +5279,7 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>242</v>
@@ -5298,13 +5301,13 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>220</v>
@@ -5320,13 +5323,13 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>220</v>
@@ -5342,13 +5345,13 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>220</v>
@@ -5364,7 +5367,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>250</v>
@@ -5384,7 +5387,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>253</v>
@@ -5404,7 +5407,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>256</v>
@@ -5426,7 +5429,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>242</v>
@@ -5446,7 +5449,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>235</v>
@@ -5466,7 +5469,7 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>256</v>
@@ -5486,7 +5489,7 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>242</v>
@@ -5506,7 +5509,7 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>253</v>
@@ -5526,7 +5529,7 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>235</v>
@@ -5546,7 +5549,7 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>240</v>
@@ -5568,13 +5571,13 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -5588,7 +5591,7 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>235</v>
@@ -5608,13 +5611,13 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>260</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
@@ -5628,7 +5631,7 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>245</v>
@@ -5648,7 +5651,7 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>245</v>
@@ -5668,13 +5671,13 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>220</v>
@@ -5690,7 +5693,7 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>247</v>
@@ -5710,13 +5713,13 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>220</v>
@@ -5732,13 +5735,13 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>220</v>
@@ -5754,13 +5757,13 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>220</v>
@@ -5776,13 +5779,13 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
@@ -5796,13 +5799,13 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
@@ -5816,7 +5819,7 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>239</v>
@@ -5838,13 +5841,13 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>261</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
@@ -5858,7 +5861,7 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>249</v>
@@ -5878,13 +5881,13 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>220</v>
@@ -5900,13 +5903,13 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>220</v>
@@ -5922,7 +5925,7 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>262</v>
@@ -5942,7 +5945,7 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>263</v>
@@ -5962,13 +5965,13 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>220</v>
@@ -5984,13 +5987,13 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>220</v>
@@ -6006,13 +6009,13 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>220</v>
@@ -6028,13 +6031,13 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>254</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>220</v>
@@ -6050,7 +6053,7 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>235</v>
@@ -6070,7 +6073,7 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>254</v>
@@ -6092,7 +6095,7 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>235</v>
@@ -6112,7 +6115,7 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>250</v>
@@ -6132,13 +6135,13 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>220</v>
@@ -6154,13 +6157,13 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>220</v>
@@ -6176,7 +6179,7 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>248</v>
@@ -6196,7 +6199,7 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>235</v>
@@ -6216,13 +6219,13 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>220</v>
@@ -6238,13 +6241,13 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>220</v>
@@ -6260,7 +6263,7 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>254</v>
@@ -6282,7 +6285,7 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>250</v>
@@ -6302,13 +6305,13 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>220</v>
@@ -6324,13 +6327,13 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>254</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>220</v>
@@ -6346,13 +6349,13 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>220</v>
@@ -6368,13 +6371,13 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>238</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
@@ -6388,13 +6391,13 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
@@ -6408,7 +6411,7 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>251</v>
@@ -6428,7 +6431,7 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>262</v>
@@ -6448,13 +6451,13 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>220</v>
@@ -6470,7 +6473,7 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>251</v>
@@ -6490,13 +6493,13 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>220</v>
@@ -6512,13 +6515,13 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>220</v>
@@ -6560,8 +6563,10 @@
     <col min="23" max="23" width="10.44140625" customWidth="1"/>
     <col min="24" max="24" width="11" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="12.44140625" customWidth="1"/>
+    <col min="26" max="26" width="10.109375" customWidth="1"/>
     <col min="27" max="27" width="11" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.88671875" customWidth="1"/>
+    <col min="29" max="29" width="11.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="57.6" x14ac:dyDescent="0.3">
@@ -6649,7 +6654,9 @@
       <c r="AB1" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="AC1" s="7"/>
+      <c r="AC1" s="7" t="s">
+        <v>277</v>
+      </c>
       <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
@@ -6659,7 +6666,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>233</v>
@@ -6701,7 +6708,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>234</v>
@@ -6743,7 +6750,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>235</v>
@@ -6785,7 +6792,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>236</v>
@@ -6827,7 +6834,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>237</v>
@@ -6869,7 +6876,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>238</v>
@@ -6911,7 +6918,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>239</v>
@@ -6953,7 +6960,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>240</v>
@@ -6995,7 +7002,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>235</v>
@@ -7037,7 +7044,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>239</v>
@@ -7079,7 +7086,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>239</v>
@@ -7121,7 +7128,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>234</v>
@@ -7163,7 +7170,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>241</v>
@@ -7205,7 +7212,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>239</v>
@@ -7247,7 +7254,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>242</v>
@@ -7289,7 +7296,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>243</v>
@@ -7331,7 +7338,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>244</v>
@@ -7373,13 +7380,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D19" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E19" s="8">
         <v>46212</v>
@@ -7435,21 +7442,27 @@
       <c r="V19" s="8">
         <v>46173</v>
       </c>
-      <c r="W19" s="6"/>
+      <c r="W19" s="10">
+        <v>46247</v>
+      </c>
       <c r="X19" s="9">
         <v>46194</v>
       </c>
       <c r="Y19" s="9">
         <v>46194</v>
       </c>
-      <c r="Z19" s="6"/>
+      <c r="Z19" s="10">
+        <v>46247</v>
+      </c>
       <c r="AA19" s="8">
         <v>46166</v>
       </c>
       <c r="AB19" s="8">
         <v>46168</v>
       </c>
-      <c r="AC19" s="6"/>
+      <c r="AC19" s="10">
+        <v>46247</v>
+      </c>
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
@@ -7459,7 +7472,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>243</v>
@@ -7537,13 +7550,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D21" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E21" s="8">
         <v>46212</v>
@@ -7599,17 +7612,23 @@
       <c r="V21" s="8">
         <v>46171</v>
       </c>
-      <c r="W21" s="6"/>
+      <c r="W21" s="10">
+        <v>46247</v>
+      </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="6"/>
-      <c r="Z21" s="6"/>
+      <c r="Z21" s="10">
+        <v>46247</v>
+      </c>
       <c r="AA21" s="8">
         <v>46166</v>
       </c>
       <c r="AB21" s="8">
         <v>46168</v>
       </c>
-      <c r="AC21" s="6"/>
+      <c r="AC21" s="10">
+        <v>46247</v>
+      </c>
       <c r="AD21" s="6"/>
       <c r="AE21" s="6"/>
       <c r="AF21" s="6"/>
@@ -7619,7 +7638,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>245</v>
@@ -7661,7 +7680,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>242</v>
@@ -7703,7 +7722,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>240</v>
@@ -7745,7 +7764,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>237</v>
@@ -7829,7 +7848,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>242</v>
@@ -7871,7 +7890,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>234</v>
@@ -7913,7 +7932,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>242</v>
@@ -7955,13 +7974,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D29" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -8005,17 +8024,23 @@
       <c r="V29" s="8">
         <v>46171</v>
       </c>
-      <c r="W29" s="6"/>
+      <c r="W29" s="10">
+        <v>46247</v>
+      </c>
       <c r="X29" s="6"/>
       <c r="Y29" s="6"/>
-      <c r="Z29" s="6"/>
+      <c r="Z29" s="10">
+        <v>46247</v>
+      </c>
       <c r="AA29" s="8">
         <v>46166</v>
       </c>
       <c r="AB29" s="8">
         <v>46168</v>
       </c>
-      <c r="AC29" s="6"/>
+      <c r="AC29" s="10">
+        <v>46247</v>
+      </c>
       <c r="AD29" s="6"/>
       <c r="AE29" s="6"/>
       <c r="AF29" s="6"/>
@@ -8025,7 +8050,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>234</v>
@@ -8067,13 +8092,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D31" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E31" s="8">
         <v>46181</v>
@@ -8084,8 +8109,12 @@
       <c r="G31" s="8">
         <v>46181</v>
       </c>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
+      <c r="H31" s="8">
+        <v>46238</v>
+      </c>
+      <c r="I31" s="8">
+        <v>46239</v>
+      </c>
       <c r="J31" s="8">
         <v>46178</v>
       </c>
@@ -8141,7 +8170,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>234</v>
@@ -8183,7 +8212,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>246</v>
@@ -8225,7 +8254,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>246</v>
@@ -8267,7 +8296,7 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>243</v>
@@ -8353,7 +8382,7 @@
         <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>247</v>
@@ -8437,7 +8466,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>248</v>
@@ -8479,7 +8508,7 @@
         <v>40</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>240</v>
@@ -8529,7 +8558,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>242</v>
@@ -8571,7 +8600,7 @@
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>241</v>
@@ -8655,7 +8684,7 @@
         <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>241</v>
@@ -8739,7 +8768,7 @@
         <v>44</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>234</v>
@@ -8781,7 +8810,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>242</v>
@@ -8823,7 +8852,7 @@
         <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>249</v>
@@ -8865,7 +8894,7 @@
         <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>246</v>
@@ -8907,7 +8936,7 @@
         <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>250</v>
@@ -8949,7 +8978,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>250</v>
@@ -8991,7 +9020,7 @@
         <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>235</v>
@@ -9033,7 +9062,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>250</v>
@@ -9075,7 +9104,7 @@
         <v>52</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>235</v>
@@ -9117,7 +9146,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>249</v>
@@ -9159,7 +9188,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>250</v>
@@ -9201,7 +9230,7 @@
         <v>55</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>251</v>
@@ -9243,7 +9272,7 @@
         <v>56</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>239</v>
@@ -9285,7 +9314,7 @@
         <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>233</v>
@@ -9327,7 +9356,7 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>238</v>
@@ -9369,7 +9398,7 @@
         <v>59</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>252</v>
@@ -9453,7 +9482,7 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>241</v>
@@ -9537,7 +9566,7 @@
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>241</v>
@@ -9579,13 +9608,13 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D60" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
@@ -9594,7 +9623,9 @@
       <c r="I60" s="10">
         <v>46197</v>
       </c>
-      <c r="J60" s="10"/>
+      <c r="J60" s="10">
+        <v>46237</v>
+      </c>
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
       <c r="M60" s="8">
@@ -9637,7 +9668,7 @@
         <v>63</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>245</v>
@@ -9679,7 +9710,7 @@
         <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>242</v>
@@ -9721,7 +9752,7 @@
         <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>244</v>
@@ -9791,13 +9822,13 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D64" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E64" s="8">
         <v>46181</v>
@@ -9808,8 +9839,12 @@
       <c r="G64" s="8">
         <v>46181</v>
       </c>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
+      <c r="H64" s="8">
+        <v>46238</v>
+      </c>
+      <c r="I64" s="8">
+        <v>46239</v>
+      </c>
       <c r="J64" s="8">
         <v>46178</v>
       </c>
@@ -9853,7 +9888,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>245</v>
@@ -9895,7 +9930,7 @@
         <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>234</v>
@@ -9937,7 +9972,7 @@
         <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>235</v>
@@ -9979,7 +10014,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>251</v>
@@ -10021,7 +10056,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>245</v>
@@ -10063,7 +10098,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>251</v>
@@ -10105,7 +10140,7 @@
         <v>73</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>247</v>
@@ -10189,7 +10224,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>250</v>
@@ -10231,7 +10266,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>253</v>
@@ -10273,13 +10308,13 @@
         <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D74" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E74" s="8">
         <v>46212</v>
@@ -10335,21 +10370,27 @@
       <c r="V74" s="8">
         <v>46171</v>
       </c>
-      <c r="W74" s="6"/>
+      <c r="W74" s="10">
+        <v>46247</v>
+      </c>
       <c r="X74" s="9">
         <v>46194</v>
       </c>
       <c r="Y74" s="9">
         <v>46194</v>
       </c>
-      <c r="Z74" s="6"/>
+      <c r="Z74" s="10">
+        <v>46247</v>
+      </c>
       <c r="AA74" s="8">
         <v>46166</v>
       </c>
       <c r="AB74" s="8">
         <v>46168</v>
       </c>
-      <c r="AC74" s="6"/>
+      <c r="AC74" s="10">
+        <v>46247</v>
+      </c>
       <c r="AD74" s="6"/>
       <c r="AE74" s="6"/>
       <c r="AF74" s="6"/>
@@ -10359,7 +10400,7 @@
         <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>245</v>
@@ -10401,7 +10442,7 @@
         <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>241</v>
@@ -10485,7 +10526,7 @@
         <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>252</v>
@@ -10569,7 +10610,7 @@
         <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>256</v>
@@ -10653,7 +10694,7 @@
         <v>81</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>234</v>
@@ -10695,13 +10736,13 @@
         <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D80" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -10710,7 +10751,9 @@
       <c r="I80" s="10">
         <v>46197</v>
       </c>
-      <c r="J80" s="10"/>
+      <c r="J80" s="10">
+        <v>46237</v>
+      </c>
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
       <c r="M80" s="8">
@@ -10753,13 +10796,13 @@
         <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D81" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
@@ -10768,7 +10811,9 @@
       <c r="I81" s="10">
         <v>46197</v>
       </c>
-      <c r="J81" s="10"/>
+      <c r="J81" s="10">
+        <v>46237</v>
+      </c>
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
       <c r="M81" s="8">
@@ -10811,7 +10856,7 @@
         <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>253</v>
@@ -10853,7 +10898,7 @@
         <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>239</v>
@@ -10895,7 +10940,7 @@
         <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>235</v>
@@ -10937,7 +10982,7 @@
         <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>234</v>
@@ -10979,7 +11024,7 @@
         <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>234</v>
@@ -11021,7 +11066,7 @@
         <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>251</v>
@@ -11063,7 +11108,7 @@
         <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>242</v>
@@ -11105,7 +11150,7 @@
         <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>242</v>
@@ -11147,13 +11192,13 @@
         <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D90" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E90" s="8">
         <v>46212</v>
@@ -11209,21 +11254,27 @@
       <c r="V90" s="8">
         <v>46171</v>
       </c>
-      <c r="W90" s="6"/>
+      <c r="W90" s="10">
+        <v>46247</v>
+      </c>
       <c r="X90" s="9">
         <v>46194</v>
       </c>
       <c r="Y90" s="9">
         <v>46194</v>
       </c>
-      <c r="Z90" s="6"/>
+      <c r="Z90" s="10">
+        <v>46247</v>
+      </c>
       <c r="AA90" s="8">
         <v>46166</v>
       </c>
       <c r="AB90" s="8">
         <v>46168</v>
       </c>
-      <c r="AC90" s="6"/>
+      <c r="AC90" s="10">
+        <v>46247</v>
+      </c>
       <c r="AD90" s="6"/>
       <c r="AE90" s="6"/>
       <c r="AF90" s="6"/>
@@ -11233,7 +11284,7 @@
         <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>235</v>
@@ -11275,7 +11326,7 @@
         <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>237</v>
@@ -11339,7 +11390,7 @@
         <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>235</v>
@@ -11381,7 +11432,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>234</v>
@@ -11423,7 +11474,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>255</v>
@@ -11465,7 +11516,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>249</v>
@@ -11507,7 +11558,7 @@
         <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>245</v>
@@ -11549,7 +11600,7 @@
         <v>100</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>250</v>
@@ -11591,7 +11642,7 @@
         <v>101</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>234</v>
@@ -11633,13 +11684,13 @@
         <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D100" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
@@ -11648,7 +11699,9 @@
       <c r="I100" s="8">
         <v>46227</v>
       </c>
-      <c r="J100" s="6"/>
+      <c r="J100" s="10">
+        <v>46237</v>
+      </c>
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
       <c r="M100" s="8">
@@ -11691,7 +11744,7 @@
         <v>103</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>256</v>
@@ -11767,7 +11820,7 @@
         <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>241</v>
@@ -11809,13 +11862,13 @@
         <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D103" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E103" s="8">
         <v>46212</v>
@@ -11871,21 +11924,27 @@
       <c r="V103" s="8">
         <v>46171</v>
       </c>
-      <c r="W103" s="6"/>
+      <c r="W103" s="10">
+        <v>46247</v>
+      </c>
       <c r="X103" s="9">
         <v>46194</v>
       </c>
       <c r="Y103" s="9">
         <v>46194</v>
       </c>
-      <c r="Z103" s="6"/>
+      <c r="Z103" s="10">
+        <v>46247</v>
+      </c>
       <c r="AA103" s="8">
         <v>46166</v>
       </c>
       <c r="AB103" s="8">
         <v>46168</v>
       </c>
-      <c r="AC103" s="6"/>
+      <c r="AC103" s="10">
+        <v>46247</v>
+      </c>
       <c r="AD103" s="6"/>
       <c r="AE103" s="6"/>
       <c r="AF103" s="6"/>
@@ -11895,7 +11954,7 @@
         <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>250</v>
@@ -11937,7 +11996,7 @@
         <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>234</v>
@@ -11979,13 +12038,13 @@
         <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D106" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -12033,21 +12092,27 @@
       <c r="V106" s="8">
         <v>46171</v>
       </c>
-      <c r="W106" s="6"/>
+      <c r="W106" s="10">
+        <v>46247</v>
+      </c>
       <c r="X106" s="9">
         <v>46194</v>
       </c>
       <c r="Y106" s="9">
         <v>46194</v>
       </c>
-      <c r="Z106" s="6"/>
+      <c r="Z106" s="10">
+        <v>46247</v>
+      </c>
       <c r="AA106" s="8">
         <v>46166</v>
       </c>
       <c r="AB106" s="8">
         <v>46168</v>
       </c>
-      <c r="AC106" s="6"/>
+      <c r="AC106" s="10">
+        <v>46247</v>
+      </c>
       <c r="AD106" s="6"/>
       <c r="AE106" s="6"/>
       <c r="AF106" s="6"/>
@@ -12057,7 +12122,7 @@
         <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>241</v>
@@ -12099,7 +12164,7 @@
         <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>240</v>
@@ -12149,7 +12214,7 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>237</v>
@@ -12233,7 +12298,7 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>235</v>
@@ -12275,7 +12340,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>234</v>
@@ -12317,7 +12382,7 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>239</v>
@@ -12359,7 +12424,7 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>239</v>
@@ -12401,7 +12466,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>242</v>
@@ -12443,7 +12508,7 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>247</v>
@@ -12527,7 +12592,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>257</v>
@@ -12569,7 +12634,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>249</v>
@@ -12611,7 +12676,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>246</v>
@@ -12653,7 +12718,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>248</v>
@@ -12695,7 +12760,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>257</v>
@@ -12737,7 +12802,7 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>243</v>
@@ -12815,7 +12880,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>253</v>
@@ -12857,7 +12922,7 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>258</v>
@@ -12899,7 +12964,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>258</v>
@@ -12941,7 +13006,7 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>253</v>
@@ -12983,7 +13048,7 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>244</v>
@@ -13063,7 +13128,7 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>242</v>
@@ -13105,7 +13170,7 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>239</v>
@@ -13147,7 +13212,7 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>238</v>
@@ -13189,7 +13254,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>259</v>
@@ -13231,7 +13296,7 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>239</v>
@@ -13273,7 +13338,7 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>241</v>
@@ -13357,7 +13422,7 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>242</v>
@@ -13399,7 +13464,7 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>253</v>
@@ -13441,13 +13506,13 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D135" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -13456,7 +13521,9 @@
       <c r="I135" s="10">
         <v>46197</v>
       </c>
-      <c r="J135" s="10"/>
+      <c r="J135" s="10">
+        <v>46237</v>
+      </c>
       <c r="K135" s="6"/>
       <c r="L135" s="6"/>
       <c r="M135" s="8">
@@ -13499,7 +13566,7 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>235</v>
@@ -13541,7 +13608,7 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>252</v>
@@ -13619,7 +13686,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>245</v>
@@ -13661,7 +13728,7 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>256</v>
@@ -13745,7 +13812,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>235</v>
@@ -13787,7 +13854,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>249</v>
@@ -13829,7 +13896,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>245</v>
@@ -13871,7 +13938,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -13913,7 +13980,7 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>237</v>
@@ -13997,7 +14064,7 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>245</v>
@@ -14039,7 +14106,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>245</v>
@@ -14081,7 +14148,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>245</v>
@@ -14123,7 +14190,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>243</v>
@@ -14165,7 +14232,7 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>243</v>
@@ -14249,7 +14316,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>249</v>
@@ -14291,7 +14358,7 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>252</v>
@@ -14359,7 +14426,7 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>242</v>
@@ -14401,7 +14468,7 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>239</v>
@@ -14443,7 +14510,7 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>239</v>
@@ -14485,7 +14552,7 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>247</v>
@@ -14549,7 +14616,7 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>252</v>
@@ -14591,7 +14658,7 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>257</v>
@@ -14633,7 +14700,7 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>242</v>
@@ -14675,7 +14742,7 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>247</v>
@@ -14757,7 +14824,7 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>239</v>
@@ -14799,7 +14866,7 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>244</v>
@@ -14879,7 +14946,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>250</v>
@@ -14921,7 +14988,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>253</v>
@@ -14963,7 +15030,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>256</v>
@@ -15005,7 +15072,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>242</v>
@@ -15047,7 +15114,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>235</v>
@@ -15089,7 +15156,7 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>256</v>
@@ -15131,7 +15198,7 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>242</v>
@@ -15173,7 +15240,7 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>253</v>
@@ -15215,7 +15282,7 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>235</v>
@@ -15257,7 +15324,7 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>240</v>
@@ -15299,7 +15366,7 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>239</v>
@@ -15341,7 +15408,7 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>235</v>
@@ -15383,7 +15450,7 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>260</v>
@@ -15425,7 +15492,7 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>245</v>
@@ -15467,7 +15534,7 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>245</v>
@@ -15509,7 +15576,7 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>243</v>
@@ -15595,7 +15662,7 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>247</v>
@@ -15637,7 +15704,7 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>243</v>
@@ -15707,7 +15774,7 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>252</v>
@@ -15785,7 +15852,7 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>256</v>
@@ -15857,7 +15924,7 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>239</v>
@@ -15899,7 +15966,7 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>250</v>
@@ -15941,7 +16008,7 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>239</v>
@@ -15983,7 +16050,7 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>261</v>
@@ -16025,7 +16092,7 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>249</v>
@@ -16067,7 +16134,7 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>239</v>
@@ -16109,7 +16176,7 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>244</v>
@@ -16189,7 +16256,7 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>262</v>
@@ -16231,7 +16298,7 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>263</v>
@@ -16273,7 +16340,7 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>241</v>
@@ -16357,7 +16424,7 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>244</v>
@@ -16437,7 +16504,7 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>237</v>
@@ -16509,7 +16576,7 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>254</v>
@@ -16551,7 +16618,7 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>235</v>
@@ -16593,7 +16660,7 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>254</v>
@@ -16635,7 +16702,7 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>235</v>
@@ -16677,7 +16744,7 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>250</v>
@@ -16719,13 +16786,13 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D199" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E199" s="8">
         <v>46212</v>
@@ -16781,21 +16848,27 @@
       <c r="V199" s="8">
         <v>46171</v>
       </c>
-      <c r="W199" s="6"/>
+      <c r="W199" s="10">
+        <v>46247</v>
+      </c>
       <c r="X199" s="9">
         <v>46194</v>
       </c>
       <c r="Y199" s="9">
         <v>46194</v>
       </c>
-      <c r="Z199" s="6"/>
+      <c r="Z199" s="10">
+        <v>46247</v>
+      </c>
       <c r="AA199" s="8">
         <v>46166</v>
       </c>
       <c r="AB199" s="8">
         <v>46168</v>
       </c>
-      <c r="AC199" s="6"/>
+      <c r="AC199" s="10">
+        <v>46247</v>
+      </c>
       <c r="AD199" s="6"/>
       <c r="AE199" s="6"/>
       <c r="AF199" s="6"/>
@@ -16805,7 +16878,7 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>252</v>
@@ -16889,7 +16962,7 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>248</v>
@@ -16931,7 +17004,7 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>235</v>
@@ -16973,7 +17046,7 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>237</v>
@@ -17057,7 +17130,7 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>237</v>
@@ -17135,7 +17208,7 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>254</v>
@@ -17177,7 +17250,7 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>250</v>
@@ -17219,7 +17292,7 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>252</v>
@@ -17277,7 +17350,7 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>254</v>
@@ -17347,7 +17420,7 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>241</v>
@@ -17431,7 +17504,7 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>238</v>
@@ -17473,7 +17546,7 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>239</v>
@@ -17515,7 +17588,7 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>251</v>
@@ -17557,7 +17630,7 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>262</v>
@@ -17599,7 +17672,7 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>244</v>
@@ -17677,7 +17750,7 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>251</v>
@@ -17719,7 +17792,7 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>256</v>
@@ -17803,7 +17876,7 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>256</v>

--- a/Matar Trainings.xlsx
+++ b/Matar Trainings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.karuru\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075510EF-AA94-422A-A3A4-87502DD7A059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DFFECE-210E-460F-86D9-350BFB8651EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2ACD8935-9A55-49F4-8AD3-9F8021E2249D}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="Cargo Matar SOPS" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cargo Matar SOPS'!$A$1:$AB$217</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Meta Data'!$A$1:$E$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cargo Matar SOPS'!$A$1:$AC$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Meta Data'!$A$1:$E$229</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="512">
   <si>
     <t>Emp. No.</t>
   </si>
@@ -706,6 +706,42 @@
     <t>Q0629</t>
   </si>
   <si>
+    <t>Q0630</t>
+  </si>
+  <si>
+    <t>Q0631</t>
+  </si>
+  <si>
+    <t>Q0632</t>
+  </si>
+  <si>
+    <t>Q0633</t>
+  </si>
+  <si>
+    <t>Q0634</t>
+  </si>
+  <si>
+    <t>Q0635</t>
+  </si>
+  <si>
+    <t>Q0636</t>
+  </si>
+  <si>
+    <t>Q0637</t>
+  </si>
+  <si>
+    <t>Q0638</t>
+  </si>
+  <si>
+    <t>Q0639</t>
+  </si>
+  <si>
+    <t>Q0640</t>
+  </si>
+  <si>
+    <t>Q0641</t>
+  </si>
+  <si>
     <t>Cargo</t>
   </si>
   <si>
@@ -883,6 +919,9 @@
     <t>Norbert Mueller</t>
   </si>
   <si>
+    <t>Management</t>
+  </si>
+  <si>
     <t>Mohamed Farkan Mohamed Sareek</t>
   </si>
   <si>
@@ -892,6 +931,9 @@
     <t>Abdunaser Ahmed Aragaw</t>
   </si>
   <si>
+    <t>CARGO CM</t>
+  </si>
+  <si>
     <t>Rizardo Villalobos</t>
   </si>
   <si>
@@ -901,6 +943,9 @@
     <t xml:space="preserve">Mahesh Ramachandra </t>
   </si>
   <si>
+    <t>CARGO PM</t>
+  </si>
+  <si>
     <t>Joel Cabrillos Misa</t>
   </si>
   <si>
@@ -1126,6 +1171,9 @@
     <t>Sooraj Kurisinkal Reji</t>
   </si>
   <si>
+    <t>IT/PLC</t>
+  </si>
+  <si>
     <t>Jose Isagani Jr. Jamero Alaan</t>
   </si>
   <si>
@@ -1459,6 +1507,9 @@
     <t>Quennan Carandang Cuesta</t>
   </si>
   <si>
+    <t>U5</t>
+  </si>
+  <si>
     <t>Lester John Fuentes Monter</t>
   </si>
   <si>
@@ -1528,19 +1579,7 @@
     <t>Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
-    <t>CARGO CM</t>
-  </si>
-  <si>
-    <t>CARGO PM</t>
-  </si>
-  <si>
-    <t>IT/PLC</t>
-  </si>
-  <si>
-    <t>U5</t>
+    <t>Jerusha Anns Philip</t>
   </si>
 </sst>
 </file>
@@ -1993,7 +2032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC757972-15C5-427C-AB07-EDA7DBD0B6ED}">
-  <dimension ref="A1:AC217"/>
+  <dimension ref="A1:AC229"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.5546875" customWidth="1"/>
@@ -2045,13 +2084,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>494</v>
+        <v>291</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -2065,13 +2104,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -2085,13 +2124,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -2105,16 +2144,16 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -2127,16 +2166,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -2149,13 +2188,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -2169,16 +2208,16 @@
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -2191,16 +2230,16 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -2213,13 +2252,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -2233,16 +2272,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -2255,13 +2294,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>494</v>
+        <v>291</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2275,13 +2314,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -2295,16 +2334,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -2317,16 +2356,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -2339,13 +2378,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -2359,16 +2398,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -2381,16 +2420,16 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -2403,16 +2442,16 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -2425,16 +2464,16 @@
         <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -2447,16 +2486,16 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -2469,13 +2508,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -2489,13 +2528,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -2509,16 +2548,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -2531,16 +2570,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -2553,13 +2592,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -2573,13 +2612,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -2593,13 +2632,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -2613,16 +2652,16 @@
         <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -2635,13 +2674,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -2655,16 +2694,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -2677,13 +2716,13 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -2697,13 +2736,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -2717,13 +2756,13 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -2737,16 +2776,16 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -2759,16 +2798,16 @@
         <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -2781,13 +2820,13 @@
         <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -2801,16 +2840,16 @@
         <v>40</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -2823,13 +2862,13 @@
         <v>41</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -2843,16 +2882,16 @@
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -2865,16 +2904,16 @@
         <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -2887,13 +2926,13 @@
         <v>44</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -2907,13 +2946,13 @@
         <v>45</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -2927,13 +2966,13 @@
         <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -2947,13 +2986,13 @@
         <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -2967,13 +3006,13 @@
         <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -2987,13 +3026,13 @@
         <v>49</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -3007,13 +3046,13 @@
         <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -3027,13 +3066,13 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -3047,13 +3086,13 @@
         <v>52</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -3067,13 +3106,13 @@
         <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -3087,13 +3126,13 @@
         <v>54</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -3107,13 +3146,13 @@
         <v>55</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -3127,16 +3166,16 @@
         <v>56</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -3149,13 +3188,13 @@
         <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>494</v>
+        <v>291</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -3169,13 +3208,13 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -3189,16 +3228,16 @@
         <v>59</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -3211,16 +3250,16 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -3233,16 +3272,16 @@
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -3255,16 +3294,16 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -3277,13 +3316,13 @@
         <v>63</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -3297,13 +3336,13 @@
         <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
@@ -3317,16 +3356,16 @@
         <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -3339,16 +3378,16 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -3361,13 +3400,13 @@
         <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -3381,13 +3420,13 @@
         <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -3401,13 +3440,13 @@
         <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -3421,13 +3460,13 @@
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
@@ -3441,13 +3480,13 @@
         <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
@@ -3461,13 +3500,13 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
@@ -3481,16 +3520,16 @@
         <v>73</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -3503,13 +3542,13 @@
         <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
@@ -3523,13 +3562,13 @@
         <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -3543,16 +3582,16 @@
         <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -3565,13 +3604,13 @@
         <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -3585,16 +3624,16 @@
         <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -3607,16 +3646,16 @@
         <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -3629,16 +3668,16 @@
         <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -3651,13 +3690,13 @@
         <v>81</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
@@ -3671,16 +3710,16 @@
         <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
@@ -3693,16 +3732,16 @@
         <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
@@ -3715,13 +3754,13 @@
         <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
@@ -3735,13 +3774,13 @@
         <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -3755,13 +3794,13 @@
         <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
@@ -3775,13 +3814,13 @@
         <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -3795,13 +3834,13 @@
         <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
@@ -3815,13 +3854,13 @@
         <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
@@ -3835,13 +3874,13 @@
         <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -3855,13 +3894,13 @@
         <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
@@ -3875,16 +3914,16 @@
         <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
@@ -3897,13 +3936,13 @@
         <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
@@ -3917,16 +3956,16 @@
         <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
@@ -3939,13 +3978,13 @@
         <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
@@ -3959,13 +3998,13 @@
         <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
@@ -3979,13 +4018,13 @@
         <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
@@ -3999,13 +4038,13 @@
         <v>98</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
@@ -4019,13 +4058,13 @@
         <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -4039,13 +4078,13 @@
         <v>100</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
@@ -4059,13 +4098,13 @@
         <v>101</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
@@ -4079,13 +4118,13 @@
         <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
@@ -4099,16 +4138,16 @@
         <v>103</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
@@ -4121,13 +4160,13 @@
         <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
@@ -4141,16 +4180,16 @@
         <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
@@ -4163,13 +4202,13 @@
         <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
@@ -4183,13 +4222,13 @@
         <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
@@ -4203,16 +4242,16 @@
         <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
@@ -4225,16 +4264,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
@@ -4247,16 +4286,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
@@ -4269,16 +4308,16 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
@@ -4291,13 +4330,13 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
@@ -4311,13 +4350,13 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
@@ -4331,13 +4370,13 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
@@ -4351,13 +4390,13 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
@@ -4371,13 +4410,13 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
@@ -4391,16 +4430,16 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
@@ -4413,13 +4452,13 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
@@ -4433,13 +4472,13 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
@@ -4453,13 +4492,13 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
@@ -4473,13 +4512,13 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
@@ -4493,13 +4532,13 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
@@ -4513,16 +4552,16 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
@@ -4535,13 +4574,13 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
@@ -4555,16 +4594,16 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
@@ -4577,13 +4616,13 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
@@ -4597,13 +4636,13 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
@@ -4617,16 +4656,16 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
@@ -4639,13 +4678,13 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
@@ -4659,13 +4698,13 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -4679,13 +4718,13 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>494</v>
+        <v>291</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -4699,13 +4738,13 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
@@ -4719,13 +4758,13 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -4739,16 +4778,16 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
@@ -4761,13 +4800,13 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
@@ -4781,13 +4820,13 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
@@ -4801,16 +4840,16 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
@@ -4823,13 +4862,13 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
@@ -4843,16 +4882,16 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
@@ -4865,13 +4904,13 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
@@ -4885,16 +4924,16 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
@@ -4907,13 +4946,13 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
@@ -4927,13 +4966,13 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
@@ -4947,13 +4986,13 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
@@ -4967,13 +5006,13 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
@@ -4987,16 +5026,16 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
@@ -5009,13 +5048,13 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
@@ -5029,13 +5068,13 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
@@ -5049,13 +5088,13 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
@@ -5069,13 +5108,13 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
@@ -5089,16 +5128,16 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
@@ -5111,13 +5150,13 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
@@ -5131,16 +5170,16 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
@@ -5153,16 +5192,16 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
@@ -5175,13 +5214,13 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
@@ -5195,13 +5234,13 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
@@ -5215,16 +5254,16 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
@@ -5237,16 +5276,16 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
@@ -5259,13 +5298,13 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
@@ -5279,16 +5318,16 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
@@ -5301,16 +5340,16 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
@@ -5323,16 +5362,16 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
@@ -5345,16 +5384,16 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
@@ -5367,13 +5406,13 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
@@ -5387,13 +5426,13 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
@@ -5407,16 +5446,16 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
@@ -5429,13 +5468,13 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
@@ -5449,13 +5488,13 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
@@ -5469,13 +5508,13 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
@@ -5489,13 +5528,13 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
@@ -5509,13 +5548,13 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
@@ -5529,13 +5568,13 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
@@ -5549,16 +5588,16 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
@@ -5571,13 +5610,13 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -5591,13 +5630,13 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
@@ -5611,13 +5650,13 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>494</v>
+        <v>291</v>
       </c>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
@@ -5631,13 +5670,13 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
@@ -5651,13 +5690,13 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
@@ -5671,16 +5710,16 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
@@ -5693,13 +5732,13 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
@@ -5713,16 +5752,16 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
@@ -5735,16 +5774,16 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
@@ -5757,16 +5796,16 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F181" s="1"/>
       <c r="G181" s="1"/>
@@ -5779,13 +5818,13 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
@@ -5799,13 +5838,13 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
@@ -5819,16 +5858,16 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
@@ -5841,13 +5880,13 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>494</v>
+        <v>291</v>
       </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
@@ -5861,13 +5900,13 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
@@ -5881,16 +5920,16 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F187" s="1"/>
       <c r="G187" s="1"/>
@@ -5903,16 +5942,16 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
@@ -5925,13 +5964,13 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
@@ -5945,13 +5984,13 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
@@ -5965,16 +6004,16 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
@@ -5987,16 +6026,16 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
@@ -6009,16 +6048,16 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
@@ -6031,16 +6070,16 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F194" s="1"/>
       <c r="G194" s="1"/>
@@ -6053,13 +6092,13 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
@@ -6073,16 +6112,16 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
@@ -6095,13 +6134,13 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
@@ -6115,13 +6154,13 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
@@ -6135,16 +6174,16 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
@@ -6157,16 +6196,16 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
@@ -6179,13 +6218,13 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
@@ -6199,13 +6238,13 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
@@ -6219,16 +6258,16 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
@@ -6241,16 +6280,16 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
@@ -6263,16 +6302,16 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
@@ -6285,13 +6324,13 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
@@ -6305,16 +6344,16 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F207" s="1"/>
       <c r="G207" s="1"/>
@@ -6327,16 +6366,16 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
@@ -6349,16 +6388,16 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F209" s="1"/>
       <c r="G209" s="1"/>
@@ -6371,13 +6410,13 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>494</v>
+        <v>291</v>
       </c>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
@@ -6391,13 +6430,13 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
@@ -6411,13 +6450,13 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
@@ -6431,13 +6470,13 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
@@ -6451,16 +6490,16 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F214" s="1"/>
       <c r="G214" s="1"/>
@@ -6473,13 +6512,13 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
@@ -6493,16 +6532,16 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F216" s="1"/>
       <c r="G216" s="1"/>
@@ -6515,16 +6554,16 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>496</v>
+        <v>299</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F217" s="1"/>
       <c r="G217" s="1"/>
@@ -6532,8 +6571,248 @@
       <c r="I217" s="1"/>
       <c r="J217" s="1"/>
     </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A218" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E218" s="1"/>
+      <c r="F218" s="1"/>
+      <c r="G218" s="1"/>
+      <c r="H218" s="1"/>
+      <c r="I218" s="1"/>
+      <c r="J218" s="1"/>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A219" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B219" s="1">
+        <v>0</v>
+      </c>
+      <c r="C219" s="1">
+        <v>0</v>
+      </c>
+      <c r="D219" s="1">
+        <v>0</v>
+      </c>
+      <c r="E219" s="1"/>
+      <c r="F219" s="1"/>
+      <c r="G219" s="1"/>
+      <c r="H219" s="1"/>
+      <c r="I219" s="1"/>
+      <c r="J219" s="1"/>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A220" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B220" s="1">
+        <v>0</v>
+      </c>
+      <c r="C220" s="1">
+        <v>0</v>
+      </c>
+      <c r="D220" s="1">
+        <v>0</v>
+      </c>
+      <c r="E220" s="1"/>
+      <c r="F220" s="1"/>
+      <c r="G220" s="1"/>
+      <c r="H220" s="1"/>
+      <c r="I220" s="1"/>
+      <c r="J220" s="1"/>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A221" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B221" s="1">
+        <v>0</v>
+      </c>
+      <c r="C221" s="1">
+        <v>0</v>
+      </c>
+      <c r="D221" s="1">
+        <v>0</v>
+      </c>
+      <c r="E221" s="1"/>
+      <c r="F221" s="1"/>
+      <c r="G221" s="1"/>
+      <c r="H221" s="1"/>
+      <c r="I221" s="1"/>
+      <c r="J221" s="1"/>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A222" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B222" s="1">
+        <v>0</v>
+      </c>
+      <c r="C222" s="1">
+        <v>0</v>
+      </c>
+      <c r="D222" s="1">
+        <v>0</v>
+      </c>
+      <c r="E222" s="1"/>
+      <c r="F222" s="1"/>
+      <c r="G222" s="1"/>
+      <c r="H222" s="1"/>
+      <c r="I222" s="1"/>
+      <c r="J222" s="1"/>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A223" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B223" s="1">
+        <v>0</v>
+      </c>
+      <c r="C223" s="1">
+        <v>0</v>
+      </c>
+      <c r="D223" s="1">
+        <v>0</v>
+      </c>
+      <c r="E223" s="1"/>
+      <c r="F223" s="1"/>
+      <c r="G223" s="1"/>
+      <c r="H223" s="1"/>
+      <c r="I223" s="1"/>
+      <c r="J223" s="1"/>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A224" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B224" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C224" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D224" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E224" s="1"/>
+      <c r="F224" s="1"/>
+      <c r="G224" s="1"/>
+      <c r="H224" s="1"/>
+      <c r="I224" s="1"/>
+      <c r="J224" s="1"/>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A225" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B225" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C225" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D225" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E225" s="1"/>
+      <c r="F225" s="1"/>
+      <c r="G225" s="1"/>
+      <c r="H225" s="1"/>
+      <c r="I225" s="1"/>
+      <c r="J225" s="1"/>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A226" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B226" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C226" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D226" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E226" s="1"/>
+      <c r="F226" s="1"/>
+      <c r="G226" s="1"/>
+      <c r="H226" s="1"/>
+      <c r="I226" s="1"/>
+      <c r="J226" s="1"/>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A227" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B227" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C227" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D227" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E227" s="1"/>
+      <c r="F227" s="1"/>
+      <c r="G227" s="1"/>
+      <c r="H227" s="1"/>
+      <c r="I227" s="1"/>
+      <c r="J227" s="1"/>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A228" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B228" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C228" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D228" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E228" s="1"/>
+      <c r="F228" s="1"/>
+      <c r="G228" s="1"/>
+      <c r="H228" s="1"/>
+      <c r="I228" s="1"/>
+      <c r="J228" s="1"/>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A229" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B229" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C229" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D229" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E229" s="1"/>
+      <c r="F229" s="1"/>
+      <c r="G229" s="1"/>
+      <c r="H229" s="1"/>
+      <c r="I229" s="1"/>
+      <c r="J229" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E217" xr:uid="{CC757972-15C5-427C-AB07-EDA7DBD0B6ED}"/>
+  <autoFilter ref="A1:E229" xr:uid="{CC757972-15C5-427C-AB07-EDA7DBD0B6ED}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6542,7 +6821,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3D0D685-D75C-4894-B13E-60533E1B3A71}">
-  <dimension ref="A1:AF217"/>
+  <dimension ref="A1:AF229"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" customWidth="1"/>
@@ -6580,82 +6859,82 @@
         <v>3</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="X1" s="7" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="Y1" s="7" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="Z1" s="7" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AA1" s="7" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AB1" s="7" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AC1" s="7" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
@@ -6666,10 +6945,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -6708,10 +6987,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -6750,10 +7029,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -6792,10 +7071,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -6834,10 +7113,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -6876,10 +7155,10 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -6918,10 +7197,10 @@
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -6960,10 +7239,10 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -7002,10 +7281,10 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -7044,10 +7323,10 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -7086,10 +7365,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -7128,10 +7407,10 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -7170,10 +7449,10 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -7212,10 +7491,10 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -7254,10 +7533,10 @@
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -7296,10 +7575,10 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -7338,10 +7617,10 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -7380,10 +7659,10 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D19" s="1">
         <v>25</v>
@@ -7472,10 +7751,10 @@
         <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D20" s="1">
         <v>18</v>
@@ -7550,10 +7829,10 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D21" s="1">
         <v>23</v>
@@ -7638,10 +7917,10 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -7680,10 +7959,10 @@
         <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -7722,10 +8001,10 @@
         <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -7764,10 +8043,10 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D25" s="1">
         <v>21</v>
@@ -7848,10 +8127,10 @@
         <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -7890,10 +8169,10 @@
         <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -7932,10 +8211,10 @@
         <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -7974,10 +8253,10 @@
         <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D29" s="1">
         <v>17</v>
@@ -8050,10 +8329,10 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -8092,10 +8371,10 @@
         <v>33</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D31" s="1">
         <v>18</v>
@@ -8170,10 +8449,10 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
@@ -8212,10 +8491,10 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
@@ -8254,10 +8533,10 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
@@ -8296,10 +8575,10 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D35" s="1">
         <v>22</v>
@@ -8382,10 +8661,10 @@
         <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D36" s="1">
         <v>21</v>
@@ -8466,10 +8745,10 @@
         <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
@@ -8508,10 +8787,10 @@
         <v>40</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D38" s="1">
         <v>4</v>
@@ -8558,10 +8837,10 @@
         <v>41</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
@@ -8600,10 +8879,10 @@
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D40" s="1">
         <v>21</v>
@@ -8684,10 +8963,10 @@
         <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D41" s="1">
         <v>21</v>
@@ -8768,10 +9047,10 @@
         <v>44</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
@@ -8810,10 +9089,10 @@
         <v>45</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
@@ -8852,10 +9131,10 @@
         <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
@@ -8894,10 +9173,10 @@
         <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
@@ -8936,10 +9215,10 @@
         <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
@@ -8978,10 +9257,10 @@
         <v>49</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
@@ -9020,10 +9299,10 @@
         <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
@@ -9062,10 +9341,10 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
@@ -9104,10 +9383,10 @@
         <v>52</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
@@ -9146,10 +9425,10 @@
         <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
@@ -9188,10 +9467,10 @@
         <v>54</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -9230,10 +9509,10 @@
         <v>55</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
@@ -9272,10 +9551,10 @@
         <v>56</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
@@ -9314,10 +9593,10 @@
         <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
@@ -9356,10 +9635,10 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -9398,10 +9677,10 @@
         <v>59</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D57" s="1">
         <v>21</v>
@@ -9482,10 +9761,10 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D58" s="1">
         <v>21</v>
@@ -9566,10 +9845,10 @@
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
@@ -9608,17 +9887,23 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D60" s="1">
-        <v>9</v>
-      </c>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="E60" s="10">
+        <v>46251</v>
+      </c>
+      <c r="F60" s="10">
+        <v>46251</v>
+      </c>
+      <c r="G60" s="10">
+        <v>46251</v>
+      </c>
       <c r="H60" s="6"/>
       <c r="I60" s="10">
         <v>46197</v>
@@ -9649,8 +9934,12 @@
         <v>46228</v>
       </c>
       <c r="W60" s="6"/>
-      <c r="X60" s="6"/>
-      <c r="Y60" s="6"/>
+      <c r="X60" s="10">
+        <v>46251</v>
+      </c>
+      <c r="Y60" s="10">
+        <v>46251</v>
+      </c>
       <c r="Z60" s="6"/>
       <c r="AA60" s="9">
         <v>46192</v>
@@ -9668,10 +9957,10 @@
         <v>63</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
@@ -9710,10 +9999,10 @@
         <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
@@ -9752,10 +10041,10 @@
         <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D63" s="1">
         <v>14</v>
@@ -9822,10 +10111,10 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D64" s="1">
         <v>12</v>
@@ -9888,10 +10177,10 @@
         <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
@@ -9930,10 +10219,10 @@
         <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
@@ -9972,10 +10261,10 @@
         <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
@@ -10014,10 +10303,10 @@
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
@@ -10056,10 +10345,10 @@
         <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
@@ -10098,10 +10387,10 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
@@ -10140,10 +10429,10 @@
         <v>73</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D71" s="1">
         <v>21</v>
@@ -10224,10 +10513,10 @@
         <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
@@ -10266,10 +10555,10 @@
         <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
@@ -10308,10 +10597,10 @@
         <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D74" s="1">
         <v>25</v>
@@ -10400,10 +10689,10 @@
         <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
@@ -10442,10 +10731,10 @@
         <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D76" s="1">
         <v>21</v>
@@ -10526,10 +10815,10 @@
         <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D77" s="1">
         <v>21</v>
@@ -10610,10 +10899,10 @@
         <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D78" s="1">
         <v>21</v>
@@ -10694,10 +10983,10 @@
         <v>81</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
@@ -10736,17 +11025,23 @@
         <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D80" s="1">
-        <v>9</v>
-      </c>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="E80" s="10">
+        <v>46251</v>
+      </c>
+      <c r="F80" s="10">
+        <v>46251</v>
+      </c>
+      <c r="G80" s="10">
+        <v>46251</v>
+      </c>
       <c r="H80" s="6"/>
       <c r="I80" s="10">
         <v>46197</v>
@@ -10777,8 +11072,12 @@
         <v>46228</v>
       </c>
       <c r="W80" s="6"/>
-      <c r="X80" s="6"/>
-      <c r="Y80" s="6"/>
+      <c r="X80" s="10">
+        <v>46251</v>
+      </c>
+      <c r="Y80" s="10">
+        <v>46251</v>
+      </c>
       <c r="Z80" s="6"/>
       <c r="AA80" s="9">
         <v>46192</v>
@@ -10796,17 +11095,23 @@
         <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D81" s="1">
-        <v>9</v>
-      </c>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="E81" s="10">
+        <v>46251</v>
+      </c>
+      <c r="F81" s="10">
+        <v>46251</v>
+      </c>
+      <c r="G81" s="10">
+        <v>46251</v>
+      </c>
       <c r="H81" s="6"/>
       <c r="I81" s="10">
         <v>46197</v>
@@ -10837,8 +11142,12 @@
         <v>46228</v>
       </c>
       <c r="W81" s="6"/>
-      <c r="X81" s="6"/>
-      <c r="Y81" s="6"/>
+      <c r="X81" s="10">
+        <v>46251</v>
+      </c>
+      <c r="Y81" s="10">
+        <v>46251</v>
+      </c>
       <c r="Z81" s="6"/>
       <c r="AA81" s="9">
         <v>46192</v>
@@ -10856,10 +11165,10 @@
         <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
@@ -10898,10 +11207,10 @@
         <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
@@ -10940,10 +11249,10 @@
         <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
@@ -10982,10 +11291,10 @@
         <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
@@ -11024,10 +11333,10 @@
         <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
@@ -11066,10 +11375,10 @@
         <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
@@ -11108,10 +11417,10 @@
         <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
@@ -11150,10 +11459,10 @@
         <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
@@ -11192,10 +11501,10 @@
         <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D90" s="1">
         <v>25</v>
@@ -11284,10 +11593,10 @@
         <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
@@ -11326,10 +11635,10 @@
         <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D92" s="1">
         <v>11</v>
@@ -11390,10 +11699,10 @@
         <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
@@ -11432,10 +11741,10 @@
         <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
@@ -11474,10 +11783,10 @@
         <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
@@ -11516,10 +11825,10 @@
         <v>98</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
@@ -11558,10 +11867,10 @@
         <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
@@ -11600,10 +11909,10 @@
         <v>100</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
@@ -11642,10 +11951,10 @@
         <v>101</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
@@ -11684,17 +11993,23 @@
         <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D100" s="1">
-        <v>9</v>
-      </c>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="E100" s="10">
+        <v>46251</v>
+      </c>
+      <c r="F100" s="10">
+        <v>46251</v>
+      </c>
+      <c r="G100" s="10">
+        <v>46251</v>
+      </c>
       <c r="H100" s="6"/>
       <c r="I100" s="8">
         <v>46227</v>
@@ -11725,8 +12040,12 @@
         <v>46228</v>
       </c>
       <c r="W100" s="6"/>
-      <c r="X100" s="6"/>
-      <c r="Y100" s="6"/>
+      <c r="X100" s="10">
+        <v>46251</v>
+      </c>
+      <c r="Y100" s="10">
+        <v>46251</v>
+      </c>
       <c r="Z100" s="6"/>
       <c r="AA100" s="8">
         <v>46227</v>
@@ -11744,10 +12063,10 @@
         <v>103</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D101" s="1">
         <v>17</v>
@@ -11820,10 +12139,10 @@
         <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
@@ -11862,10 +12181,10 @@
         <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D103" s="1">
         <v>25</v>
@@ -11954,10 +12273,10 @@
         <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
@@ -11996,10 +12315,10 @@
         <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
@@ -12038,10 +12357,10 @@
         <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D106" s="1">
         <v>21</v>
@@ -12122,10 +12441,10 @@
         <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
@@ -12164,10 +12483,10 @@
         <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D108" s="1">
         <v>4</v>
@@ -12214,10 +12533,10 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D109" s="1">
         <v>21</v>
@@ -12298,10 +12617,10 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
@@ -12340,10 +12659,10 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
@@ -12382,10 +12701,10 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
@@ -12424,10 +12743,10 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
@@ -12466,10 +12785,10 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
@@ -12508,10 +12827,10 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D115" s="1">
         <v>21</v>
@@ -12592,10 +12911,10 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
@@ -12634,10 +12953,10 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D117" s="1">
         <v>0</v>
@@ -12676,10 +12995,10 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D118" s="1">
         <v>0</v>
@@ -12718,10 +13037,10 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
@@ -12760,10 +13079,10 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
@@ -12802,10 +13121,10 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D121" s="1">
         <v>18</v>
@@ -12880,10 +13199,10 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D122" s="1">
         <v>0</v>
@@ -12922,10 +13241,10 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
@@ -12964,10 +13283,10 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D124" s="1">
         <v>0</v>
@@ -13006,10 +13325,10 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D125" s="1">
         <v>0</v>
@@ -13048,10 +13367,10 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D126" s="1">
         <v>19</v>
@@ -13128,10 +13447,10 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
@@ -13170,10 +13489,10 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
@@ -13212,10 +13531,10 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D129" s="1">
         <v>0</v>
@@ -13254,10 +13573,10 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
@@ -13296,10 +13615,10 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
@@ -13338,10 +13657,10 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D132" s="1">
         <v>21</v>
@@ -13422,10 +13741,10 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D133" s="1">
         <v>0</v>
@@ -13464,10 +13783,10 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D134" s="1">
         <v>0</v>
@@ -13506,17 +13825,23 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D135" s="1">
-        <v>9</v>
-      </c>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="E135" s="10">
+        <v>46251</v>
+      </c>
+      <c r="F135" s="10">
+        <v>46251</v>
+      </c>
+      <c r="G135" s="10">
+        <v>46251</v>
+      </c>
       <c r="H135" s="6"/>
       <c r="I135" s="10">
         <v>46197</v>
@@ -13547,8 +13872,12 @@
         <v>46228</v>
       </c>
       <c r="W135" s="6"/>
-      <c r="X135" s="6"/>
-      <c r="Y135" s="6"/>
+      <c r="X135" s="10">
+        <v>46251</v>
+      </c>
+      <c r="Y135" s="10">
+        <v>46251</v>
+      </c>
       <c r="Z135" s="6"/>
       <c r="AA135" s="9">
         <v>46192</v>
@@ -13566,10 +13895,10 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D136" s="1">
         <v>0</v>
@@ -13608,10 +13937,10 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D137" s="1">
         <v>18</v>
@@ -13686,10 +14015,10 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
@@ -13728,10 +14057,10 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D139" s="1">
         <v>21</v>
@@ -13812,10 +14141,10 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D140" s="1">
         <v>0</v>
@@ -13854,10 +14183,10 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D141" s="1">
         <v>0</v>
@@ -13896,10 +14225,10 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D142" s="1">
         <v>0</v>
@@ -13938,7 +14267,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -13980,10 +14309,10 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D144" s="1">
         <v>21</v>
@@ -14064,10 +14393,10 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D145" s="1">
         <v>0</v>
@@ -14106,10 +14435,10 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D146" s="1">
         <v>0</v>
@@ -14148,10 +14477,10 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D147" s="1">
         <v>0</v>
@@ -14190,10 +14519,10 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D148" s="1">
         <v>0</v>
@@ -14232,10 +14561,10 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D149" s="1">
         <v>21</v>
@@ -14316,10 +14645,10 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
@@ -14358,10 +14687,10 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D151" s="1">
         <v>13</v>
@@ -14426,10 +14755,10 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D152" s="1">
         <v>0</v>
@@ -14468,10 +14797,10 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D153" s="1">
         <v>0</v>
@@ -14510,10 +14839,10 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D154" s="1">
         <v>0</v>
@@ -14552,10 +14881,10 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D155" s="1">
         <v>11</v>
@@ -14616,10 +14945,10 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D156" s="1">
         <v>0</v>
@@ -14658,10 +14987,10 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D157" s="1">
         <v>0</v>
@@ -14700,10 +15029,10 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D158" s="1">
         <v>0</v>
@@ -14742,10 +15071,10 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D159" s="1">
         <v>20</v>
@@ -14824,10 +15153,10 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D160" s="1">
         <v>0</v>
@@ -14866,10 +15195,10 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D161" s="1">
         <v>19</v>
@@ -14946,10 +15275,10 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D162" s="1">
         <v>0</v>
@@ -14988,10 +15317,10 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D163" s="1">
         <v>0</v>
@@ -15030,10 +15359,10 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D164" s="1">
         <v>0</v>
@@ -15072,10 +15401,10 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D165" s="1">
         <v>0</v>
@@ -15114,10 +15443,10 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D166" s="1">
         <v>0</v>
@@ -15156,10 +15485,10 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D167" s="1">
         <v>0</v>
@@ -15198,10 +15527,10 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D168" s="1">
         <v>0</v>
@@ -15240,10 +15569,10 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D169" s="1">
         <v>0</v>
@@ -15282,10 +15611,10 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D170" s="1">
         <v>0</v>
@@ -15324,10 +15653,10 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D171" s="1">
         <v>0</v>
@@ -15366,10 +15695,10 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D172" s="1">
         <v>0</v>
@@ -15408,10 +15737,10 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D173" s="1">
         <v>0</v>
@@ -15450,10 +15779,10 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="D174" s="1">
         <v>0</v>
@@ -15492,10 +15821,10 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D175" s="1">
         <v>0</v>
@@ -15534,10 +15863,10 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D176" s="1">
         <v>0</v>
@@ -15576,10 +15905,10 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D177" s="1">
         <v>22</v>
@@ -15662,10 +15991,10 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D178" s="1">
         <v>0</v>
@@ -15704,10 +16033,10 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D179" s="1">
         <v>14</v>
@@ -15774,10 +16103,10 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D180" s="1">
         <v>18</v>
@@ -15852,10 +16181,10 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D181" s="1">
         <v>15</v>
@@ -15924,10 +16253,10 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D182" s="1">
         <v>0</v>
@@ -15966,10 +16295,10 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D183" s="1">
         <v>0</v>
@@ -16008,10 +16337,10 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D184" s="1">
         <v>0</v>
@@ -16050,10 +16379,10 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="D185" s="1">
         <v>0</v>
@@ -16092,10 +16421,10 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D186" s="1">
         <v>0</v>
@@ -16134,10 +16463,10 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D187" s="1">
         <v>0</v>
@@ -16176,10 +16505,10 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D188" s="1">
         <v>19</v>
@@ -16256,10 +16585,10 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="D189" s="1">
         <v>0</v>
@@ -16298,10 +16627,10 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D190" s="1">
         <v>0</v>
@@ -16340,10 +16669,10 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D191" s="1">
         <v>21</v>
@@ -16424,10 +16753,10 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D192" s="1">
         <v>19</v>
@@ -16504,10 +16833,10 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D193" s="1">
         <v>15</v>
@@ -16576,10 +16905,10 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D194" s="1">
         <v>0</v>
@@ -16618,10 +16947,10 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D195" s="1">
         <v>0</v>
@@ -16660,10 +16989,10 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D196" s="1">
         <v>0</v>
@@ -16702,10 +17031,10 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D197" s="1">
         <v>0</v>
@@ -16744,10 +17073,10 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D198" s="1">
         <v>0</v>
@@ -16786,10 +17115,10 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D199" s="1">
         <v>25</v>
@@ -16878,10 +17207,10 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D200" s="1">
         <v>21</v>
@@ -16962,10 +17291,10 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D201" s="1">
         <v>0</v>
@@ -17004,10 +17333,10 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D202" s="1">
         <v>0</v>
@@ -17046,10 +17375,10 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D203" s="1">
         <v>21</v>
@@ -17130,10 +17459,10 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D204" s="1">
         <v>18</v>
@@ -17208,10 +17537,10 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D205" s="1">
         <v>0</v>
@@ -17250,10 +17579,10 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D206" s="1">
         <v>0</v>
@@ -17292,10 +17621,10 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D207" s="1">
         <v>8</v>
@@ -17350,10 +17679,10 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D208" s="1">
         <v>14</v>
@@ -17420,10 +17749,10 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D209" s="1">
         <v>21</v>
@@ -17504,10 +17833,10 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D210" s="1">
         <v>0</v>
@@ -17546,10 +17875,10 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D211" s="1">
         <v>0</v>
@@ -17588,10 +17917,10 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D212" s="1">
         <v>0</v>
@@ -17630,10 +17959,10 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="D213" s="1">
         <v>0</v>
@@ -17672,10 +18001,10 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D214" s="1">
         <v>18</v>
@@ -17750,10 +18079,10 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D215" s="1">
         <v>0</v>
@@ -17792,10 +18121,10 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D216" s="1">
         <v>21</v>
@@ -17876,10 +18205,10 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D217" s="1">
         <v>21</v>
@@ -17955,6 +18284,510 @@
       <c r="AE217" s="6"/>
       <c r="AF217" s="6"/>
     </row>
+    <row r="218" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A218" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D218" s="1">
+        <v>0</v>
+      </c>
+      <c r="E218" s="6"/>
+      <c r="F218" s="6"/>
+      <c r="G218" s="6"/>
+      <c r="H218" s="6"/>
+      <c r="I218" s="6"/>
+      <c r="J218" s="6"/>
+      <c r="K218" s="6"/>
+      <c r="L218" s="6"/>
+      <c r="M218" s="6"/>
+      <c r="N218" s="6"/>
+      <c r="O218" s="6"/>
+      <c r="P218" s="6"/>
+      <c r="Q218" s="6"/>
+      <c r="R218" s="6"/>
+      <c r="S218" s="6"/>
+      <c r="T218" s="6"/>
+      <c r="U218" s="6"/>
+      <c r="V218" s="6"/>
+      <c r="W218" s="6"/>
+      <c r="X218" s="6"/>
+      <c r="Y218" s="6"/>
+      <c r="Z218" s="6"/>
+      <c r="AA218" s="6"/>
+      <c r="AB218" s="6"/>
+      <c r="AC218" s="6"/>
+      <c r="AD218" s="6"/>
+      <c r="AE218" s="6"/>
+      <c r="AF218" s="6"/>
+    </row>
+    <row r="219" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A219" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B219" s="1">
+        <v>0</v>
+      </c>
+      <c r="C219" s="1">
+        <v>0</v>
+      </c>
+      <c r="D219" s="1">
+        <v>0</v>
+      </c>
+      <c r="E219" s="6"/>
+      <c r="F219" s="6"/>
+      <c r="G219" s="6"/>
+      <c r="H219" s="6"/>
+      <c r="I219" s="6"/>
+      <c r="J219" s="6"/>
+      <c r="K219" s="6"/>
+      <c r="L219" s="6"/>
+      <c r="M219" s="6"/>
+      <c r="N219" s="6"/>
+      <c r="O219" s="6"/>
+      <c r="P219" s="6"/>
+      <c r="Q219" s="6"/>
+      <c r="R219" s="6"/>
+      <c r="S219" s="6"/>
+      <c r="T219" s="6"/>
+      <c r="U219" s="6"/>
+      <c r="V219" s="6"/>
+      <c r="W219" s="6"/>
+      <c r="X219" s="6"/>
+      <c r="Y219" s="6"/>
+      <c r="Z219" s="6"/>
+      <c r="AA219" s="6"/>
+      <c r="AB219" s="6"/>
+      <c r="AC219" s="6"/>
+      <c r="AD219" s="6"/>
+      <c r="AE219" s="6"/>
+      <c r="AF219" s="6"/>
+    </row>
+    <row r="220" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A220" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B220" s="1">
+        <v>0</v>
+      </c>
+      <c r="C220" s="1">
+        <v>0</v>
+      </c>
+      <c r="D220" s="1">
+        <v>0</v>
+      </c>
+      <c r="E220" s="6"/>
+      <c r="F220" s="6"/>
+      <c r="G220" s="6"/>
+      <c r="H220" s="6"/>
+      <c r="I220" s="6"/>
+      <c r="J220" s="6"/>
+      <c r="K220" s="6"/>
+      <c r="L220" s="6"/>
+      <c r="M220" s="6"/>
+      <c r="N220" s="6"/>
+      <c r="O220" s="6"/>
+      <c r="P220" s="6"/>
+      <c r="Q220" s="6"/>
+      <c r="R220" s="6"/>
+      <c r="S220" s="6"/>
+      <c r="T220" s="6"/>
+      <c r="U220" s="6"/>
+      <c r="V220" s="6"/>
+      <c r="W220" s="6"/>
+      <c r="X220" s="6"/>
+      <c r="Y220" s="6"/>
+      <c r="Z220" s="6"/>
+      <c r="AA220" s="6"/>
+      <c r="AB220" s="6"/>
+      <c r="AC220" s="6"/>
+      <c r="AD220" s="6"/>
+      <c r="AE220" s="6"/>
+      <c r="AF220" s="6"/>
+    </row>
+    <row r="221" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A221" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B221" s="1">
+        <v>0</v>
+      </c>
+      <c r="C221" s="1">
+        <v>0</v>
+      </c>
+      <c r="D221" s="1">
+        <v>0</v>
+      </c>
+      <c r="E221" s="6"/>
+      <c r="F221" s="6"/>
+      <c r="G221" s="6"/>
+      <c r="H221" s="6"/>
+      <c r="I221" s="6"/>
+      <c r="J221" s="6"/>
+      <c r="K221" s="6"/>
+      <c r="L221" s="6"/>
+      <c r="M221" s="6"/>
+      <c r="N221" s="6"/>
+      <c r="O221" s="6"/>
+      <c r="P221" s="6"/>
+      <c r="Q221" s="6"/>
+      <c r="R221" s="6"/>
+      <c r="S221" s="6"/>
+      <c r="T221" s="6"/>
+      <c r="U221" s="6"/>
+      <c r="V221" s="6"/>
+      <c r="W221" s="6"/>
+      <c r="X221" s="6"/>
+      <c r="Y221" s="6"/>
+      <c r="Z221" s="6"/>
+      <c r="AA221" s="6"/>
+      <c r="AB221" s="6"/>
+      <c r="AC221" s="6"/>
+      <c r="AD221" s="6"/>
+      <c r="AE221" s="6"/>
+      <c r="AF221" s="6"/>
+    </row>
+    <row r="222" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A222" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B222" s="1">
+        <v>0</v>
+      </c>
+      <c r="C222" s="1">
+        <v>0</v>
+      </c>
+      <c r="D222" s="1">
+        <v>0</v>
+      </c>
+      <c r="E222" s="6"/>
+      <c r="F222" s="6"/>
+      <c r="G222" s="6"/>
+      <c r="H222" s="6"/>
+      <c r="I222" s="6"/>
+      <c r="J222" s="6"/>
+      <c r="K222" s="6"/>
+      <c r="L222" s="6"/>
+      <c r="M222" s="6"/>
+      <c r="N222" s="6"/>
+      <c r="O222" s="6"/>
+      <c r="P222" s="6"/>
+      <c r="Q222" s="6"/>
+      <c r="R222" s="6"/>
+      <c r="S222" s="6"/>
+      <c r="T222" s="6"/>
+      <c r="U222" s="6"/>
+      <c r="V222" s="6"/>
+      <c r="W222" s="6"/>
+      <c r="X222" s="6"/>
+      <c r="Y222" s="6"/>
+      <c r="Z222" s="6"/>
+      <c r="AA222" s="6"/>
+      <c r="AB222" s="6"/>
+      <c r="AC222" s="6"/>
+      <c r="AD222" s="6"/>
+      <c r="AE222" s="6"/>
+      <c r="AF222" s="6"/>
+    </row>
+    <row r="223" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A223" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B223" s="1">
+        <v>0</v>
+      </c>
+      <c r="C223" s="1">
+        <v>0</v>
+      </c>
+      <c r="D223" s="1">
+        <v>0</v>
+      </c>
+      <c r="E223" s="6"/>
+      <c r="F223" s="6"/>
+      <c r="G223" s="6"/>
+      <c r="H223" s="6"/>
+      <c r="I223" s="6"/>
+      <c r="J223" s="6"/>
+      <c r="K223" s="6"/>
+      <c r="L223" s="6"/>
+      <c r="M223" s="6"/>
+      <c r="N223" s="6"/>
+      <c r="O223" s="6"/>
+      <c r="P223" s="6"/>
+      <c r="Q223" s="6"/>
+      <c r="R223" s="6"/>
+      <c r="S223" s="6"/>
+      <c r="T223" s="6"/>
+      <c r="U223" s="6"/>
+      <c r="V223" s="6"/>
+      <c r="W223" s="6"/>
+      <c r="X223" s="6"/>
+      <c r="Y223" s="6"/>
+      <c r="Z223" s="6"/>
+      <c r="AA223" s="6"/>
+      <c r="AB223" s="6"/>
+      <c r="AC223" s="6"/>
+      <c r="AD223" s="6"/>
+      <c r="AE223" s="6"/>
+      <c r="AF223" s="6"/>
+    </row>
+    <row r="224" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A224" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B224" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C224" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D224" s="1">
+        <v>0</v>
+      </c>
+      <c r="E224" s="6"/>
+      <c r="F224" s="6"/>
+      <c r="G224" s="6"/>
+      <c r="H224" s="6"/>
+      <c r="I224" s="6"/>
+      <c r="J224" s="6"/>
+      <c r="K224" s="6"/>
+      <c r="L224" s="6"/>
+      <c r="M224" s="6"/>
+      <c r="N224" s="6"/>
+      <c r="O224" s="6"/>
+      <c r="P224" s="6"/>
+      <c r="Q224" s="6"/>
+      <c r="R224" s="6"/>
+      <c r="S224" s="6"/>
+      <c r="T224" s="6"/>
+      <c r="U224" s="6"/>
+      <c r="V224" s="6"/>
+      <c r="W224" s="6"/>
+      <c r="X224" s="6"/>
+      <c r="Y224" s="6"/>
+      <c r="Z224" s="6"/>
+      <c r="AA224" s="6"/>
+      <c r="AB224" s="6"/>
+      <c r="AC224" s="6"/>
+      <c r="AD224" s="6"/>
+      <c r="AE224" s="6"/>
+      <c r="AF224" s="6"/>
+    </row>
+    <row r="225" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A225" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B225" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C225" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D225" s="1">
+        <v>0</v>
+      </c>
+      <c r="E225" s="6"/>
+      <c r="F225" s="6"/>
+      <c r="G225" s="6"/>
+      <c r="H225" s="6"/>
+      <c r="I225" s="6"/>
+      <c r="J225" s="6"/>
+      <c r="K225" s="6"/>
+      <c r="L225" s="6"/>
+      <c r="M225" s="6"/>
+      <c r="N225" s="6"/>
+      <c r="O225" s="6"/>
+      <c r="P225" s="6"/>
+      <c r="Q225" s="6"/>
+      <c r="R225" s="6"/>
+      <c r="S225" s="6"/>
+      <c r="T225" s="6"/>
+      <c r="U225" s="6"/>
+      <c r="V225" s="6"/>
+      <c r="W225" s="6"/>
+      <c r="X225" s="6"/>
+      <c r="Y225" s="6"/>
+      <c r="Z225" s="6"/>
+      <c r="AA225" s="6"/>
+      <c r="AB225" s="6"/>
+      <c r="AC225" s="6"/>
+      <c r="AD225" s="6"/>
+      <c r="AE225" s="6"/>
+      <c r="AF225" s="6"/>
+    </row>
+    <row r="226" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A226" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B226" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C226" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D226" s="1">
+        <v>0</v>
+      </c>
+      <c r="E226" s="6"/>
+      <c r="F226" s="6"/>
+      <c r="G226" s="6"/>
+      <c r="H226" s="6"/>
+      <c r="I226" s="6"/>
+      <c r="J226" s="6"/>
+      <c r="K226" s="6"/>
+      <c r="L226" s="6"/>
+      <c r="M226" s="6"/>
+      <c r="N226" s="6"/>
+      <c r="O226" s="6"/>
+      <c r="P226" s="6"/>
+      <c r="Q226" s="6"/>
+      <c r="R226" s="6"/>
+      <c r="S226" s="6"/>
+      <c r="T226" s="6"/>
+      <c r="U226" s="6"/>
+      <c r="V226" s="6"/>
+      <c r="W226" s="6"/>
+      <c r="X226" s="6"/>
+      <c r="Y226" s="6"/>
+      <c r="Z226" s="6"/>
+      <c r="AA226" s="6"/>
+      <c r="AB226" s="6"/>
+      <c r="AC226" s="6"/>
+      <c r="AD226" s="6"/>
+      <c r="AE226" s="6"/>
+      <c r="AF226" s="6"/>
+    </row>
+    <row r="227" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A227" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B227" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C227" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D227" s="1">
+        <v>0</v>
+      </c>
+      <c r="E227" s="6"/>
+      <c r="F227" s="6"/>
+      <c r="G227" s="6"/>
+      <c r="H227" s="6"/>
+      <c r="I227" s="6"/>
+      <c r="J227" s="6"/>
+      <c r="K227" s="6"/>
+      <c r="L227" s="6"/>
+      <c r="M227" s="6"/>
+      <c r="N227" s="6"/>
+      <c r="O227" s="6"/>
+      <c r="P227" s="6"/>
+      <c r="Q227" s="6"/>
+      <c r="R227" s="6"/>
+      <c r="S227" s="6"/>
+      <c r="T227" s="6"/>
+      <c r="U227" s="6"/>
+      <c r="V227" s="6"/>
+      <c r="W227" s="6"/>
+      <c r="X227" s="6"/>
+      <c r="Y227" s="6"/>
+      <c r="Z227" s="6"/>
+      <c r="AA227" s="6"/>
+      <c r="AB227" s="6"/>
+      <c r="AC227" s="6"/>
+      <c r="AD227" s="6"/>
+      <c r="AE227" s="6"/>
+      <c r="AF227" s="6"/>
+    </row>
+    <row r="228" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A228" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B228" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C228" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D228" s="1">
+        <v>0</v>
+      </c>
+      <c r="E228" s="6"/>
+      <c r="F228" s="6"/>
+      <c r="G228" s="6"/>
+      <c r="H228" s="6"/>
+      <c r="I228" s="6"/>
+      <c r="J228" s="6"/>
+      <c r="K228" s="6"/>
+      <c r="L228" s="6"/>
+      <c r="M228" s="6"/>
+      <c r="N228" s="6"/>
+      <c r="O228" s="6"/>
+      <c r="P228" s="6"/>
+      <c r="Q228" s="6"/>
+      <c r="R228" s="6"/>
+      <c r="S228" s="6"/>
+      <c r="T228" s="6"/>
+      <c r="U228" s="6"/>
+      <c r="V228" s="6"/>
+      <c r="W228" s="6"/>
+      <c r="X228" s="6"/>
+      <c r="Y228" s="6"/>
+      <c r="Z228" s="6"/>
+      <c r="AA228" s="6"/>
+      <c r="AB228" s="6"/>
+      <c r="AC228" s="6"/>
+      <c r="AD228" s="6"/>
+      <c r="AE228" s="6"/>
+      <c r="AF228" s="6"/>
+    </row>
+    <row r="229" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A229" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B229" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C229" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D229" s="1">
+        <v>0</v>
+      </c>
+      <c r="E229" s="6"/>
+      <c r="F229" s="6"/>
+      <c r="G229" s="6"/>
+      <c r="H229" s="6"/>
+      <c r="I229" s="6"/>
+      <c r="J229" s="6"/>
+      <c r="K229" s="6"/>
+      <c r="L229" s="6"/>
+      <c r="M229" s="6"/>
+      <c r="N229" s="6"/>
+      <c r="O229" s="6"/>
+      <c r="P229" s="6"/>
+      <c r="Q229" s="6"/>
+      <c r="R229" s="6"/>
+      <c r="S229" s="6"/>
+      <c r="T229" s="6"/>
+      <c r="U229" s="6"/>
+      <c r="V229" s="6"/>
+      <c r="W229" s="6"/>
+      <c r="X229" s="6"/>
+      <c r="Y229" s="6"/>
+      <c r="Z229" s="6"/>
+      <c r="AA229" s="6"/>
+      <c r="AB229" s="6"/>
+      <c r="AC229" s="6"/>
+      <c r="AD229" s="6"/>
+      <c r="AE229" s="6"/>
+      <c r="AF229" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
